--- a/research/traditional_assets/database/data/mexico/mexico_household_products.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_household_products.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0479</v>
+        <v>0.0081</v>
       </c>
       <c r="E2">
         <v>0.11</v>
@@ -599,40 +599,40 @@
         <v>0.06150000000000001</v>
       </c>
       <c r="G2">
-        <v>0.2903388426776133</v>
+        <v>0.2765746803332076</v>
       </c>
       <c r="H2">
-        <v>0.2903388426776133</v>
+        <v>0.2765746803332076</v>
       </c>
       <c r="I2">
-        <v>0.2405026826545677</v>
+        <v>0.2238181755853416</v>
       </c>
       <c r="J2">
-        <v>0.1625590391563847</v>
+        <v>0.1875499645747933</v>
       </c>
       <c r="K2">
-        <v>406.9</v>
+        <v>385.2</v>
       </c>
       <c r="L2">
-        <v>0.1465197508191999</v>
+        <v>0.1320489527270234</v>
       </c>
       <c r="M2">
         <v>304.1</v>
       </c>
       <c r="N2">
-        <v>0.07157483465530633</v>
+        <v>0.07153728713481521</v>
       </c>
       <c r="O2">
-        <v>0.7473580732366675</v>
+        <v>0.7894600207684319</v>
       </c>
       <c r="P2">
         <v>273.2</v>
       </c>
       <c r="Q2">
-        <v>0.06430202179490196</v>
+        <v>0.06426828952723287</v>
       </c>
       <c r="R2">
-        <v>0.6714180388301794</v>
+        <v>0.7092419522326064</v>
       </c>
       <c r="S2">
         <v>30.89999999999998</v>
@@ -641,73 +641,73 @@
         <v>0.1016113120683985</v>
       </c>
       <c r="U2">
-        <v>854.8</v>
+        <v>857.76</v>
       </c>
       <c r="V2">
-        <v>0.2011909525266552</v>
+        <v>0.2017817277631013</v>
       </c>
       <c r="W2">
-        <v>1.37003367003367</v>
+        <v>0.5590005748542334</v>
       </c>
       <c r="X2">
-        <v>0.10359746190867</v>
+        <v>0.9058357000135221</v>
       </c>
       <c r="Y2">
-        <v>1.266436208125</v>
+        <v>-0.3468351251592887</v>
       </c>
       <c r="Z2">
-        <v>3.010732870771899</v>
+        <v>2.609446283209589</v>
       </c>
       <c r="AA2">
-        <v>0.4894218426292237</v>
+        <v>0.2063477499591131</v>
       </c>
       <c r="AB2">
-        <v>0.09029038301608203</v>
+        <v>0.08830524147556749</v>
       </c>
       <c r="AC2">
-        <v>0.3991314596131417</v>
+        <v>0.1180425084835457</v>
       </c>
       <c r="AD2">
-        <v>1473.1</v>
+        <v>1583.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1473.1</v>
+        <v>1583.8</v>
       </c>
       <c r="AG2">
-        <v>618.3</v>
+        <v>726.04</v>
       </c>
       <c r="AH2">
-        <v>0.2574539480583034</v>
+        <v>0.2714435800799694</v>
       </c>
       <c r="AI2">
-        <v>0.8158958737191913</v>
+        <v>0.8012749165233229</v>
       </c>
       <c r="AJ2">
-        <v>0.127039243887405</v>
+        <v>0.1458799229249925</v>
       </c>
       <c r="AK2">
-        <v>0.6503628905017356</v>
+        <v>0.6489220978870973</v>
       </c>
       <c r="AL2">
-        <v>132.4</v>
+        <v>147.8</v>
       </c>
       <c r="AM2">
-        <v>62.90000000000001</v>
+        <v>77.97500000000001</v>
       </c>
       <c r="AN2">
-        <v>1.976784755770263</v>
+        <v>2.149507342363128</v>
       </c>
       <c r="AO2">
-        <v>5.044561933534743</v>
+        <v>4.417456021650879</v>
       </c>
       <c r="AP2">
-        <v>0.8297101449275361</v>
+        <v>0.9853695610868325</v>
       </c>
       <c r="AQ2">
-        <v>10.61844197138315</v>
+        <v>8.373196537351713</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>1.37003367003367</v>
       </c>
       <c r="X3">
-        <v>0.10359746190867</v>
+        <v>0.1035844175079526</v>
       </c>
       <c r="Y3">
-        <v>1.266436208125</v>
+        <v>1.266449252525717</v>
       </c>
       <c r="Z3">
         <v>3.010732870771899</v>
@@ -799,10 +799,10 @@
         <v>0.4894218426292237</v>
       </c>
       <c r="AB3">
-        <v>0.09029038301608203</v>
+        <v>0.09028069694782939</v>
       </c>
       <c r="AC3">
-        <v>0.3991314596131417</v>
+        <v>0.3991411456813944</v>
       </c>
       <c r="AD3">
         <v>1473.1</v>
@@ -845,6 +845,134 @@
       </c>
       <c r="AQ3">
         <v>10.61844197138315</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Grupo Vasconia, S.A.B. (BMV:VASCONI *)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0317</v>
+      </c>
+      <c r="G4">
+        <v>0.003542857142857143</v>
+      </c>
+      <c r="H4">
+        <v>0.003542857142857143</v>
+      </c>
+      <c r="I4">
+        <v>-0.1071428571428571</v>
+      </c>
+      <c r="J4">
+        <v>-0.1071428571428571</v>
+      </c>
+      <c r="K4">
+        <v>-21.7</v>
+      </c>
+      <c r="L4">
+        <v>-0.155</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2.96</v>
+      </c>
+      <c r="V4">
+        <v>1.327354260089686</v>
+      </c>
+      <c r="W4">
+        <v>-0.2520325203252032</v>
+      </c>
+      <c r="X4">
+        <v>1.708086982519092</v>
+      </c>
+      <c r="Y4">
+        <v>-1.960119502844295</v>
+      </c>
+      <c r="Z4">
+        <v>0.7161125319693095</v>
+      </c>
+      <c r="AA4">
+        <v>-0.07672634271099744</v>
+      </c>
+      <c r="AB4">
+        <v>0.0863297860033056</v>
+      </c>
+      <c r="AC4">
+        <v>-0.163056128714303</v>
+      </c>
+      <c r="AD4">
+        <v>110.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>110.7</v>
+      </c>
+      <c r="AG4">
+        <v>107.74</v>
+      </c>
+      <c r="AH4">
+        <v>0.980253254228283</v>
+      </c>
+      <c r="AI4">
+        <v>0.646990064289889</v>
+      </c>
+      <c r="AJ4">
+        <v>0.9797217422933527</v>
+      </c>
+      <c r="AK4">
+        <v>0.640775544189366</v>
+      </c>
+      <c r="AL4">
+        <v>15.4</v>
+      </c>
+      <c r="AM4">
+        <v>15.075</v>
+      </c>
+      <c r="AN4">
+        <v>-13.21002386634845</v>
+      </c>
+      <c r="AO4">
+        <v>-0.974025974025974</v>
+      </c>
+      <c r="AP4">
+        <v>-12.85680190930788</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.9950248756218905</v>
       </c>
     </row>
   </sheetData>
@@ -1139,49 +1267,49 @@
         <v>5.04456193353474</v>
       </c>
       <c r="F2">
-        <v>4.57464218178394</v>
+        <v>4.59974489483247</v>
       </c>
       <c r="G2">
         <v>1.97678475577026</v>
       </c>
       <c r="H2">
-        <v>2.61059044551798</v>
+        <v>2.68737251744498</v>
       </c>
       <c r="I2">
         <v>0.257453948058303</v>
       </c>
       <c r="J2">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="K2">
         <v>4248.7</v>
       </c>
       <c r="L2">
-        <v>3778.33205243144</v>
+        <v>3769.01288890318</v>
       </c>
       <c r="M2">
         <v>4867</v>
       </c>
       <c r="N2">
-        <v>4868.94405243144</v>
+        <v>4916.84288890318</v>
       </c>
       <c r="O2">
         <v>1473.1</v>
       </c>
       <c r="P2">
-        <v>1945.412</v>
+        <v>2002.63</v>
       </c>
       <c r="Q2">
-        <v>0.090290383016082</v>
+        <v>0.09028069694782941</v>
       </c>
       <c r="R2">
-        <v>0.0902618068437718</v>
+        <v>0.089555186145549</v>
       </c>
       <c r="S2">
         <v>0.051910241755517</v>
       </c>
       <c r="T2">
-        <v>0.053730241755517</v>
+        <v>0.051910241755517</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1322,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.10359746190867</v>
+        <v>0.103584417507953</v>
       </c>
       <c r="X2">
-        <v>0.109081097949842</v>
+        <v>0.109825540817105</v>
       </c>
       <c r="Y2">
         <v>0.840833682912047</v>
       </c>
       <c r="Z2">
-        <v>0.920609260177605</v>
+        <v>0.931649631637675</v>
       </c>
       <c r="AA2">
         <v>1473.1</v>
@@ -1236,7 +1364,7 @@
         <v>4248.7</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524602</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1552,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09230949292527393</v>
+        <v>0.09229899612415422</v>
       </c>
       <c r="C2">
-        <v>5588.261066611122</v>
+        <v>5588.312062476969</v>
       </c>
       <c r="D2">
-        <v>4733.461066611122</v>
+        <v>4733.512062476969</v>
       </c>
       <c r="E2">
         <v>-1473.1</v>
@@ -1475,19 +1603,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09230949292527393</v>
+        <v>0.09229899612415422</v>
       </c>
       <c r="T2">
         <v>0.6766170509100436</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1634,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09220586686405328</v>
+        <v>0.09218560155333692</v>
       </c>
       <c r="C3">
-        <v>5537.717991595659</v>
+        <v>5538.399405683585</v>
       </c>
       <c r="D3">
-        <v>4740.135991595659</v>
+        <v>4740.817405683584</v>
       </c>
       <c r="E3">
         <v>-1415.882</v>
@@ -1539,37 +1667,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M3">
-        <v>4.037158361095958</v>
+        <v>3.957053161095958</v>
       </c>
       <c r="N3">
-        <v>679.0710049042101</v>
+        <v>679.1511101042101</v>
       </c>
       <c r="O3">
-        <v>203.721301471263</v>
+        <v>203.745333031263</v>
       </c>
       <c r="P3">
-        <v>475.3497034329471</v>
+        <v>475.4057770729471</v>
       </c>
       <c r="Q3">
-        <v>552.6497034329471</v>
+        <v>552.7057770729472</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09263834792575566</v>
+        <v>0.09262777690483005</v>
       </c>
       <c r="T3">
         <v>0.6814012118760742</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>169.2051938928311</v>
+        <v>172.6305246493353</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1716,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09210224080283262</v>
+        <v>0.09207220698251964</v>
       </c>
       <c r="C4">
-        <v>5487.193768553701</v>
+        <v>5488.509332768788</v>
       </c>
       <c r="D4">
-        <v>4746.829768553701</v>
+        <v>4748.145332768788</v>
       </c>
       <c r="E4">
         <v>-1358.664</v>
@@ -1621,37 +1749,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M4">
-        <v>8.074316722191917</v>
+        <v>7.914106322191916</v>
       </c>
       <c r="N4">
-        <v>675.0338465431141</v>
+        <v>675.1940569431141</v>
       </c>
       <c r="O4">
-        <v>202.5101539629342</v>
+        <v>202.5582170829342</v>
       </c>
       <c r="P4">
-        <v>472.5236925801799</v>
+        <v>472.6358398601799</v>
       </c>
       <c r="Q4">
-        <v>549.82369258018</v>
+        <v>549.93583986018</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09297391425277785</v>
+        <v>0.09296326749735642</v>
       </c>
       <c r="T4">
         <v>0.6862830087801871</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.60259694641557</v>
+        <v>86.31526232466766</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1798,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09199861474161197</v>
+        <v>0.09195881241170234</v>
       </c>
       <c r="C5">
-        <v>5436.688477463558</v>
+        <v>5438.641948619061</v>
       </c>
       <c r="D5">
-        <v>4753.542477463558</v>
+        <v>4755.49594861906</v>
       </c>
       <c r="E5">
         <v>-1301.446</v>
@@ -1703,37 +1831,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M5">
-        <v>12.11147508328787</v>
+        <v>11.87115948328787</v>
       </c>
       <c r="N5">
-        <v>670.9966881820181</v>
+        <v>671.2370037820182</v>
       </c>
       <c r="O5">
-        <v>201.2990064546054</v>
+        <v>201.3711011346055</v>
       </c>
       <c r="P5">
-        <v>469.6976817274127</v>
+        <v>469.8659026474127</v>
       </c>
       <c r="Q5">
-        <v>546.9976817274128</v>
+        <v>547.1659026474128</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09331639947314069</v>
+        <v>0.09330567542168745</v>
       </c>
       <c r="T5">
         <v>0.6912654612905703</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.40173129761039</v>
+        <v>57.54350821644512</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1880,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09189498868039131</v>
+        <v>0.09184541784088505</v>
       </c>
       <c r="C6">
-        <v>5386.202198756585</v>
+        <v>5388.797358771387</v>
       </c>
       <c r="D6">
-        <v>4760.274198756585</v>
+        <v>4762.869358771387</v>
       </c>
       <c r="E6">
         <v>-1244.228</v>
@@ -1785,37 +1913,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M6">
-        <v>16.14863344438383</v>
+        <v>15.82821264438383</v>
       </c>
       <c r="N6">
-        <v>666.9595298209223</v>
+        <v>667.2799506209222</v>
       </c>
       <c r="O6">
-        <v>200.0878589462767</v>
+        <v>200.1839851862767</v>
       </c>
       <c r="P6">
-        <v>466.8716708746456</v>
+        <v>467.0959654346456</v>
       </c>
       <c r="Q6">
-        <v>544.1716708746457</v>
+        <v>544.3959654346456</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09366601980226108</v>
+        <v>0.09365521684444206</v>
       </c>
       <c r="T6">
         <v>0.6963517148949199</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.30129847320779</v>
+        <v>43.15763116233384</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1962,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09179136261917066</v>
+        <v>0.09173202327006776</v>
       </c>
       <c r="C7">
-        <v>5335.735013320398</v>
+        <v>5338.975669418313</v>
       </c>
       <c r="D7">
-        <v>4767.025013320398</v>
+        <v>4770.265669418313</v>
       </c>
       <c r="E7">
         <v>-1187.01</v>
@@ -1867,37 +1995,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M7">
-        <v>20.18579180547979</v>
+        <v>19.78526580547979</v>
       </c>
       <c r="N7">
-        <v>662.9223714598263</v>
+        <v>663.3228974598263</v>
       </c>
       <c r="O7">
-        <v>198.8767114379479</v>
+        <v>198.9968692379479</v>
       </c>
       <c r="P7">
-        <v>464.0456600218785</v>
+        <v>464.3260282218785</v>
       </c>
       <c r="Q7">
-        <v>541.3456600218785</v>
+        <v>541.6260282218785</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09402300055936297</v>
+        <v>0.09401211703399148</v>
       </c>
       <c r="T7">
         <v>0.7015450475225189</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +2033,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.84103877856624</v>
+        <v>34.52610492986707</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2044,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09168773655795003</v>
+        <v>0.09161862869925044</v>
       </c>
       <c r="C8">
-        <v>5285.287002502107</v>
+        <v>5289.17698741304</v>
       </c>
       <c r="D8">
-        <v>4773.795002502106</v>
+        <v>4777.68498741304</v>
       </c>
       <c r="E8">
         <v>-1129.792</v>
@@ -1949,37 +2077,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M8">
-        <v>24.22295016657575</v>
+        <v>23.74231896657574</v>
       </c>
       <c r="N8">
-        <v>658.8852130987303</v>
+        <v>659.3658442987303</v>
       </c>
       <c r="O8">
-        <v>197.6655639296191</v>
+        <v>197.8097532896191</v>
       </c>
       <c r="P8">
-        <v>461.2196491691112</v>
+        <v>461.5560910091112</v>
       </c>
       <c r="Q8">
-        <v>538.5196491691113</v>
+        <v>538.8560910091113</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09438757665172234</v>
+        <v>0.09437661084459514</v>
       </c>
       <c r="T8">
         <v>0.706848876589003</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.2008656488052</v>
+        <v>28.77175410822256</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2126,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09158411049672936</v>
+        <v>0.09150523412843316</v>
       </c>
       <c r="C9">
-        <v>5234.858248111586</v>
+        <v>5239.401420274568</v>
       </c>
       <c r="D9">
-        <v>4780.584248111586</v>
+        <v>4785.127420274568</v>
       </c>
       <c r="E9">
         <v>-1072.574</v>
@@ -2031,37 +2159,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M9">
-        <v>28.26010852767171</v>
+        <v>27.69937212767171</v>
       </c>
       <c r="N9">
-        <v>654.8480547376344</v>
+        <v>655.4087911376344</v>
       </c>
       <c r="O9">
-        <v>196.4544164212903</v>
+        <v>196.6226373412903</v>
       </c>
       <c r="P9">
-        <v>458.3936383163441</v>
+        <v>458.786153796344</v>
       </c>
       <c r="Q9">
-        <v>535.6936383163442</v>
+        <v>536.0861537963441</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09475999309015395</v>
+        <v>0.09474894323177095</v>
       </c>
       <c r="T9">
         <v>0.7122667664956266</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.17217055611874</v>
+        <v>24.66150352133362</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2208,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09148048443550873</v>
+        <v>0.09139183955761587</v>
       </c>
       <c r="C10">
-        <v>5184.44883242477</v>
+        <v>5189.649076192898</v>
       </c>
       <c r="D10">
-        <v>4787.39283242477</v>
+        <v>4792.593076192898</v>
       </c>
       <c r="E10">
         <v>-1015.356</v>
@@ -2113,37 +2241,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M10">
-        <v>32.29726688876767</v>
+        <v>31.65642528876766</v>
       </c>
       <c r="N10">
-        <v>650.8108963765384</v>
+        <v>651.4517379765384</v>
       </c>
       <c r="O10">
-        <v>195.2432689129615</v>
+        <v>195.4355213929615</v>
       </c>
       <c r="P10">
-        <v>455.5676274635769</v>
+        <v>456.0162165835769</v>
       </c>
       <c r="Q10">
-        <v>532.8676274635769</v>
+        <v>533.316216583577</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.0951405055381167</v>
+        <v>0.09512936980127665</v>
       </c>
       <c r="T10">
         <v>0.7178024366176116</v>
       </c>
       <c r="U10">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.15064923660389</v>
+        <v>21.57881558116692</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2290,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09137685837428806</v>
+        <v>0.09127844498679859</v>
       </c>
       <c r="C11">
-        <v>5134.058838186977</v>
+        <v>5139.920064034262</v>
       </c>
       <c r="D11">
-        <v>4794.220838186977</v>
+        <v>4800.082064034262</v>
       </c>
       <c r="E11">
         <v>-958.138</v>
@@ -2195,37 +2323,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M11">
-        <v>36.33442524986361</v>
+        <v>35.61347844986361</v>
       </c>
       <c r="N11">
-        <v>646.7737380154424</v>
+        <v>647.4946848154425</v>
       </c>
       <c r="O11">
-        <v>194.0321214046327</v>
+        <v>194.2484054446327</v>
       </c>
       <c r="P11">
-        <v>452.7416166108097</v>
+        <v>453.2462793708098</v>
       </c>
       <c r="Q11">
-        <v>530.0416166108098</v>
+        <v>530.5462793708098</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09552938089702367</v>
+        <v>0.09551815739428797</v>
       </c>
       <c r="T11">
         <v>0.7234597698192005</v>
       </c>
       <c r="U11">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.80057709920347</v>
+        <v>19.18116940548171</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2372,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09127323231306742</v>
+        <v>0.09116505041598129</v>
       </c>
       <c r="C12">
-        <v>5083.688348616259</v>
+        <v>5090.214493346431</v>
       </c>
       <c r="D12">
-        <v>4801.068348616259</v>
+        <v>4807.594493346432</v>
       </c>
       <c r="E12">
         <v>-900.92</v>
@@ -2277,37 +2405,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M12">
-        <v>40.37158361095958</v>
+        <v>39.57053161095958</v>
       </c>
       <c r="N12">
-        <v>642.7365796543465</v>
+        <v>643.5376316543465</v>
       </c>
       <c r="O12">
-        <v>192.820973896304</v>
+        <v>193.0612894963039</v>
       </c>
       <c r="P12">
-        <v>449.9156057580426</v>
+        <v>450.4763421580425</v>
       </c>
       <c r="Q12">
-        <v>527.2156057580427</v>
+        <v>527.7763421580426</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09592689793057302</v>
+        <v>0.09591558471158843</v>
       </c>
       <c r="T12">
         <v>0.7292428215363803</v>
       </c>
       <c r="U12">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.92051938928312</v>
+        <v>17.26305246493353</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2454,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09116960625184677</v>
+        <v>0.091051655845164</v>
       </c>
       <c r="C13">
-        <v>5033.337447406786</v>
+        <v>5040.53247436404</v>
       </c>
       <c r="D13">
-        <v>4807.935447406786</v>
+        <v>4815.13047436404</v>
       </c>
       <c r="E13">
         <v>-843.702</v>
@@ -2359,37 +2487,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M13">
-        <v>44.40874197205554</v>
+        <v>43.52758477205553</v>
       </c>
       <c r="N13">
-        <v>638.6994212932506</v>
+        <v>639.5805784932505</v>
       </c>
       <c r="O13">
-        <v>191.6098263879752</v>
+        <v>191.8741735479751</v>
       </c>
       <c r="P13">
-        <v>447.0895949052754</v>
+        <v>447.7064049452754</v>
       </c>
       <c r="Q13">
-        <v>524.3895949052754</v>
+        <v>525.0064049452754</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09633334793116842</v>
+        <v>0.09632194297983948</v>
       </c>
       <c r="T13">
         <v>0.7351558294719238</v>
       </c>
       <c r="U13">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.38229035389374</v>
+        <v>15.69368405903049</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2536,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.0910659801906261</v>
+        <v>0.0909382612743467</v>
       </c>
       <c r="C14">
-        <v>4983.006218732254</v>
+        <v>4990.874118013992</v>
       </c>
       <c r="D14">
-        <v>4814.822218732254</v>
+        <v>4822.690118013992</v>
       </c>
       <c r="E14">
         <v>-786.484</v>
@@ -2441,37 +2569,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M14">
-        <v>48.44590033315149</v>
+        <v>47.48463793315149</v>
       </c>
       <c r="N14">
-        <v>634.6622629321546</v>
+        <v>635.6235253321546</v>
       </c>
       <c r="O14">
-        <v>190.3986788796464</v>
+        <v>190.6870575996464</v>
       </c>
       <c r="P14">
-        <v>444.2635840525082</v>
+        <v>444.9364677325082</v>
       </c>
       <c r="Q14">
-        <v>521.5635840525083</v>
+        <v>522.2364677325083</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09674903543177735</v>
+        <v>0.09673753666327803</v>
       </c>
       <c r="T14">
         <v>0.7412032239514569</v>
       </c>
       <c r="U14">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.1004328244026</v>
+        <v>14.38587705411128</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2618,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09096235412940547</v>
+        <v>0.09082486670352941</v>
       </c>
       <c r="C15">
-        <v>4932.694747249321</v>
+        <v>4941.239535920892</v>
       </c>
       <c r="D15">
-        <v>4821.728747249321</v>
+        <v>4830.273535920892</v>
       </c>
       <c r="E15">
         <v>-729.266</v>
@@ -2523,37 +2651,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M15">
-        <v>52.48305869424745</v>
+        <v>51.44169109424745</v>
       </c>
       <c r="N15">
-        <v>630.6251045710586</v>
+        <v>631.6664721710587</v>
       </c>
       <c r="O15">
-        <v>189.1875313713176</v>
+        <v>189.4999416513176</v>
       </c>
       <c r="P15">
-        <v>441.437573199741</v>
+        <v>442.1665305197411</v>
       </c>
       <c r="Q15">
-        <v>518.7375731997411</v>
+        <v>519.4665305197411</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09717427896688305</v>
+        <v>0.09716268422449678</v>
       </c>
       <c r="T15">
         <v>0.7473896389937378</v>
       </c>
       <c r="U15">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.0157841456024</v>
+        <v>13.27927112687195</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2700,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09096652806818481</v>
+        <v>0.09085847213271211</v>
       </c>
       <c r="C16">
-        <v>4875.198177264595</v>
+        <v>4881.77164115601</v>
       </c>
       <c r="D16">
-        <v>4821.450177264594</v>
+        <v>4828.02364115601</v>
       </c>
       <c r="E16">
         <v>-672.0479999999999</v>
@@ -2605,37 +2733,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M16">
-        <v>57.40137425534341</v>
+        <v>56.60032225534341</v>
       </c>
       <c r="N16">
-        <v>625.7067890099627</v>
+        <v>626.5078410099627</v>
       </c>
       <c r="O16">
-        <v>187.7120367029888</v>
+        <v>187.9523523029888</v>
       </c>
       <c r="P16">
-        <v>437.9947523069739</v>
+        <v>438.5554887069739</v>
       </c>
       <c r="Q16">
-        <v>515.2947523069739</v>
+        <v>515.855488706974</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09760941188652608</v>
+        <v>0.09759771893830202</v>
       </c>
       <c r="T16">
         <v>0.7537199241532812</v>
       </c>
       <c r="U16">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.90055416141394</v>
+        <v>12.06898010551197</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2782,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09087060200696416</v>
+        <v>0.09075557756189483</v>
       </c>
       <c r="C17">
-        <v>4824.390454192822</v>
+        <v>4831.449092600275</v>
       </c>
       <c r="D17">
-        <v>4827.860454192822</v>
+        <v>4834.919092600275</v>
       </c>
       <c r="E17">
         <v>-614.83</v>
@@ -2687,37 +2815,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M17">
-        <v>61.50147241643936</v>
+        <v>60.64320241643936</v>
       </c>
       <c r="N17">
-        <v>621.6066908488667</v>
+        <v>622.4649608488667</v>
       </c>
       <c r="O17">
-        <v>186.48200725466</v>
+        <v>186.73948825466</v>
       </c>
       <c r="P17">
-        <v>435.1246835942067</v>
+        <v>435.7254725942067</v>
       </c>
       <c r="Q17">
-        <v>512.4246835942067</v>
+        <v>513.0254725942068</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09805478322780778</v>
+        <v>0.09804298976302034</v>
       </c>
       <c r="T17">
         <v>0.7601991571989314</v>
       </c>
       <c r="U17">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.10718388398635</v>
+        <v>11.26438143181117</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2864,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.0907746759457435</v>
+        <v>0.09065268299107752</v>
       </c>
       <c r="C18">
-        <v>4773.599799162499</v>
+        <v>4781.146268577367</v>
       </c>
       <c r="D18">
-        <v>4834.287799162499</v>
+        <v>4841.834268577367</v>
       </c>
       <c r="E18">
         <v>-557.612</v>
@@ -2769,37 +2897,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M18">
-        <v>65.60157057753531</v>
+        <v>64.68608257753532</v>
       </c>
       <c r="N18">
-        <v>617.5065926877708</v>
+        <v>618.4220806877707</v>
       </c>
       <c r="O18">
-        <v>185.2519778063312</v>
+        <v>185.5266242063312</v>
       </c>
       <c r="P18">
-        <v>432.2546148814396</v>
+        <v>432.8954564814395</v>
       </c>
       <c r="Q18">
-        <v>509.5546148814396</v>
+        <v>510.1954564814396</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0985107586486438</v>
+        <v>0.09849886227404145</v>
       </c>
       <c r="T18">
         <v>0.7668326576980494</v>
       </c>
       <c r="U18">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.4129848912372</v>
+        <v>10.56035759232298</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2946,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09067874988452285</v>
+        <v>0.09054978842026024</v>
       </c>
       <c r="C19">
-        <v>4722.826280432701</v>
+        <v>4730.863253841947</v>
       </c>
       <c r="D19">
-        <v>4840.7322804327</v>
+        <v>4848.769253841947</v>
       </c>
       <c r="E19">
         <v>-500.394</v>
@@ -2851,37 +2979,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M19">
-        <v>69.70166873863127</v>
+        <v>68.72896273863127</v>
       </c>
       <c r="N19">
-        <v>613.4064945266748</v>
+        <v>614.3792005266748</v>
       </c>
       <c r="O19">
-        <v>184.0219483580024</v>
+        <v>184.3137601580025</v>
       </c>
       <c r="P19">
-        <v>429.3845461686724</v>
+        <v>430.0654403686724</v>
       </c>
       <c r="Q19">
-        <v>506.6845461686725</v>
+        <v>507.3654403686725</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09897772142901803</v>
+        <v>0.09896571966484621</v>
       </c>
       <c r="T19">
         <v>0.7736260015826886</v>
       </c>
       <c r="U19">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.800456368223248</v>
+        <v>9.939160086892214</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3028,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.0908600238233022</v>
+        <v>0.09066109384944294</v>
       </c>
       <c r="C20">
-        <v>4653.444386913287</v>
+        <v>4666.14426257935</v>
       </c>
       <c r="D20">
-        <v>4828.568386913286</v>
+        <v>4841.26826257935</v>
       </c>
       <c r="E20">
         <v>-443.1760000000002</v>
@@ -2933,37 +3061,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M20">
-        <v>76.06759969972723</v>
+        <v>74.52271369972722</v>
       </c>
       <c r="N20">
-        <v>607.0405635655789</v>
+        <v>608.5854495655789</v>
       </c>
       <c r="O20">
-        <v>182.1121690696737</v>
+        <v>182.5756348696736</v>
       </c>
       <c r="P20">
-        <v>424.9283944959052</v>
+        <v>426.0098146959052</v>
       </c>
       <c r="Q20">
-        <v>502.2283944959053</v>
+        <v>503.3098146959053</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09945607354549896</v>
+        <v>0.09944396382128035</v>
       </c>
       <c r="T20">
         <v>0.7805850367815869</v>
       </c>
       <c r="U20">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.980277620982376</v>
+        <v>9.166442408655961</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3110,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09077949776208155</v>
+        <v>0.09057009927862565</v>
       </c>
       <c r="C21">
-        <v>4601.622313979352</v>
+        <v>4615.056750222102</v>
       </c>
       <c r="D21">
-        <v>4833.964313979352</v>
+        <v>4847.398750222102</v>
       </c>
       <c r="E21">
         <v>-385.9580000000001</v>
@@ -3015,37 +3143,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M21">
-        <v>80.29357746082319</v>
+        <v>78.66286446082319</v>
       </c>
       <c r="N21">
-        <v>602.8145858044829</v>
+        <v>604.4452988044829</v>
       </c>
       <c r="O21">
-        <v>180.8443757413449</v>
+        <v>181.3335896413449</v>
       </c>
       <c r="P21">
-        <v>421.9702100631381</v>
+        <v>423.1117091631381</v>
       </c>
       <c r="Q21">
-        <v>499.2702100631382</v>
+        <v>500.4117091631381</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09994623682534978</v>
+        <v>0.09993401647540423</v>
       </c>
       <c r="T21">
         <v>0.7877159000100877</v>
       </c>
       <c r="U21">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.507631430404356</v>
+        <v>8.683998071358278</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3192,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09069897170086091</v>
+        <v>0.09047910470780837</v>
       </c>
       <c r="C22">
-        <v>4549.812314438664</v>
+        <v>4563.984783597151</v>
       </c>
       <c r="D22">
-        <v>4839.372314438663</v>
+        <v>4853.544783597151</v>
       </c>
       <c r="E22">
         <v>-328.74</v>
@@ -3097,37 +3225,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M22">
-        <v>84.51955522191915</v>
+        <v>82.80301522191915</v>
       </c>
       <c r="N22">
-        <v>598.5886080433869</v>
+        <v>600.3051480433869</v>
       </c>
       <c r="O22">
-        <v>179.5765824130161</v>
+        <v>180.0915444130161</v>
       </c>
       <c r="P22">
-        <v>419.0120256303708</v>
+        <v>420.2136036303708</v>
       </c>
       <c r="Q22">
-        <v>496.3120256303709</v>
+        <v>497.5136036303709</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1004486541871969</v>
+        <v>0.1004363204458812</v>
       </c>
       <c r="T22">
         <v>0.7950250348193013</v>
       </c>
       <c r="U22">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.082249858884136</v>
+        <v>8.249798167790361</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3274,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09061844563964024</v>
+        <v>0.09038811013699107</v>
       </c>
       <c r="C23">
-        <v>4498.014428857956</v>
+        <v>4512.92842191103</v>
       </c>
       <c r="D23">
-        <v>4844.792428857955</v>
+        <v>4859.706421911029</v>
       </c>
       <c r="E23">
         <v>-271.5220000000002</v>
@@ -3179,37 +3307,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M23">
-        <v>88.7455329830151</v>
+        <v>86.94316598301511</v>
       </c>
       <c r="N23">
-        <v>594.362630282291</v>
+        <v>596.164997282291</v>
       </c>
       <c r="O23">
-        <v>178.3087890846873</v>
+        <v>178.8494991846873</v>
       </c>
       <c r="P23">
-        <v>416.0538411976037</v>
+        <v>417.3154980976037</v>
       </c>
       <c r="Q23">
-        <v>493.3538411976037</v>
+        <v>494.6154980976038</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1009637909759262</v>
+        <v>0.1009513409725728</v>
       </c>
       <c r="T23">
         <v>0.8025192110160897</v>
       </c>
       <c r="U23">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.697380817984893</v>
+        <v>7.856950635990821</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3356,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09076891957841959</v>
+        <v>0.09042031556617378</v>
       </c>
       <c r="C24">
-        <v>4430.678038040438</v>
+        <v>4453.527864312911</v>
       </c>
       <c r="D24">
-        <v>4834.674038040438</v>
+        <v>4857.523864312911</v>
       </c>
       <c r="E24">
         <v>-214.3040000000001</v>
@@ -3261,37 +3389,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M24">
-        <v>94.85970474411107</v>
+        <v>92.09035354411105</v>
       </c>
       <c r="N24">
-        <v>588.2484585211951</v>
+        <v>591.017809721195</v>
       </c>
       <c r="O24">
-        <v>176.4745375563585</v>
+        <v>177.3053429163585</v>
       </c>
       <c r="P24">
-        <v>411.7739209648365</v>
+        <v>413.7124668048365</v>
       </c>
       <c r="Q24">
-        <v>489.0739209648366</v>
+        <v>491.0124668048365</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1014921364002639</v>
+        <v>0.1014795671537949</v>
       </c>
       <c r="T24">
         <v>0.8102055455768984</v>
       </c>
       <c r="U24">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.201246990047308</v>
+        <v>7.417803678406978</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3438,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09069889351719895</v>
+        <v>0.09033492099535649</v>
       </c>
       <c r="C25">
-        <v>4378.163571007285</v>
+        <v>4402.101340554482</v>
       </c>
       <c r="D25">
-        <v>4839.377571007285</v>
+        <v>4863.315340554482</v>
       </c>
       <c r="E25">
         <v>-157.086</v>
@@ -3343,37 +3471,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M25">
-        <v>99.17150950520703</v>
+        <v>96.27627870520702</v>
       </c>
       <c r="N25">
-        <v>583.936653760099</v>
+        <v>586.8318845600991</v>
       </c>
       <c r="O25">
-        <v>175.1809961280297</v>
+        <v>176.0495653680297</v>
       </c>
       <c r="P25">
-        <v>408.7556576320693</v>
+        <v>410.7823191920694</v>
       </c>
       <c r="Q25">
-        <v>486.0556576320694</v>
+        <v>488.0823191920695</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1020342050823767</v>
+        <v>0.1020215134955683</v>
       </c>
       <c r="T25">
         <v>0.8180915251912345</v>
       </c>
       <c r="U25">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.888149294827858</v>
+        <v>7.095290474997979</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3520,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09062886745597828</v>
+        <v>0.09024952642453919</v>
       </c>
       <c r="C26">
-        <v>4325.65826478468</v>
+        <v>4350.688643278791</v>
       </c>
       <c r="D26">
-        <v>4844.09026478468</v>
+        <v>4869.12064327879</v>
       </c>
       <c r="E26">
         <v>-99.86800000000017</v>
@@ -3425,37 +3553,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M26">
-        <v>103.483314266303</v>
+        <v>100.462203866303</v>
       </c>
       <c r="N26">
-        <v>579.6248489990031</v>
+        <v>582.6459593990031</v>
       </c>
       <c r="O26">
-        <v>173.8874546997009</v>
+        <v>174.7937878197009</v>
       </c>
       <c r="P26">
-        <v>405.7373942993022</v>
+        <v>407.8521715793022</v>
       </c>
       <c r="Q26">
-        <v>483.0373942993023</v>
+        <v>485.1521715793023</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1025905387298082</v>
+        <v>0.1025777215831778</v>
       </c>
       <c r="T26">
         <v>0.8261850305848955</v>
       </c>
       <c r="U26">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.601143074210031</v>
+        <v>6.799653371873063</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3602,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09055884139475763</v>
+        <v>0.09016413185372191</v>
       </c>
       <c r="C27">
-        <v>4273.162146161711</v>
+        <v>4299.289822058716</v>
       </c>
       <c r="D27">
-        <v>4848.812146161711</v>
+        <v>4874.939822058715</v>
       </c>
       <c r="E27">
         <v>-42.65000000000009</v>
@@ -3507,37 +3635,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M27">
-        <v>107.7951190273989</v>
+        <v>104.6481290273989</v>
       </c>
       <c r="N27">
-        <v>575.3130442379071</v>
+        <v>578.4600342379072</v>
       </c>
       <c r="O27">
-        <v>172.5939132713721</v>
+        <v>173.5380102713721</v>
       </c>
       <c r="P27">
-        <v>402.719130966535</v>
+        <v>404.922023966535</v>
       </c>
       <c r="Q27">
-        <v>480.019130966535</v>
+        <v>482.2220239665351</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1031617079411712</v>
+        <v>0.1031487618864569</v>
       </c>
       <c r="T27">
         <v>0.8344943627890539</v>
       </c>
       <c r="U27">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.33709735124163</v>
+        <v>6.52766723699814</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3684,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09074361533353698</v>
+        <v>0.09007873728290461</v>
       </c>
       <c r="C28">
-        <v>4203.50462631616</v>
+        <v>4247.904926704401</v>
       </c>
       <c r="D28">
-        <v>4836.37262631616</v>
+        <v>4880.772926704401</v>
       </c>
       <c r="E28">
         <v>14.56799999999998</v>
@@ -3589,45 +3717,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M28">
-        <v>114.1896589884949</v>
+        <v>108.8340541884949</v>
       </c>
       <c r="N28">
-        <v>568.9185042768112</v>
+        <v>574.2741090768112</v>
       </c>
       <c r="O28">
-        <v>170.6755512830433</v>
+        <v>172.2822327230434</v>
       </c>
       <c r="P28">
-        <v>398.2429529937679</v>
+        <v>401.9918763537679</v>
       </c>
       <c r="Q28">
-        <v>475.5429529937679</v>
+        <v>479.2918763537679</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1037483141582467</v>
+        <v>0.1037352357114462</v>
       </c>
       <c r="T28">
         <v>0.8430282715392705</v>
       </c>
       <c r="U28">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.05373024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>5.982224391563619</v>
+        <v>6.276603112498212</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3766,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09068338927231634</v>
+        <v>0.0901823427120873</v>
       </c>
       <c r="C29">
-        <v>4150.334202836495</v>
+        <v>4183.611683888599</v>
       </c>
       <c r="D29">
-        <v>4840.420202836495</v>
+        <v>4873.697683888598</v>
       </c>
       <c r="E29">
         <v>71.78600000000006</v>
@@ -3671,37 +3799,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M29">
-        <v>118.5815689495909</v>
+        <v>114.5648653495909</v>
       </c>
       <c r="N29">
-        <v>564.5265943157152</v>
+        <v>568.5432979157152</v>
       </c>
       <c r="O29">
-        <v>169.3579782947146</v>
+        <v>170.5629893747146</v>
       </c>
       <c r="P29">
-        <v>395.1686160210006</v>
+        <v>397.9803085410007</v>
       </c>
       <c r="Q29">
-        <v>472.4686160210007</v>
+        <v>475.2803085410007</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1043509917785298</v>
+        <v>0.1043377773124626</v>
       </c>
       <c r="T29">
         <v>0.8517959860086715</v>
       </c>
       <c r="U29">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.760660525209411</v>
+        <v>5.962632271079134</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3848,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09062316321109568</v>
+        <v>0.09010394814127003</v>
       </c>
       <c r="C30">
-        <v>4097.170559892296</v>
+        <v>4131.745379847932</v>
       </c>
       <c r="D30">
-        <v>4844.474559892296</v>
+        <v>4879.049379847932</v>
       </c>
       <c r="E30">
         <v>129.0040000000001</v>
@@ -3753,37 +3881,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M30">
-        <v>122.9734789106868</v>
+        <v>118.8080085106868</v>
       </c>
       <c r="N30">
-        <v>560.1346843546193</v>
+        <v>564.3001547546193</v>
       </c>
       <c r="O30">
-        <v>168.0404053063858</v>
+        <v>169.2900464263858</v>
       </c>
       <c r="P30">
-        <v>392.0942790482335</v>
+        <v>395.0101083282335</v>
       </c>
       <c r="Q30">
-        <v>469.3942790482336</v>
+        <v>472.3101083282336</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1049704104438207</v>
+        <v>0.104957056180174</v>
       </c>
       <c r="T30">
         <v>0.8608072481022222</v>
       </c>
       <c r="U30">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.554922649309074</v>
+        <v>5.749681118540593</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3930,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09056293714987503</v>
+        <v>0.09002555357045272</v>
       </c>
       <c r="C31">
-        <v>4044.013714536064</v>
+        <v>4079.890841877188</v>
       </c>
       <c r="D31">
-        <v>4848.535714536063</v>
+        <v>4884.412841877187</v>
       </c>
       <c r="E31">
         <v>186.2219999999998</v>
@@ -3835,37 +3963,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M31">
-        <v>127.3653888717828</v>
+        <v>123.0511516717827</v>
       </c>
       <c r="N31">
-        <v>555.7427743935233</v>
+        <v>560.0570115935234</v>
       </c>
       <c r="O31">
-        <v>166.722832318057</v>
+        <v>168.017103478057</v>
       </c>
       <c r="P31">
-        <v>389.0199420754663</v>
+        <v>392.0399081154663</v>
       </c>
       <c r="Q31">
-        <v>466.3199420754664</v>
+        <v>469.3399081154664</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1056072775222185</v>
+        <v>0.1055937795230321</v>
       </c>
       <c r="T31">
         <v>0.8700723485646055</v>
       </c>
       <c r="U31">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.363373592436349</v>
+        <v>5.551416252384023</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +4012,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09050271108865438</v>
+        <v>0.08994715899963543</v>
       </c>
       <c r="C32">
-        <v>3990.863683877526</v>
+        <v>4028.048108821828</v>
       </c>
       <c r="D32">
-        <v>4852.603683877525</v>
+        <v>4889.788108821827</v>
       </c>
       <c r="E32">
         <v>243.4399999999998</v>
@@ -3917,37 +4045,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M32">
-        <v>131.7572988328787</v>
+        <v>127.2942948328787</v>
       </c>
       <c r="N32">
-        <v>551.3508644324273</v>
+        <v>555.8138684324274</v>
       </c>
       <c r="O32">
-        <v>165.4052593297282</v>
+        <v>166.7441605297282</v>
       </c>
       <c r="P32">
-        <v>385.9456051026991</v>
+        <v>389.0697079026992</v>
       </c>
       <c r="Q32">
-        <v>463.2456051026992</v>
+        <v>466.3697079026992</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1062623408028561</v>
+        <v>0.1062486949614005</v>
       </c>
       <c r="T32">
         <v>0.8796021661830568</v>
       </c>
       <c r="U32">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.18459447268847</v>
+        <v>5.366369043971221</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4094,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09044248502743371</v>
+        <v>0.08986876442881814</v>
       </c>
       <c r="C33">
-        <v>3937.720485083885</v>
+        <v>3976.217219698506</v>
       </c>
       <c r="D33">
-        <v>4856.678485083885</v>
+        <v>4895.175219698505</v>
       </c>
       <c r="E33">
         <v>300.6579999999999</v>
@@ -3999,37 +4127,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M33">
-        <v>136.1492087939747</v>
+        <v>131.5374379939747</v>
       </c>
       <c r="N33">
-        <v>546.9589544713314</v>
+        <v>551.5707252713314</v>
       </c>
       <c r="O33">
-        <v>164.0876863413994</v>
+        <v>165.4712175813994</v>
       </c>
       <c r="P33">
-        <v>382.871268129932</v>
+        <v>386.099507689932</v>
       </c>
       <c r="Q33">
-        <v>460.1712681299321</v>
+        <v>463.3995076899321</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1069363914249615</v>
+        <v>0.1069225934559535</v>
       </c>
       <c r="T33">
         <v>0.8894082103991443</v>
       </c>
       <c r="U33">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.017349489698519</v>
+        <v>5.193260365133439</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4176,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09038225896621307</v>
+        <v>0.08979036985800085</v>
       </c>
       <c r="C34">
-        <v>3884.584135380049</v>
+        <v>3924.398213696006</v>
       </c>
       <c r="D34">
-        <v>4860.760135380048</v>
+        <v>4900.574213696005</v>
       </c>
       <c r="E34">
         <v>357.876</v>
@@ -4081,37 +4209,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M34">
-        <v>140.5411187550706</v>
+        <v>135.7805811550706</v>
       </c>
       <c r="N34">
-        <v>542.5670445102354</v>
+        <v>547.3275821102354</v>
       </c>
       <c r="O34">
-        <v>162.7701133530706</v>
+        <v>164.1982746330706</v>
       </c>
       <c r="P34">
-        <v>379.7969311571647</v>
+        <v>383.1293074771648</v>
       </c>
       <c r="Q34">
-        <v>457.0969311571648</v>
+        <v>460.4293074771649</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1076302670653642</v>
+        <v>0.1076163124944639</v>
       </c>
       <c r="T34">
         <v>0.899502667680411</v>
       </c>
       <c r="U34">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.860557318145441</v>
+        <v>5.030970978723019</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4258,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09032203290499241</v>
+        <v>0.08971197528718355</v>
       </c>
       <c r="C35">
-        <v>3831.454652048883</v>
+        <v>3872.591130176187</v>
       </c>
       <c r="D35">
-        <v>4864.848652048882</v>
+        <v>4905.985130176186</v>
       </c>
       <c r="E35">
         <v>415.0940000000001</v>
@@ -4163,37 +4291,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M35">
-        <v>144.9330287161666</v>
+        <v>140.0237243161666</v>
       </c>
       <c r="N35">
-        <v>538.1751345491394</v>
+        <v>543.0844389491394</v>
       </c>
       <c r="O35">
-        <v>161.4525403647418</v>
+        <v>162.9253316847418</v>
       </c>
       <c r="P35">
-        <v>376.7225941843976</v>
+        <v>380.1591072643976</v>
       </c>
       <c r="Q35">
-        <v>454.0225941843977</v>
+        <v>457.4591072643977</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1083448554114505</v>
+        <v>0.1083307395639746</v>
       </c>
       <c r="T35">
         <v>0.9098984520447007</v>
       </c>
       <c r="U35">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.713267702444064</v>
+        <v>4.878517312701109</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4340,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09026180684377176</v>
+        <v>0.08963358071636625</v>
       </c>
       <c r="C36">
-        <v>3778.332052431444</v>
+        <v>3820.796008674949</v>
       </c>
       <c r="D36">
-        <v>4868.944052431444</v>
+        <v>4911.408008674948</v>
       </c>
       <c r="E36">
         <v>472.3119999999999</v>
@@ -4245,37 +4373,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M36">
-        <v>149.3249386772626</v>
+        <v>144.2668674772625</v>
       </c>
       <c r="N36">
-        <v>533.7832245880435</v>
+        <v>538.8412957880436</v>
       </c>
       <c r="O36">
-        <v>160.134967376413</v>
+        <v>161.6523887364131</v>
       </c>
       <c r="P36">
-        <v>373.6482572116304</v>
+        <v>377.1889070516305</v>
       </c>
       <c r="Q36">
-        <v>450.9482572116305</v>
+        <v>454.4889070516306</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1090810979498424</v>
+        <v>0.1090668159386219</v>
       </c>
       <c r="T36">
         <v>0.9206092601776048</v>
       </c>
       <c r="U36">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.574642181783943</v>
+        <v>4.735031509386372</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4422,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09083858078255112</v>
+        <v>0.08955518614554897</v>
       </c>
       <c r="C37">
-        <v>3682.174074819691</v>
+        <v>3769.012888903185</v>
       </c>
       <c r="D37">
-        <v>4830.004074819691</v>
+        <v>4916.842888903185</v>
       </c>
       <c r="E37">
         <v>529.53</v>
@@ -4327,45 +4455,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M37">
-        <v>158.9236866383585</v>
+        <v>148.5100106383585</v>
       </c>
       <c r="N37">
-        <v>524.1844766269476</v>
+        <v>534.5981526269476</v>
       </c>
       <c r="O37">
-        <v>157.2553429880843</v>
+        <v>160.3794457880843</v>
       </c>
       <c r="P37">
-        <v>366.9291336388633</v>
+        <v>374.2187068388633</v>
       </c>
       <c r="Q37">
-        <v>444.2291336388633</v>
+        <v>451.5187068388634</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1098399941048003</v>
+        <v>0.1098255408171047</v>
       </c>
       <c r="T37">
         <v>0.9316496316376754</v>
       </c>
       <c r="U37">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.05555024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.298340780501553</v>
+        <v>4.599744894832474</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4504,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09079655472133047</v>
+        <v>0.09010679157473167</v>
       </c>
       <c r="C38">
-        <v>3627.772346995679</v>
+        <v>3673.807064168357</v>
       </c>
       <c r="D38">
-        <v>4832.820346995678</v>
+        <v>4878.855064168356</v>
       </c>
       <c r="E38">
         <v>586.7479999999996</v>
@@ -4409,37 +4537,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M38">
-        <v>163.4643633994545</v>
+        <v>157.9027737994545</v>
       </c>
       <c r="N38">
-        <v>519.6437998658516</v>
+        <v>525.2053894658516</v>
       </c>
       <c r="O38">
-        <v>155.8931399597555</v>
+        <v>157.5616168397555</v>
       </c>
       <c r="P38">
-        <v>363.7506599060962</v>
+        <v>367.6437726260961</v>
       </c>
       <c r="Q38">
-        <v>441.0506599060963</v>
+        <v>444.9437726260962</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1106226057646006</v>
+        <v>0.1106079758480399</v>
       </c>
       <c r="T38">
         <v>0.9430350147058734</v>
       </c>
       <c r="U38">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.05555024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.178942425487621</v>
+        <v>4.326131497429503</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4586,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0907545286601098</v>
+        <v>0.09004589700391438</v>
       </c>
       <c r="C39">
-        <v>3573.373905304004</v>
+        <v>3620.753887937826</v>
       </c>
       <c r="D39">
-        <v>4835.639905304004</v>
+        <v>4883.019887937826</v>
       </c>
       <c r="E39">
         <v>643.9659999999999</v>
@@ -4491,37 +4619,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M39">
-        <v>168.0050401605504</v>
+        <v>162.2889619605504</v>
       </c>
       <c r="N39">
-        <v>515.1031231047557</v>
+        <v>520.8192013047557</v>
       </c>
       <c r="O39">
-        <v>154.5309369314267</v>
+        <v>156.2457603914267</v>
       </c>
       <c r="P39">
-        <v>360.572186173329</v>
+        <v>364.573440913329</v>
       </c>
       <c r="Q39">
-        <v>437.8721861733291</v>
+        <v>441.873440913329</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1114300622389977</v>
+        <v>0.1114152500863065</v>
       </c>
       <c r="T39">
         <v>0.9547818385063949</v>
       </c>
       <c r="U39">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.05555024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.065998035609576</v>
+        <v>4.209209024526003</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4668,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09143070259888916</v>
+        <v>0.08998500243309709</v>
       </c>
       <c r="C40">
-        <v>3471.186569211412</v>
+        <v>3567.707828367504</v>
       </c>
       <c r="D40">
-        <v>4790.670569211411</v>
+        <v>4887.191828367503</v>
       </c>
       <c r="E40">
         <v>701.1839999999997</v>
@@ -4573,45 +4701,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M40">
-        <v>178.4162837216464</v>
+        <v>166.6751501216464</v>
       </c>
       <c r="N40">
-        <v>504.6918795436597</v>
+        <v>516.4330131436598</v>
       </c>
       <c r="O40">
-        <v>151.4075638630979</v>
+        <v>154.9299039430979</v>
       </c>
       <c r="P40">
-        <v>353.2843156805618</v>
+        <v>361.5031092005619</v>
       </c>
       <c r="Q40">
-        <v>430.5843156805619</v>
+        <v>438.8031092005619</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1122635656964399</v>
+        <v>0.1122485654290333</v>
       </c>
       <c r="T40">
         <v>0.9669075921069333</v>
       </c>
       <c r="U40">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.05744024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.828732159509877</v>
+        <v>4.098440365985846</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4750,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09140757653766851</v>
+        <v>0.0908796078622798</v>
       </c>
       <c r="C41">
-        <v>3415.492763135792</v>
+        <v>3449.907670307575</v>
       </c>
       <c r="D41">
-        <v>4792.194763135792</v>
+        <v>4826.609670307575</v>
       </c>
       <c r="E41">
         <v>758.402</v>
@@ -4655,37 +4783,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M41">
-        <v>183.1114490827424</v>
+        <v>178.8715952827424</v>
       </c>
       <c r="N41">
-        <v>499.9967141825637</v>
+        <v>504.2365679825637</v>
       </c>
       <c r="O41">
-        <v>149.9990142547691</v>
+        <v>151.2709703947691</v>
       </c>
       <c r="P41">
-        <v>349.9976999277946</v>
+        <v>352.9655975877946</v>
       </c>
       <c r="Q41">
-        <v>427.2976999277947</v>
+        <v>430.2655975877947</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1131243971360933</v>
+        <v>0.1131092025862757</v>
       </c>
       <c r="T41">
         <v>0.9794309113992927</v>
       </c>
       <c r="U41">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.05744024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.730559540035264</v>
+        <v>3.81898625204028</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4832,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09138445047644786</v>
+        <v>0.09084321329146251</v>
       </c>
       <c r="C42">
-        <v>3359.799927240215</v>
+        <v>3395.124965862043</v>
       </c>
       <c r="D42">
-        <v>4793.719927240215</v>
+        <v>4829.044965862043</v>
       </c>
       <c r="E42">
         <v>815.6199999999999</v>
@@ -4737,37 +4865,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M42">
-        <v>187.8066144438383</v>
+        <v>183.4580464438383</v>
       </c>
       <c r="N42">
-        <v>495.3015488214678</v>
+        <v>499.6501168214678</v>
       </c>
       <c r="O42">
-        <v>148.5904646464403</v>
+        <v>149.8950350464403</v>
       </c>
       <c r="P42">
-        <v>346.7110841750275</v>
+        <v>349.7550817750275</v>
       </c>
       <c r="Q42">
-        <v>424.0110841750276</v>
+        <v>427.0550817750275</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1140139229570684</v>
+        <v>0.1139985276487595</v>
       </c>
       <c r="T42">
         <v>0.9923716746680641</v>
       </c>
       <c r="U42">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.05744024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.637295551534383</v>
+        <v>3.723511595739274</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4914,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09136132441522721</v>
+        <v>0.09080681872064522</v>
       </c>
       <c r="C43">
-        <v>3304.108062451286</v>
+        <v>3340.344720143738</v>
       </c>
       <c r="D43">
-        <v>4795.246062451286</v>
+        <v>4831.482720143737</v>
       </c>
       <c r="E43">
         <v>872.8380000000002</v>
@@ -4819,37 +4947,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M43">
-        <v>192.5017798049343</v>
+        <v>188.0444976049343</v>
       </c>
       <c r="N43">
-        <v>490.6063834603718</v>
+        <v>495.0636656603718</v>
       </c>
       <c r="O43">
-        <v>147.1819150381115</v>
+        <v>148.5190996981115</v>
       </c>
       <c r="P43">
-        <v>343.4244684222602</v>
+        <v>346.5445659622603</v>
       </c>
       <c r="Q43">
-        <v>420.7244684222603</v>
+        <v>423.8445659622603</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1149336021957038</v>
+        <v>0.1149179993235309</v>
       </c>
       <c r="T43">
         <v>1.00575110787815</v>
       </c>
       <c r="U43">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.05744024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.548581025887202</v>
+        <v>3.632694239745632</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4996,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09271999835400654</v>
+        <v>0.09077042414982793</v>
       </c>
       <c r="C44">
-        <v>3158.846658264632</v>
+        <v>3285.566936878115</v>
       </c>
       <c r="D44">
-        <v>4707.202658264631</v>
+        <v>4833.922936878114</v>
       </c>
       <c r="E44">
         <v>930.0559999999996</v>
@@ -4901,45 +5029,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M44">
-        <v>208.4917783660302</v>
+        <v>192.6309487660302</v>
       </c>
       <c r="N44">
-        <v>474.6163848992759</v>
+        <v>490.4772144992759</v>
       </c>
       <c r="O44">
-        <v>142.3849154697828</v>
+        <v>147.1431643497828</v>
       </c>
       <c r="P44">
-        <v>332.2314694294931</v>
+        <v>343.3340501494931</v>
       </c>
       <c r="Q44">
-        <v>409.5314694294932</v>
+        <v>420.6340501494932</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1158849945115335</v>
+        <v>0.115869176918122</v>
       </c>
       <c r="T44">
         <v>1.0195919008541</v>
       </c>
       <c r="U44">
-        <v>0.08675748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.06073024175551697</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.276427342214113</v>
+        <v>3.546201519751689</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5078,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09272977229278591</v>
+        <v>0.09157682957901064</v>
       </c>
       <c r="C45">
-        <v>3101.00700841046</v>
+        <v>3174.851696062644</v>
       </c>
       <c r="D45">
-        <v>4706.58100841046</v>
+        <v>4780.425696062644</v>
       </c>
       <c r="E45">
         <v>987.2739999999999</v>
@@ -4983,37 +5111,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M45">
-        <v>213.4558683271262</v>
+        <v>204.1064471271262</v>
       </c>
       <c r="N45">
-        <v>469.6522949381799</v>
+        <v>479.0017161381799</v>
       </c>
       <c r="O45">
-        <v>140.895688481454</v>
+        <v>143.700514841454</v>
       </c>
       <c r="P45">
-        <v>328.756606456726</v>
+        <v>335.3012012967259</v>
       </c>
       <c r="Q45">
-        <v>406.0566064567261</v>
+        <v>412.601201296726</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1168697690138835</v>
+        <v>0.116853729165155</v>
       </c>
       <c r="T45">
         <v>1.033918335688856</v>
       </c>
       <c r="U45">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.200231357511459</v>
+        <v>3.346823056695692</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5160,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09273954623156525</v>
+        <v>0.09156003500819335</v>
       </c>
       <c r="C46">
-        <v>3043.167522729173</v>
+        <v>3118.735777813024</v>
       </c>
       <c r="D46">
-        <v>4705.959522729172</v>
+        <v>4781.527777813023</v>
       </c>
       <c r="E46">
         <v>1044.492</v>
@@ -5065,37 +5193,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M46">
-        <v>218.4199582882221</v>
+        <v>208.8531086882221</v>
       </c>
       <c r="N46">
-        <v>464.688204977084</v>
+        <v>474.255054577084</v>
       </c>
       <c r="O46">
-        <v>139.4064614931252</v>
+        <v>142.2765163731252</v>
       </c>
       <c r="P46">
-        <v>325.2817434839587</v>
+        <v>331.9785382039588</v>
       </c>
       <c r="Q46">
-        <v>402.5817434839588</v>
+        <v>409.2785382039589</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1178897140341746</v>
+        <v>0.117873443992439</v>
       </c>
       <c r="T46">
         <v>1.048756428910568</v>
       </c>
       <c r="U46">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.127498826658925</v>
+        <v>3.270758896316245</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5242,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.0927493201703446</v>
+        <v>0.09154324043737605</v>
       </c>
       <c r="C47">
-        <v>2985.328201155739</v>
+        <v>3062.620367829544</v>
       </c>
       <c r="D47">
-        <v>4705.338201155739</v>
+        <v>4782.630367829544</v>
       </c>
       <c r="E47">
         <v>1101.71</v>
@@ -5147,37 +5275,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M47">
-        <v>223.3840482493181</v>
+        <v>213.5997702493181</v>
       </c>
       <c r="N47">
-        <v>459.724115015988</v>
+        <v>469.508393015988</v>
       </c>
       <c r="O47">
-        <v>137.9172345047964</v>
+        <v>140.8525179047964</v>
       </c>
       <c r="P47">
-        <v>321.8068805111916</v>
+        <v>328.6558751111916</v>
       </c>
       <c r="Q47">
-        <v>399.1068805111917</v>
+        <v>405.9558751111916</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1189467479642945</v>
+        <v>0.1189302393588971</v>
       </c>
       <c r="T47">
         <v>1.064134089158523</v>
       </c>
       <c r="U47">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.057998852733171</v>
+        <v>3.198075365286994</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5324,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09575369410912395</v>
+        <v>0.09152644586655875</v>
       </c>
       <c r="C48">
-        <v>2744.597382815608</v>
+        <v>3006.505466463896</v>
       </c>
       <c r="D48">
-        <v>4521.825382815608</v>
+        <v>4783.733466463896</v>
       </c>
       <c r="E48">
         <v>1158.928</v>
@@ -5229,45 +5357,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M48">
-        <v>252.825998610414</v>
+        <v>218.3464318104141</v>
       </c>
       <c r="N48">
-        <v>430.282164654892</v>
+        <v>464.761731454892</v>
       </c>
       <c r="O48">
-        <v>129.0846493964676</v>
+        <v>139.4285194364676</v>
       </c>
       <c r="P48">
-        <v>301.1975152584245</v>
+        <v>325.3332120184244</v>
       </c>
       <c r="Q48">
-        <v>378.4975152584245</v>
+        <v>402.6332120184245</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1200429312992336</v>
+        <v>0.1200261752944832</v>
       </c>
       <c r="T48">
         <v>1.080081292378625</v>
       </c>
       <c r="U48">
-        <v>0.09605748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.06724024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.7018904978911</v>
+        <v>3.128551987780755</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5406,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0958285680479033</v>
+        <v>0.09150965129574147</v>
       </c>
       <c r="C49">
-        <v>2682.988578054089</v>
+        <v>2950.391074068092</v>
       </c>
       <c r="D49">
-        <v>4517.434578054088</v>
+        <v>4784.837074068091</v>
       </c>
       <c r="E49">
         <v>1216.146</v>
@@ -5311,45 +5439,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M49">
-        <v>258.32221597151</v>
+        <v>223.09309337151</v>
       </c>
       <c r="N49">
-        <v>424.7859472937961</v>
+        <v>460.0150698937961</v>
       </c>
       <c r="O49">
-        <v>127.4357841881388</v>
+        <v>138.0045209681388</v>
       </c>
       <c r="P49">
-        <v>297.3501631056573</v>
+        <v>322.0105489256572</v>
       </c>
       <c r="Q49">
-        <v>374.6501631056573</v>
+        <v>399.3105489256573</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1211804800430383</v>
+        <v>0.1211634673031103</v>
       </c>
       <c r="T49">
         <v>1.096630276852316</v>
       </c>
       <c r="U49">
-        <v>0.09605748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.06724024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.644403466021076</v>
+        <v>3.061987051870527</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5488,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09590344198668263</v>
+        <v>0.09411365672492417</v>
       </c>
       <c r="C50">
-        <v>2621.388292181486</v>
+        <v>2727.929548784972</v>
       </c>
       <c r="D50">
-        <v>4513.052292181485</v>
+        <v>4619.593548784971</v>
       </c>
       <c r="E50">
         <v>1273.364</v>
@@ -5393,37 +5521,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M50">
-        <v>263.8184333326059</v>
+        <v>249.2621741326059</v>
       </c>
       <c r="N50">
-        <v>419.2897299327001</v>
+        <v>433.8459891327001</v>
       </c>
       <c r="O50">
-        <v>125.78691897981</v>
+        <v>130.15379673981</v>
       </c>
       <c r="P50">
-        <v>293.5028109528901</v>
+        <v>303.6921923928901</v>
       </c>
       <c r="Q50">
-        <v>370.8028109528902</v>
+        <v>380.9921923928902</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1223617806616048</v>
+        <v>0.1223445013120693</v>
       </c>
       <c r="T50">
         <v>1.113815760728841</v>
       </c>
       <c r="U50">
-        <v>0.09605748822216711</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.06724024175551697</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.589311727145637</v>
+        <v>2.740520761493064</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5570,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09597831592546197</v>
+        <v>0.09415146215410686</v>
       </c>
       <c r="C51">
-        <v>2559.796500429741</v>
+        <v>2668.396523933948</v>
       </c>
       <c r="D51">
-        <v>4508.678500429741</v>
+        <v>4617.278523933947</v>
       </c>
       <c r="E51">
         <v>1330.582</v>
@@ -5475,37 +5603,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M51">
-        <v>269.3146506937019</v>
+        <v>254.4551360937019</v>
       </c>
       <c r="N51">
-        <v>413.7935125716041</v>
+        <v>428.6530271716042</v>
       </c>
       <c r="O51">
-        <v>124.1380537714812</v>
+        <v>128.5959081514812</v>
       </c>
       <c r="P51">
-        <v>289.6554588001229</v>
+        <v>300.0571190201229</v>
       </c>
       <c r="Q51">
-        <v>366.955458800123</v>
+        <v>377.357119020123</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1235894067946248</v>
+        <v>0.123571850380203</v>
       </c>
       <c r="T51">
         <v>1.131675185149543</v>
       </c>
       <c r="U51">
-        <v>0.09605748822216711</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.06724024175551697</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.536468630673277</v>
+        <v>2.684591766360553</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5652,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09769818986424134</v>
+        <v>0.09418926758328958</v>
       </c>
       <c r="C52">
-        <v>2404.394448473454</v>
+        <v>2608.865818185507</v>
       </c>
       <c r="D52">
-        <v>4410.494448473453</v>
+        <v>4614.965818185507</v>
       </c>
       <c r="E52">
         <v>1387.8</v>
@@ -5557,45 +5685,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M52">
-        <v>288.2570980547979</v>
+        <v>259.6480980547979</v>
       </c>
       <c r="N52">
-        <v>394.8510652105082</v>
+        <v>423.4600652105082</v>
       </c>
       <c r="O52">
-        <v>118.4553195631524</v>
+        <v>127.0380195631525</v>
       </c>
       <c r="P52">
-        <v>276.3957456473557</v>
+        <v>296.4220456473557</v>
       </c>
       <c r="Q52">
-        <v>353.6957456473558</v>
+        <v>373.7220456473558</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1248661379729657</v>
+        <v>0.1248482934110622</v>
       </c>
       <c r="T52">
         <v>1.150248986547074</v>
       </c>
       <c r="U52">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.07053024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.369787831331899</v>
+        <v>2.630899931033342</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5734,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09780596380302067</v>
+        <v>0.09422707301247228</v>
       </c>
       <c r="C53">
-        <v>2341.166041730562</v>
+        <v>2549.337428056616</v>
       </c>
       <c r="D53">
-        <v>4404.484041730561</v>
+        <v>4612.655428056615</v>
       </c>
       <c r="E53">
         <v>1445.018</v>
@@ -5639,45 +5767,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M53">
-        <v>294.0222400158938</v>
+        <v>264.8410600158938</v>
       </c>
       <c r="N53">
-        <v>389.0859232494122</v>
+        <v>418.2671032494123</v>
       </c>
       <c r="O53">
-        <v>116.7257769748237</v>
+        <v>125.4801309748237</v>
       </c>
       <c r="P53">
-        <v>272.3601462745886</v>
+        <v>292.7869722745886</v>
       </c>
       <c r="Q53">
-        <v>349.6601462745887</v>
+        <v>370.0869722745887</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1261949806279735</v>
+        <v>0.1261768361574666</v>
       </c>
       <c r="T53">
         <v>1.169580902287361</v>
       </c>
       <c r="U53">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.07053024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.323321403266568</v>
+        <v>2.579313657875826</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5816,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09791373774180001</v>
+        <v>0.09426487844165499</v>
       </c>
       <c r="C54">
-        <v>2277.953994072692</v>
+        <v>2489.811350071207</v>
       </c>
       <c r="D54">
-        <v>4398.489994072692</v>
+        <v>4610.347350071207</v>
       </c>
       <c r="E54">
         <v>1502.236</v>
@@ -5721,45 +5849,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M54">
-        <v>299.7873819769898</v>
+        <v>270.0340219769898</v>
       </c>
       <c r="N54">
-        <v>383.3207812883163</v>
+        <v>413.0741412883163</v>
       </c>
       <c r="O54">
-        <v>114.9962343864949</v>
+        <v>123.9222423864949</v>
       </c>
       <c r="P54">
-        <v>268.3245469018213</v>
+        <v>289.1518989018214</v>
       </c>
       <c r="Q54">
-        <v>345.6245469018214</v>
+        <v>366.4518989018215</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.12757919172694</v>
+        <v>0.1275607348516378</v>
       </c>
       <c r="T54">
         <v>1.189718314516827</v>
       </c>
       <c r="U54">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.07053024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.278642145511442</v>
+        <v>2.529711472147444</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5898,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09802151168057938</v>
+        <v>0.09574958387083771</v>
       </c>
       <c r="C55">
-        <v>2214.75823880154</v>
+        <v>2343.741255803884</v>
       </c>
       <c r="D55">
-        <v>4392.51223880154</v>
+        <v>4521.495255803883</v>
       </c>
       <c r="E55">
         <v>1559.454</v>
@@ -5803,37 +5931,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M55">
-        <v>305.5525239380858</v>
+        <v>287.0539445380857</v>
       </c>
       <c r="N55">
-        <v>377.5556393272203</v>
+        <v>396.0542187272204</v>
       </c>
       <c r="O55">
-        <v>113.2666917981661</v>
+        <v>118.8162656181661</v>
       </c>
       <c r="P55">
-        <v>264.2889475290542</v>
+        <v>277.2379531090543</v>
       </c>
       <c r="Q55">
-        <v>341.5889475290543</v>
+        <v>354.5379531090543</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1290223054258625</v>
+        <v>0.1290035228519441</v>
       </c>
       <c r="T55">
         <v>1.210712637904993</v>
       </c>
       <c r="U55">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.235648897482924</v>
+        <v>2.3797205238358</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5980,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09812928561935871</v>
+        <v>0.09581468930002041</v>
       </c>
       <c r="C56">
-        <v>2151.578709580898</v>
+        <v>2282.705341807682</v>
       </c>
       <c r="D56">
-        <v>4386.550709580898</v>
+        <v>4517.677341807682</v>
       </c>
       <c r="E56">
         <v>1616.672</v>
@@ -5885,37 +6013,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M56">
-        <v>311.3176658991817</v>
+        <v>292.4700566991817</v>
       </c>
       <c r="N56">
-        <v>371.7904973661243</v>
+        <v>390.6381065661243</v>
       </c>
       <c r="O56">
-        <v>111.5371492098373</v>
+        <v>117.1914319698373</v>
       </c>
       <c r="P56">
-        <v>260.253348156287</v>
+        <v>273.446674596287</v>
       </c>
       <c r="Q56">
-        <v>337.5533481562871</v>
+        <v>350.7466745962871</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1305281631986512</v>
+        <v>0.130509040765307</v>
       </c>
       <c r="T56">
         <v>1.23261975796221</v>
       </c>
       <c r="U56">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.19424799197398</v>
+        <v>2.335651625246248</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6062,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09823705955813808</v>
+        <v>0.0958797947292031</v>
       </c>
       <c r="C57">
-        <v>2088.415340434191</v>
+        <v>2221.675870003098</v>
       </c>
       <c r="D57">
-        <v>4380.605340434191</v>
+        <v>4513.865870003097</v>
       </c>
       <c r="E57">
         <v>1673.89</v>
@@ -5967,37 +6095,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M57">
-        <v>317.0828078602777</v>
+        <v>297.8861688602777</v>
       </c>
       <c r="N57">
-        <v>366.0253554050284</v>
+        <v>385.2219944050284</v>
       </c>
       <c r="O57">
-        <v>109.8076066215085</v>
+        <v>115.5665983215085</v>
       </c>
       <c r="P57">
-        <v>256.2177487835199</v>
+        <v>269.6553960835199</v>
       </c>
       <c r="Q57">
-        <v>333.5177487835199</v>
+        <v>346.95539608352</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1321009479835639</v>
+        <v>0.1320814705859306</v>
       </c>
       <c r="T57">
         <v>1.255500527799748</v>
       </c>
       <c r="U57">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.15435257393809</v>
+        <v>2.293185232059953</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6144,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09834483349691742</v>
+        <v>0.09594490015838583</v>
       </c>
       <c r="C58">
-        <v>2025.268065742054</v>
+        <v>2160.652824098439</v>
       </c>
       <c r="D58">
-        <v>4374.676065742054</v>
+        <v>4510.060824098439</v>
       </c>
       <c r="E58">
         <v>1731.108</v>
@@ -6049,37 +6177,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M58">
-        <v>322.8479498213737</v>
+        <v>303.3022810213736</v>
       </c>
       <c r="N58">
-        <v>360.2602134439324</v>
+        <v>379.8058822439324</v>
       </c>
       <c r="O58">
-        <v>108.0780640331797</v>
+        <v>113.9417646731797</v>
       </c>
       <c r="P58">
-        <v>252.1821494107527</v>
+        <v>265.8641175707527</v>
       </c>
       <c r="Q58">
-        <v>329.4821494107528</v>
+        <v>343.1641175707528</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1337452229859726</v>
+        <v>0.1337253744893098</v>
       </c>
       <c r="T58">
         <v>1.279421332629901</v>
       </c>
       <c r="U58">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V58">
         <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.115881992260624</v>
+        <v>2.252235495773168</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6226,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09845260743569677</v>
+        <v>0.09601000558756852</v>
       </c>
       <c r="C59">
-        <v>1962.136820239908</v>
+        <v>2099.636187856906</v>
       </c>
       <c r="D59">
-        <v>4368.762820239907</v>
+        <v>4506.262187856905</v>
       </c>
       <c r="E59">
         <v>1788.326</v>
@@ -6131,37 +6259,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M59">
-        <v>328.6130917824696</v>
+        <v>308.7183931824696</v>
       </c>
       <c r="N59">
-        <v>354.4950714828365</v>
+        <v>374.3897700828365</v>
       </c>
       <c r="O59">
-        <v>106.3485214448509</v>
+        <v>112.3169310248509</v>
       </c>
       <c r="P59">
-        <v>248.1465500379855</v>
+        <v>262.0728390579856</v>
       </c>
       <c r="Q59">
-        <v>325.4465500379856</v>
+        <v>339.3728390579856</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.13546597589547</v>
+        <v>0.1354457390393578</v>
       </c>
       <c r="T59">
         <v>1.304454733033549</v>
       </c>
       <c r="U59">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.078761255554297</v>
+        <v>2.212722592338551</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6308,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09856038137447612</v>
+        <v>0.09607511101675123</v>
       </c>
       <c r="C60">
-        <v>1899.021539015571</v>
+        <v>2038.625945096347</v>
       </c>
       <c r="D60">
-        <v>4362.86553901557</v>
+        <v>4502.469945096346</v>
       </c>
       <c r="E60">
         <v>1845.543999999999</v>
@@ -6213,37 +6341,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M60">
-        <v>334.3782337435655</v>
+        <v>314.1345053435655</v>
       </c>
       <c r="N60">
-        <v>348.7299295217405</v>
+        <v>368.9736579217406</v>
       </c>
       <c r="O60">
-        <v>104.6189788565222</v>
+        <v>110.6920973765222</v>
       </c>
       <c r="P60">
-        <v>244.1109506652184</v>
+        <v>258.2815605452184</v>
       </c>
       <c r="Q60">
-        <v>321.4109506652184</v>
+        <v>335.5815605452185</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1372686694197054</v>
+        <v>0.1372480257108366</v>
       </c>
       <c r="T60">
         <v>1.330680200123086</v>
       </c>
       <c r="U60">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V60">
         <v>0.3</v>
       </c>
       <c r="W60">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.042920544251637</v>
+        <v>2.174572202815473</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6390,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.09866815531325546</v>
+        <v>0.09614021644593393</v>
       </c>
       <c r="C61">
-        <v>1835.922157506886</v>
+        <v>1977.622079689047</v>
       </c>
       <c r="D61">
-        <v>4356.984157506885</v>
+        <v>4498.684079689046</v>
       </c>
       <c r="E61">
         <v>1902.761999999999</v>
@@ -6295,37 +6423,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M61">
-        <v>340.1433757046615</v>
+        <v>319.5506175046614</v>
       </c>
       <c r="N61">
-        <v>342.9647875606446</v>
+        <v>363.5575457606446</v>
       </c>
       <c r="O61">
-        <v>102.8894362681934</v>
+        <v>109.0672637281934</v>
       </c>
       <c r="P61">
-        <v>240.0753512924512</v>
+        <v>254.4902820324513</v>
       </c>
       <c r="Q61">
-        <v>317.3753512924513</v>
+        <v>331.7902820324513</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1391592992134157</v>
+        <v>0.1391382288053144</v>
       </c>
       <c r="T61">
         <v>1.35818495829016</v>
       </c>
       <c r="U61">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.008294772315169</v>
+        <v>2.13771504683555</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6472,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1056219292520348</v>
+        <v>0.09620532187511666</v>
       </c>
       <c r="C62">
-        <v>1430.062587111989</v>
+        <v>1916.624575561477</v>
       </c>
       <c r="D62">
-        <v>4008.342587111988</v>
+        <v>4494.904575561476</v>
       </c>
       <c r="E62">
         <v>1959.98</v>
@@ -6377,45 +6505,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M62">
-        <v>401.8677216657575</v>
+        <v>324.9667296657574</v>
       </c>
       <c r="N62">
-        <v>281.2404415995486</v>
+        <v>358.1414335995486</v>
       </c>
       <c r="O62">
-        <v>84.37213247986458</v>
+        <v>107.4424300798646</v>
       </c>
       <c r="P62">
-        <v>196.868309119684</v>
+        <v>250.699003519684</v>
       </c>
       <c r="Q62">
-        <v>274.1683091196841</v>
+        <v>327.9990035196841</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1411444604968116</v>
+        <v>0.1411229420545161</v>
       </c>
       <c r="T62">
         <v>1.387064954365589</v>
       </c>
       <c r="U62">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.699833369133993</v>
+        <v>2.102086462721624</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6554,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1058438031908142</v>
+        <v>0.09627042730429936</v>
       </c>
       <c r="C63">
-        <v>1362.63668882644</v>
+        <v>1855.633416694093</v>
       </c>
       <c r="D63">
-        <v>3998.134688826439</v>
+        <v>4491.131416694092</v>
       </c>
       <c r="E63">
         <v>2017.197999999999</v>
@@ -6459,45 +6587,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M63">
-        <v>408.5655170268534</v>
+        <v>330.3828418268534</v>
       </c>
       <c r="N63">
-        <v>274.5426462384527</v>
+        <v>352.7253214384527</v>
       </c>
       <c r="O63">
-        <v>82.3627938715358</v>
+        <v>105.8175964315358</v>
       </c>
       <c r="P63">
-        <v>192.1798523669169</v>
+        <v>246.9077250069169</v>
       </c>
       <c r="Q63">
-        <v>269.4798523669169</v>
+        <v>324.2077250069169</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1432314249229456</v>
+        <v>0.1432094354703436</v>
       </c>
       <c r="T63">
         <v>1.417425975880783</v>
       </c>
       <c r="U63">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V63">
         <v>0.3</v>
       </c>
       <c r="W63">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.671967248328517</v>
+        <v>2.067626028906515</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6636,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1060656771295935</v>
+        <v>0.09633553273348205</v>
       </c>
       <c r="C64">
-        <v>1295.26265062715</v>
+        <v>1794.648587121083</v>
       </c>
       <c r="D64">
-        <v>3987.978650627149</v>
+        <v>4487.364587121082</v>
       </c>
       <c r="E64">
         <v>2074.416</v>
@@ -6541,45 +6669,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M64">
-        <v>415.2633123879494</v>
+        <v>335.7989539879493</v>
       </c>
       <c r="N64">
-        <v>267.8448508773566</v>
+        <v>347.3092092773567</v>
       </c>
       <c r="O64">
-        <v>80.35345526320698</v>
+        <v>104.192762783207</v>
       </c>
       <c r="P64">
-        <v>187.4913956141497</v>
+        <v>243.1164464941497</v>
       </c>
       <c r="Q64">
-        <v>264.7913956141497</v>
+        <v>320.4164464941498</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1454282295820342</v>
+        <v>0.1454057443291093</v>
       </c>
       <c r="T64">
         <v>1.449384945896778</v>
       </c>
       <c r="U64">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.645000034645799</v>
+        <v>2.034277221988668</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6718,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1062875510683729</v>
+        <v>0.09640063816266477</v>
       </c>
       <c r="C65">
-        <v>1227.940078311416</v>
+        <v>1733.670070930157</v>
       </c>
       <c r="D65">
-        <v>3977.874078311415</v>
+        <v>4483.604070930156</v>
       </c>
       <c r="E65">
         <v>2131.634</v>
@@ -6623,45 +6751,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M65">
-        <v>421.9611077490454</v>
+        <v>341.2150661490453</v>
       </c>
       <c r="N65">
-        <v>261.1470555162607</v>
+        <v>341.8930971162608</v>
       </c>
       <c r="O65">
-        <v>78.34411665487821</v>
+        <v>102.5679291348782</v>
       </c>
       <c r="P65">
-        <v>182.8029388613825</v>
+        <v>239.3251679813825</v>
       </c>
       <c r="Q65">
-        <v>260.1029388613825</v>
+        <v>316.6251679813826</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1477437804389113</v>
+        <v>0.1477207725856461</v>
       </c>
       <c r="T65">
         <v>1.483071427805528</v>
       </c>
       <c r="U65">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.618888922984755</v>
+        <v>2.001987107353927</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6800,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1065094250071522</v>
+        <v>0.1028273435918475</v>
       </c>
       <c r="C66">
-        <v>1160.66858166169</v>
+        <v>1333.891708688969</v>
       </c>
       <c r="D66">
-        <v>3967.82058166169</v>
+        <v>4141.043708688969</v>
       </c>
       <c r="E66">
         <v>2188.852</v>
@@ -6705,37 +6833,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M66">
-        <v>428.6589031101414</v>
+        <v>398.6308967101413</v>
       </c>
       <c r="N66">
-        <v>254.4492601551647</v>
+        <v>284.4772665551648</v>
       </c>
       <c r="O66">
-        <v>76.33477804654942</v>
+        <v>85.34317996654943</v>
       </c>
       <c r="P66">
-        <v>178.1144821086153</v>
+        <v>199.1340865886153</v>
       </c>
       <c r="Q66">
-        <v>255.4144821086154</v>
+        <v>276.4340865886154</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1501879730100593</v>
+        <v>0.1501644135231017</v>
       </c>
       <c r="T66">
         <v>1.518629380931431</v>
       </c>
       <c r="U66">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.593593783563118</v>
+        <v>1.713635769085953</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6882,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1067312989459316</v>
+        <v>0.1029918490210302</v>
       </c>
       <c r="C67">
-        <v>1093.447774395353</v>
+        <v>1268.590887134016</v>
       </c>
       <c r="D67">
-        <v>3957.817774395352</v>
+        <v>4132.960887134015</v>
       </c>
       <c r="E67">
         <v>2246.07</v>
@@ -6787,37 +6915,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M67">
-        <v>435.3566984712373</v>
+        <v>404.8595044712372</v>
       </c>
       <c r="N67">
-        <v>247.7514647940688</v>
+        <v>278.2486587940688</v>
       </c>
       <c r="O67">
-        <v>74.32543943822064</v>
+        <v>83.47459763822064</v>
       </c>
       <c r="P67">
-        <v>173.4260253558481</v>
+        <v>194.7740611558482</v>
       </c>
       <c r="Q67">
-        <v>250.7260253558482</v>
+        <v>272.0740611558483</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1527718337281301</v>
+        <v>0.1527476910855547</v>
       </c>
       <c r="T67">
         <v>1.5562192170931</v>
       </c>
       <c r="U67">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V67">
         <v>0.3</v>
       </c>
       <c r="W67">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.569076956123685</v>
+        <v>1.687272141869246</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6964,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1069531728847109</v>
+        <v>0.1031563544502129</v>
       </c>
       <c r="C68">
-        <v>1026.277274115235</v>
+        <v>1203.321557510584</v>
       </c>
       <c r="D68">
-        <v>3947.865274115235</v>
+        <v>4124.909557510584</v>
       </c>
       <c r="E68">
         <v>2303.288</v>
@@ -6869,37 +6997,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M68">
-        <v>442.0544938323333</v>
+        <v>411.0881122323332</v>
       </c>
       <c r="N68">
-        <v>241.0536694329728</v>
+        <v>272.0200510329728</v>
       </c>
       <c r="O68">
-        <v>72.31610082989184</v>
+        <v>81.60601530989184</v>
       </c>
       <c r="P68">
-        <v>168.737568603081</v>
+        <v>190.414035723081</v>
       </c>
       <c r="Q68">
-        <v>246.037568603081</v>
+        <v>267.7140357230811</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1555076862531462</v>
+        <v>0.1554829261516814</v>
       </c>
       <c r="T68">
         <v>1.596020220087809</v>
       </c>
       <c r="U68">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V68">
         <v>0.3</v>
       </c>
       <c r="W68">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.545303062849084</v>
+        <v>1.661707412446985</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7046,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1071750468234903</v>
+        <v>0.1033208598793956</v>
       </c>
       <c r="C69">
-        <v>959.1567022608924</v>
+        <v>1138.083536130315</v>
       </c>
       <c r="D69">
-        <v>3937.962702260892</v>
+        <v>4116.889536130315</v>
       </c>
       <c r="E69">
         <v>2360.506</v>
@@ -6951,37 +7079,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M69">
-        <v>448.7522891934292</v>
+        <v>417.3167199934292</v>
       </c>
       <c r="N69">
-        <v>234.3558740718768</v>
+        <v>265.7914432718769</v>
       </c>
       <c r="O69">
-        <v>70.30676222156305</v>
+        <v>79.73743298156307</v>
       </c>
       <c r="P69">
-        <v>164.0491118503138</v>
+        <v>186.0540102903138</v>
       </c>
       <c r="Q69">
-        <v>241.3491118503138</v>
+        <v>263.3540102903139</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1584093480221027</v>
+        <v>0.1583839330399976</v>
       </c>
       <c r="T69">
         <v>1.638233405082197</v>
       </c>
       <c r="U69">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V69">
         <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.522238838030441</v>
+        <v>1.636905809276134</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7128,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.140290773749563</v>
+        <v>0.1034853653085783</v>
       </c>
       <c r="C70">
-        <v>-170.761018136116</v>
+        <v>1072.876640730642</v>
       </c>
       <c r="D70">
-        <v>2865.262981863883</v>
+        <v>4108.900640730641</v>
       </c>
       <c r="E70">
         <v>2417.724</v>
@@ -7033,45 +7161,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M70">
-        <v>709.9099741545251</v>
+        <v>423.5453277545251</v>
       </c>
       <c r="N70">
-        <v>-26.80181088921904</v>
+        <v>259.5628355107809</v>
       </c>
       <c r="O70">
-        <v>-8.040543266765711</v>
+        <v>77.86885065323428</v>
       </c>
       <c r="P70">
-        <v>-18.76126762245333</v>
+        <v>181.6939848575466</v>
       </c>
       <c r="Q70">
-        <v>58.53873237754674</v>
+        <v>258.9939848575467</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1626117568254943</v>
+        <v>0.1614662528588336</v>
       </c>
       <c r="T70">
-        <v>1.699369772572544</v>
+        <v>1.683084914138734</v>
       </c>
       <c r="U70">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V70">
-        <v>0.2886738550527598</v>
+        <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.1297867817138306</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.9622461835091992</v>
+        <v>1.612833665022073</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7210,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1416573486317847</v>
+        <v>0.103649870737761</v>
       </c>
       <c r="C71">
-        <v>-259.8294643693357</v>
+        <v>1007.700690460997</v>
       </c>
       <c r="D71">
-        <v>2833.412535630664</v>
+        <v>4100.942690460996</v>
       </c>
       <c r="E71">
         <v>2474.942</v>
@@ -7115,45 +7243,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M71">
-        <v>720.3498267156211</v>
+        <v>429.7739355156211</v>
       </c>
       <c r="N71">
-        <v>-37.24166345031506</v>
+        <v>253.3342277496849</v>
       </c>
       <c r="O71">
-        <v>-11.17249903509452</v>
+        <v>76.00026832490548</v>
       </c>
       <c r="P71">
-        <v>-26.06916441522054</v>
+        <v>177.3339594247795</v>
       </c>
       <c r="Q71">
-        <v>51.23083558477953</v>
+        <v>254.6339594247795</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1663798780134135</v>
+        <v>0.1647474320208203</v>
       </c>
       <c r="T71">
-        <v>1.754188152332949</v>
+        <v>1.730830068940854</v>
       </c>
       <c r="U71">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V71">
-        <v>0.2844901759940241</v>
+        <v>0.3</v>
       </c>
       <c r="W71">
-        <v>0.1305501252864152</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.948300586646747</v>
+        <v>1.589459264079724</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7292,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1430239235140063</v>
+        <v>0.1038143761669437</v>
       </c>
       <c r="C72">
-        <v>-348.1975921991266</v>
+        <v>942.5555058691584</v>
       </c>
       <c r="D72">
-        <v>2802.262407800873</v>
+        <v>4093.015505869158</v>
       </c>
       <c r="E72">
         <v>2532.16</v>
@@ -7197,45 +7325,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M72">
-        <v>730.789679276717</v>
+        <v>436.0025432767171</v>
       </c>
       <c r="N72">
-        <v>-47.68151601141096</v>
+        <v>247.105619988589</v>
       </c>
       <c r="O72">
-        <v>-14.30445480342329</v>
+        <v>74.13168599657671</v>
       </c>
       <c r="P72">
-        <v>-33.37706120798767</v>
+        <v>172.9739339920123</v>
       </c>
       <c r="Q72">
-        <v>43.9229387920124</v>
+        <v>250.2739339920124</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1703992072805273</v>
+        <v>0.1682473564602728</v>
       </c>
       <c r="T72">
-        <v>1.812661090744047</v>
+        <v>1.781758234063115</v>
       </c>
       <c r="U72">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V72">
-        <v>0.2804260306226809</v>
+        <v>0.3</v>
       </c>
       <c r="W72">
-        <v>0.1312916590426402</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.9347534354089364</v>
+        <v>1.5667527031643</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7374,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.144390498396228</v>
+        <v>0.1039788815961264</v>
       </c>
       <c r="C73">
-        <v>-435.8882480530465</v>
+        <v>877.4409088877665</v>
       </c>
       <c r="D73">
-        <v>2771.789751946952</v>
+        <v>4085.118908887766</v>
       </c>
       <c r="E73">
         <v>2589.377999999999</v>
@@ -7279,45 +7407,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M73">
-        <v>741.2295318378128</v>
+        <v>442.2311510378129</v>
       </c>
       <c r="N73">
-        <v>-58.12136857250675</v>
+        <v>240.8770122274931</v>
       </c>
       <c r="O73">
-        <v>-17.43641057175202</v>
+        <v>72.26310366824794</v>
       </c>
       <c r="P73">
-        <v>-40.68495800075473</v>
+        <v>168.6139085592452</v>
       </c>
       <c r="Q73">
-        <v>36.61504199924534</v>
+        <v>245.9139085592453</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.174695731669511</v>
+        <v>0.1719886549989978</v>
       </c>
       <c r="T73">
-        <v>1.87516664559729</v>
+        <v>1.836198686435187</v>
       </c>
       <c r="U73">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V73">
-        <v>0.2764763682195446</v>
+        <v>0.3</v>
       </c>
       <c r="W73">
-        <v>0.132012304524042</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.9215878940651487</v>
+        <v>1.544685763683113</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7456,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1457570732784497</v>
+        <v>0.1041433870253091</v>
       </c>
       <c r="C74">
-        <v>-522.9232952927287</v>
+        <v>812.3567228209804</v>
       </c>
       <c r="D74">
-        <v>2741.97270470727</v>
+        <v>4077.252722820979</v>
       </c>
       <c r="E74">
         <v>2646.595999999999</v>
@@ -7361,45 +7489,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M74">
-        <v>751.6693843989088</v>
+        <v>448.4597587989089</v>
       </c>
       <c r="N74">
-        <v>-68.56122113360277</v>
+        <v>234.6484044663972</v>
       </c>
       <c r="O74">
-        <v>-20.56836634008083</v>
+        <v>70.39452133991917</v>
       </c>
       <c r="P74">
-        <v>-47.99285479352194</v>
+        <v>164.2538831264781</v>
       </c>
       <c r="Q74">
-        <v>29.30714520647813</v>
+        <v>241.5538831264781</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1792991506577078</v>
+        <v>0.1759971891476318</v>
       </c>
       <c r="T74">
-        <v>1.94213688294005</v>
+        <v>1.894527742548122</v>
       </c>
       <c r="U74">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V74">
-        <v>0.2726364186609398</v>
+        <v>0.3</v>
       </c>
       <c r="W74">
-        <v>0.1327129320754049</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.9087880622031328</v>
+        <v>1.52323179474307</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7538,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1471236481606714</v>
+        <v>0.1043078924544918</v>
       </c>
       <c r="C75">
-        <v>-609.3236665269487</v>
+        <v>747.3027723313107</v>
       </c>
       <c r="D75">
-        <v>2712.790333473051</v>
+        <v>4069.41677233131</v>
       </c>
       <c r="E75">
         <v>2703.814</v>
@@ -7443,45 +7571,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M75">
-        <v>762.1092369600049</v>
+        <v>454.6883665600049</v>
       </c>
       <c r="N75">
-        <v>-79.00107369469879</v>
+        <v>228.4197967053012</v>
       </c>
       <c r="O75">
-        <v>-23.70032210840964</v>
+        <v>68.52593901159035</v>
       </c>
       <c r="P75">
-        <v>-55.30075158628915</v>
+        <v>159.8938576937108</v>
       </c>
       <c r="Q75">
-        <v>21.99924841371092</v>
+        <v>237.1938576937109</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1842435636450303</v>
+        <v>0.1803026517517202</v>
       </c>
       <c r="T75">
-        <v>2.014067878604497</v>
+        <v>1.957177469484237</v>
       </c>
       <c r="U75">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V75">
-        <v>0.268901673199831</v>
+        <v>0.3</v>
       </c>
       <c r="W75">
-        <v>0.1333943643513879</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8963389106661035</v>
+        <v>1.502365605773986</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7620,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1484902230428931</v>
+        <v>0.1351241125626112</v>
       </c>
       <c r="C76">
-        <v>-695.1094126192957</v>
+        <v>-387.1515067099908</v>
       </c>
       <c r="D76">
-        <v>2684.222587380704</v>
+        <v>2992.180493290009</v>
       </c>
       <c r="E76">
         <v>2761.032</v>
@@ -7525,37 +7653,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M76">
-        <v>772.5490895211009</v>
+        <v>701.415671921101</v>
       </c>
       <c r="N76">
-        <v>-89.44092625579481</v>
+        <v>-18.30750865579489</v>
       </c>
       <c r="O76">
-        <v>-26.83227787673844</v>
+        <v>-5.492252596738467</v>
       </c>
       <c r="P76">
-        <v>-62.60864837905636</v>
+        <v>-12.81525605905642</v>
       </c>
       <c r="Q76">
-        <v>14.69135162094371</v>
+        <v>64.48474394094364</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1895683160929161</v>
+        <v>0.1859755834764475</v>
       </c>
       <c r="T76">
-        <v>2.091532027781593</v>
+        <v>2.039725538336097</v>
       </c>
       <c r="U76">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V76">
-        <v>0.2652678668052387</v>
+        <v>0.2921697606474977</v>
       </c>
       <c r="W76">
-        <v>0.1340573795388309</v>
+        <v>0.1172573795388309</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.884226222684129</v>
+        <v>0.9738992021583256</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7702,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1498567979251147</v>
+        <v>0.1363226874448329</v>
       </c>
       <c r="C77">
-        <v>-780.2997486315944</v>
+        <v>-474.8627626544485</v>
       </c>
       <c r="D77">
-        <v>2656.250251368405</v>
+        <v>2961.687237345551</v>
       </c>
       <c r="E77">
         <v>2818.25</v>
@@ -7607,37 +7735,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M77">
-        <v>782.9889420821968</v>
+        <v>710.8942620821969</v>
       </c>
       <c r="N77">
-        <v>-99.88077881689071</v>
+        <v>-27.78609881689079</v>
       </c>
       <c r="O77">
-        <v>-29.96423364506721</v>
+        <v>-8.335829645067236</v>
       </c>
       <c r="P77">
-        <v>-69.9165451718235</v>
+        <v>-19.45026917182355</v>
       </c>
       <c r="Q77">
-        <v>7.383454828176568</v>
+        <v>57.84973082817652</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1953190487366327</v>
+        <v>0.1915826068155055</v>
       </c>
       <c r="T77">
-        <v>2.175193308892856</v>
+        <v>2.121314559869541</v>
       </c>
       <c r="U77">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V77">
-        <v>0.2617309619145022</v>
+        <v>0.2882741638388644</v>
       </c>
       <c r="W77">
-        <v>0.1347027143212754</v>
+        <v>0.1179027143212754</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8724365397150073</v>
+        <v>0.9609138794628813</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7784,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1512233728073363</v>
+        <v>0.1375212623270546</v>
       </c>
       <c r="C78">
-        <v>-864.9130969242879</v>
+        <v>-561.9587761114699</v>
       </c>
       <c r="D78">
-        <v>2628.854903075712</v>
+        <v>2931.809223888529</v>
       </c>
       <c r="E78">
         <v>2875.467999999999</v>
@@ -7689,37 +7817,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M78">
-        <v>793.4287946432927</v>
+        <v>720.3728522432928</v>
       </c>
       <c r="N78">
-        <v>-110.3206313779866</v>
+        <v>-37.26468897798668</v>
       </c>
       <c r="O78">
-        <v>-33.09618941339598</v>
+        <v>-11.179406693396</v>
       </c>
       <c r="P78">
-        <v>-77.22444196459062</v>
+        <v>-26.08528228459068</v>
       </c>
       <c r="Q78">
-        <v>0.07555803540944339</v>
+        <v>51.21471771540939</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2015490091006591</v>
+        <v>0.1976568820994848</v>
       </c>
       <c r="T78">
-        <v>2.265826363430059</v>
+        <v>2.209702666530772</v>
       </c>
       <c r="U78">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V78">
-        <v>0.2582871334682588</v>
+        <v>0.2844810827357214</v>
       </c>
       <c r="W78">
-        <v>0.135331066609445</v>
+        <v>0.118531066609445</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8609571115608625</v>
+        <v>0.9482702757857382</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7866,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.152589947689558</v>
+        <v>0.1387198372092762</v>
       </c>
       <c r="C79">
-        <v>-948.9671276169438</v>
+        <v>-648.4579811332405</v>
       </c>
       <c r="D79">
-        <v>2602.018872383056</v>
+        <v>2902.528018866758</v>
       </c>
       <c r="E79">
         <v>2932.685999999999</v>
@@ -7771,37 +7899,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M79">
-        <v>803.8686472043886</v>
+        <v>729.8514424043888</v>
       </c>
       <c r="N79">
-        <v>-120.7604839390825</v>
+        <v>-46.74327913908269</v>
       </c>
       <c r="O79">
-        <v>-36.22814518172476</v>
+        <v>-14.02298374172481</v>
       </c>
       <c r="P79">
-        <v>-84.53233875735776</v>
+        <v>-32.72029539735788</v>
       </c>
       <c r="Q79">
-        <v>-7.232338757357695</v>
+        <v>44.57970460264219</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2083207051485138</v>
+        <v>0.204259355234245</v>
       </c>
       <c r="T79">
-        <v>2.364340553144409</v>
+        <v>2.305776695510371</v>
       </c>
       <c r="U79">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V79">
-        <v>0.2549327551115281</v>
+        <v>0.2807865232196731</v>
       </c>
       <c r="W79">
-        <v>0.1359430980589608</v>
+        <v>0.1191430980589609</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8497758503717605</v>
+        <v>0.9359550773989104</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7948,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1539565225717797</v>
+        <v>0.1399184120914979</v>
       </c>
       <c r="C80">
-        <v>-1032.478796595607</v>
+        <v>-734.3780826199409</v>
       </c>
       <c r="D80">
-        <v>2575.725203404392</v>
+        <v>2873.825917380059</v>
       </c>
       <c r="E80">
         <v>2989.904</v>
@@ -7853,37 +7981,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M80">
-        <v>814.3084997654847</v>
+        <v>739.3300325654848</v>
       </c>
       <c r="N80">
-        <v>-131.2003365001787</v>
+        <v>-56.2218693001787</v>
       </c>
       <c r="O80">
-        <v>-39.36010095005359</v>
+        <v>-16.86656079005361</v>
       </c>
       <c r="P80">
-        <v>-91.84023555012506</v>
+        <v>-39.35530851012508</v>
       </c>
       <c r="Q80">
-        <v>-14.54023555012499</v>
+        <v>37.94469148987498</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2157080099279917</v>
+        <v>0.211462053199438</v>
       </c>
       <c r="T80">
-        <v>2.471810578287337</v>
+        <v>2.410584727124479</v>
       </c>
       <c r="U80">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V80">
-        <v>0.2516643864562521</v>
+        <v>0.2771866959989081</v>
       </c>
       <c r="W80">
-        <v>0.1365394363943866</v>
+        <v>0.1197394363943866</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.838881288187507</v>
+        <v>0.9239556533296935</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8030,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1553230974540014</v>
+        <v>0.1411169869737196</v>
       </c>
       <c r="C81">
-        <v>-1115.464381238805</v>
+        <v>-819.7360920183855</v>
       </c>
       <c r="D81">
-        <v>2549.957618761195</v>
+        <v>2845.685907981614</v>
       </c>
       <c r="E81">
         <v>3047.122</v>
@@ -7935,37 +8063,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M81">
-        <v>824.7483523265806</v>
+        <v>748.8086227265808</v>
       </c>
       <c r="N81">
-        <v>-141.6401890612746</v>
+        <v>-65.7004594612747</v>
       </c>
       <c r="O81">
-        <v>-42.49205671838236</v>
+        <v>-19.71013783838241</v>
       </c>
       <c r="P81">
-        <v>-99.14813234289218</v>
+        <v>-45.9903216228923</v>
       </c>
       <c r="Q81">
-        <v>-21.84813234289211</v>
+        <v>31.30967837710777</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2237988675436104</v>
+        <v>0.2193507223994113</v>
       </c>
       <c r="T81">
-        <v>2.589515843920068</v>
+        <v>2.525374476035168</v>
       </c>
       <c r="U81">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V81">
-        <v>0.2484787613112363</v>
+        <v>0.2736780036444915</v>
       </c>
       <c r="W81">
-        <v>0.1371206775567635</v>
+        <v>0.1203206775567636</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8282625377041208</v>
+        <v>0.912260012148305</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8112,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1566896723362231</v>
+        <v>0.1423155618559412</v>
       </c>
       <c r="C82">
-        <v>-1197.939514020367</v>
+        <v>-904.5483609436969</v>
       </c>
       <c r="D82">
-        <v>2524.700485979633</v>
+        <v>2818.091639056302</v>
       </c>
       <c r="E82">
         <v>3104.34</v>
@@ -8017,37 +8145,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M82">
-        <v>835.1882048876765</v>
+        <v>758.2872128876767</v>
       </c>
       <c r="N82">
-        <v>-152.0800416223705</v>
+        <v>-75.1790496223706</v>
       </c>
       <c r="O82">
-        <v>-45.62401248671114</v>
+        <v>-22.55371488671118</v>
       </c>
       <c r="P82">
-        <v>-106.4560291356593</v>
+        <v>-52.62533473565942</v>
       </c>
       <c r="Q82">
-        <v>-29.15602913565925</v>
+        <v>24.67466526434065</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2326988109207909</v>
+        <v>0.2280282585193818</v>
       </c>
       <c r="T82">
-        <v>2.718991636116071</v>
+        <v>2.651643199836927</v>
       </c>
       <c r="U82">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V82">
-        <v>0.2453727767948458</v>
+        <v>0.2702570285989354</v>
       </c>
       <c r="W82">
-        <v>0.1376873876900811</v>
+        <v>0.1208873876900811</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8179092559828194</v>
+        <v>0.9008567619964511</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8194,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1580562472184447</v>
+        <v>0.1435141367381629</v>
       </c>
       <c r="C83">
-        <v>-1279.919214134838</v>
+        <v>-988.8306128636077</v>
       </c>
       <c r="D83">
-        <v>2499.938785865162</v>
+        <v>2791.027387136392</v>
       </c>
       <c r="E83">
         <v>3161.558</v>
@@ -8099,37 +8227,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M83">
-        <v>845.6280574487726</v>
+        <v>767.7658030487726</v>
       </c>
       <c r="N83">
-        <v>-162.5198941834665</v>
+        <v>-84.65763978346649</v>
       </c>
       <c r="O83">
-        <v>-48.75596825503994</v>
+        <v>-25.39729193503995</v>
       </c>
       <c r="P83">
-        <v>-113.7639259284265</v>
+        <v>-59.26034784842655</v>
       </c>
       <c r="Q83">
-        <v>-36.46392592842648</v>
+        <v>18.03965215157352</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2425355904429378</v>
+        <v>0.2376192194940861</v>
       </c>
       <c r="T83">
-        <v>2.862096459069548</v>
+        <v>2.791203368249397</v>
       </c>
       <c r="U83">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V83">
-        <v>0.2423434832541687</v>
+        <v>0.2669205220730226</v>
       </c>
       <c r="W83">
-        <v>0.1382401049806007</v>
+        <v>0.1214401049806007</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8078116108472291</v>
+        <v>0.889735073576742</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8276,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2042577478908336</v>
+        <v>0.1447127116203846</v>
       </c>
       <c r="C84">
-        <v>-1959.658392243154</v>
+        <v>-1072.597972974389</v>
       </c>
       <c r="D84">
-        <v>1877.417607756846</v>
+        <v>2764.478027025611</v>
       </c>
       <c r="E84">
         <v>3218.776</v>
@@ -8181,45 +8309,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M84">
-        <v>1100.983837209869</v>
+        <v>777.2443932098687</v>
       </c>
       <c r="N84">
-        <v>-417.8756739445625</v>
+        <v>-94.13622994456261</v>
       </c>
       <c r="O84">
-        <v>-125.3627021833688</v>
+        <v>-28.24086898336878</v>
       </c>
       <c r="P84">
-        <v>-292.5129717611938</v>
+        <v>-65.89536096119383</v>
       </c>
       <c r="Q84">
-        <v>-215.2129717611937</v>
+        <v>11.40463903880624</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2647482665240297</v>
+        <v>0.2482758427993132</v>
       </c>
       <c r="T84">
-        <v>3.185245012999303</v>
+        <v>2.946270222041031</v>
       </c>
       <c r="U84">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V84">
-        <v>0.1861357470050923</v>
+        <v>0.2636653937550589</v>
       </c>
       <c r="W84">
-        <v>0.1909793413615954</v>
+        <v>0.1219793413615954</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.6204524900169743</v>
+        <v>0.8788846458501962</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8358,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2061463227730552</v>
+        <v>0.1459112865026063</v>
       </c>
       <c r="C85">
-        <v>-2035.793966897578</v>
+        <v>-1155.864996387698</v>
       </c>
       <c r="D85">
-        <v>1858.500033102423</v>
+        <v>2738.429003612302</v>
       </c>
       <c r="E85">
         <v>3275.994</v>
@@ -8263,45 +8391,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M85">
-        <v>1114.410469370965</v>
+        <v>786.7229833709646</v>
       </c>
       <c r="N85">
-        <v>-431.3023061056585</v>
+        <v>-103.6148201056585</v>
       </c>
       <c r="O85">
-        <v>-129.3906918316976</v>
+        <v>-31.08444603169755</v>
       </c>
       <c r="P85">
-        <v>-301.911614273961</v>
+        <v>-72.53037407396096</v>
       </c>
       <c r="Q85">
-        <v>-224.6116142739609</v>
+        <v>4.769625926039112</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2776275763195608</v>
+        <v>0.2601861864933904</v>
       </c>
       <c r="T85">
-        <v>3.372612366705145</v>
+        <v>3.119580235102267</v>
       </c>
       <c r="U85">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V85">
-        <v>0.1838931476435851</v>
+        <v>0.260488702264034</v>
       </c>
       <c r="W85">
-        <v>0.1915055840948553</v>
+        <v>0.1225055840948553</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.6129771588119505</v>
+        <v>0.8682956742134469</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8440,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2080348976552769</v>
+        <v>0.1471098613848279</v>
       </c>
       <c r="C86">
-        <v>-2111.552103392201</v>
+        <v>-1238.645694738733</v>
       </c>
       <c r="D86">
-        <v>1839.959896607798</v>
+        <v>2712.866305261266</v>
       </c>
       <c r="E86">
         <v>3333.211999999999</v>
@@ -8345,45 +8473,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M86">
-        <v>1127.83710153206</v>
+        <v>796.2015735320604</v>
       </c>
       <c r="N86">
-        <v>-444.7289382667543</v>
+        <v>-113.0934102667543</v>
       </c>
       <c r="O86">
-        <v>-133.4186814800263</v>
+        <v>-33.92802308002629</v>
       </c>
       <c r="P86">
-        <v>-311.310256786728</v>
+        <v>-79.165387186728</v>
       </c>
       <c r="Q86">
-        <v>-234.010256786728</v>
+        <v>-1.865387186727929</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2921167998395332</v>
+        <v>0.2735853231492272</v>
       </c>
       <c r="T86">
-        <v>3.583400639624214</v>
+        <v>3.314553999796157</v>
       </c>
       <c r="U86">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V86">
-        <v>0.1817039435049711</v>
+        <v>0.2573876462847004</v>
       </c>
       <c r="W86">
-        <v>0.1920192972392281</v>
+        <v>0.1230192972392281</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.6056798116832369</v>
+        <v>0.8579588209490013</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8522,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2099234725374985</v>
+        <v>0.1483084362670496</v>
       </c>
       <c r="C87">
-        <v>-2186.943985965565</v>
+        <v>-1320.953561317867</v>
       </c>
       <c r="D87">
-        <v>1821.786014034434</v>
+        <v>2687.776438682132</v>
       </c>
       <c r="E87">
         <v>3390.429999999999</v>
@@ -8427,45 +8555,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M87">
-        <v>1141.263733693156</v>
+        <v>805.6801636931564</v>
       </c>
       <c r="N87">
-        <v>-458.1555704278503</v>
+        <v>-122.5720004278503</v>
       </c>
       <c r="O87">
-        <v>-137.4466711283551</v>
+        <v>-36.77160012835509</v>
       </c>
       <c r="P87">
-        <v>-320.7088992994952</v>
+        <v>-85.80040029949521</v>
       </c>
       <c r="Q87">
-        <v>-243.4088992994951</v>
+        <v>-8.500400299495141</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3085379198288354</v>
+        <v>0.2887710113591757</v>
       </c>
       <c r="T87">
-        <v>3.822294015599161</v>
+        <v>3.535524266449235</v>
       </c>
       <c r="U87">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V87">
-        <v>0.1795662500519714</v>
+        <v>0.2543595563284098</v>
       </c>
       <c r="W87">
-        <v>0.1925209230154979</v>
+        <v>0.1235209230154979</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.5985541668399047</v>
+        <v>0.8478651877613659</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8604,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2118120474197202</v>
+        <v>0.1495070111492713</v>
       </c>
       <c r="C88">
-        <v>-2261.980361296673</v>
+        <v>-1402.801594820465</v>
       </c>
       <c r="D88">
-        <v>1803.967638703327</v>
+        <v>2663.146405179535</v>
       </c>
       <c r="E88">
         <v>3447.648</v>
@@ -8509,45 +8637,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M88">
-        <v>1154.690365854252</v>
+        <v>815.1587538542524</v>
       </c>
       <c r="N88">
-        <v>-471.5822025889463</v>
+        <v>-132.0505905889463</v>
       </c>
       <c r="O88">
-        <v>-141.4746607766839</v>
+        <v>-39.61517717668389</v>
       </c>
       <c r="P88">
-        <v>-330.1075418122624</v>
+        <v>-92.43541341226242</v>
       </c>
       <c r="Q88">
-        <v>-252.8075418122623</v>
+        <v>-15.13541341226235</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3273049141023237</v>
+        <v>0.3061260835991168</v>
       </c>
       <c r="T88">
-        <v>4.095315016713387</v>
+        <v>3.788061714052752</v>
       </c>
       <c r="U88">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V88">
-        <v>0.1774782704002043</v>
+        <v>0.2514018870687771</v>
       </c>
       <c r="W88">
-        <v>0.1930108830760406</v>
+        <v>0.1240108830760406</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5915942346673476</v>
+        <v>0.838006290229257</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8686,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2137006223019419</v>
+        <v>0.150705586031493</v>
       </c>
       <c r="C89">
-        <v>-2336.671559695961</v>
+        <v>-1484.202321802774</v>
       </c>
       <c r="D89">
-        <v>1786.494440304038</v>
+        <v>2638.963678197225</v>
       </c>
       <c r="E89">
         <v>3504.866</v>
@@ -8591,45 +8719,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M89">
-        <v>1168.116998015348</v>
+        <v>824.6373440153484</v>
       </c>
       <c r="N89">
-        <v>-485.0088347500423</v>
+        <v>-141.5291807500423</v>
       </c>
       <c r="O89">
-        <v>-145.5026504250127</v>
+        <v>-42.45875422501269</v>
       </c>
       <c r="P89">
-        <v>-339.5061843250296</v>
+        <v>-99.07042652502963</v>
       </c>
       <c r="Q89">
-        <v>-262.2061843250295</v>
+        <v>-21.77042652502956</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.348959138264041</v>
+        <v>0.326151166952895</v>
       </c>
       <c r="T89">
-        <v>4.410339248768264</v>
+        <v>4.079451076672195</v>
       </c>
       <c r="U89">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V89">
-        <v>0.1754382902806617</v>
+        <v>0.2485122102059175</v>
       </c>
       <c r="W89">
-        <v>0.1934895796869156</v>
+        <v>0.1244895796869156</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.584794300935539</v>
+        <v>0.8283740340197252</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8768,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2155891971841636</v>
+        <v>0.1519041609137146</v>
       </c>
       <c r="C90">
-        <v>-2411.027515076557</v>
+        <v>-1565.167817925339</v>
       </c>
       <c r="D90">
-        <v>1769.356484923442</v>
+        <v>2615.21618207466</v>
       </c>
       <c r="E90">
         <v>3562.083999999999</v>
@@ -8673,45 +8801,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M90">
-        <v>1181.543630176444</v>
+        <v>834.1159341764443</v>
       </c>
       <c r="N90">
-        <v>-498.4354669111383</v>
+        <v>-151.0077709111382</v>
       </c>
       <c r="O90">
-        <v>-149.5306400733415</v>
+        <v>-45.30233127334146</v>
       </c>
       <c r="P90">
-        <v>-348.9048268377968</v>
+        <v>-105.7054396377968</v>
       </c>
       <c r="Q90">
-        <v>-271.6048268377967</v>
+        <v>-28.40543963779669</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3742223997860444</v>
+        <v>0.3495137641989696</v>
       </c>
       <c r="T90">
-        <v>4.777867519498954</v>
+        <v>4.419405333061544</v>
       </c>
       <c r="U90">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V90">
-        <v>0.1734446733456542</v>
+        <v>0.245688207817214</v>
       </c>
       <c r="W90">
-        <v>0.1939573968293617</v>
+        <v>0.1249573968293617</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.5781489111521806</v>
+        <v>0.8189606927240466</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8850,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2174777720663853</v>
+        <v>0.1531027357959363</v>
       </c>
       <c r="C91">
-        <v>-2485.057783786931</v>
+        <v>-1645.709728059663</v>
       </c>
       <c r="D91">
-        <v>1752.544216213068</v>
+        <v>2591.892271940337</v>
       </c>
       <c r="E91">
         <v>3619.301999999999</v>
@@ -8755,45 +8883,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M91">
-        <v>1194.97026233754</v>
+        <v>843.5945243375402</v>
       </c>
       <c r="N91">
-        <v>-511.8620990722341</v>
+        <v>-160.4863610722341</v>
       </c>
       <c r="O91">
-        <v>-153.5586297216702</v>
+        <v>-48.14590832167023</v>
       </c>
       <c r="P91">
-        <v>-358.3034693505639</v>
+        <v>-112.3404527505639</v>
       </c>
       <c r="Q91">
-        <v>-281.0034693505638</v>
+        <v>-35.04045275056382</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4040789815847757</v>
+        <v>0.3771241063988759</v>
       </c>
       <c r="T91">
-        <v>5.212219112180676</v>
+        <v>4.821169454248957</v>
       </c>
       <c r="U91">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V91">
-        <v>0.1714958567912086</v>
+        <v>0.2429276661563464</v>
       </c>
       <c r="W91">
-        <v>0.1944147012270336</v>
+        <v>0.1254147012270336</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.5716528559706955</v>
+        <v>0.8097588871878214</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8932,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.219366346948607</v>
+        <v>0.1543013106781579</v>
       </c>
       <c r="C92">
-        <v>-2558.771562379992</v>
+        <v>-1725.839285328429</v>
       </c>
       <c r="D92">
-        <v>1736.048437620008</v>
+        <v>2568.98071467157</v>
       </c>
       <c r="E92">
         <v>3676.52</v>
@@ -8837,45 +8965,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M92">
-        <v>1208.396894498636</v>
+        <v>853.0731144986363</v>
       </c>
       <c r="N92">
-        <v>-525.2887312333303</v>
+        <v>-169.9649512333302</v>
       </c>
       <c r="O92">
-        <v>-157.5866193699991</v>
+        <v>-50.98948536999907</v>
       </c>
       <c r="P92">
-        <v>-367.7021118633312</v>
+        <v>-118.9754658633312</v>
       </c>
       <c r="Q92">
-        <v>-290.4021118633311</v>
+        <v>-41.67546586333108</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4399068797432534</v>
+        <v>0.4102565170387636</v>
       </c>
       <c r="T92">
-        <v>5.733441023398745</v>
+        <v>5.303286399673854</v>
       </c>
       <c r="U92">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V92">
-        <v>0.1695903472713063</v>
+        <v>0.2402284698657203</v>
       </c>
       <c r="W92">
-        <v>0.1948618433047574</v>
+        <v>0.1258618433047573</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.565301157571021</v>
+        <v>0.8007615662190677</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +9014,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2212549218308286</v>
+        <v>0.2071113724333695</v>
       </c>
       <c r="C93">
-        <v>-2632.177704388022</v>
+        <v>-2503.163546062043</v>
       </c>
       <c r="D93">
-        <v>1719.860295611978</v>
+        <v>1848.874453937957</v>
       </c>
       <c r="E93">
         <v>3733.738</v>
@@ -8919,37 +9047,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M93">
-        <v>1221.823526659732</v>
+        <v>1143.720956659732</v>
       </c>
       <c r="N93">
-        <v>-538.7153633944263</v>
+        <v>-460.612793394426</v>
       </c>
       <c r="O93">
-        <v>-161.6146090183279</v>
+        <v>-138.1838380183278</v>
       </c>
       <c r="P93">
-        <v>-377.1007543760984</v>
+        <v>-322.4289553760982</v>
       </c>
       <c r="Q93">
-        <v>-299.8007543760983</v>
+        <v>-245.1289553760981</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4836965330480593</v>
+        <v>0.4782126508540689</v>
       </c>
       <c r="T93">
-        <v>6.370490025998605</v>
+        <v>6.292130948717255</v>
       </c>
       <c r="U93">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V93">
-        <v>0.1677267170815117</v>
+        <v>0.1791804616207283</v>
       </c>
       <c r="W93">
-        <v>0.1952991580840695</v>
+        <v>0.1802991580840695</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5590890569383724</v>
+        <v>0.5972682054024278</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9096,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2231434967130503</v>
+        <v>0.2088499473155911</v>
       </c>
       <c r="C94">
-        <v>-2705.284736167767</v>
+        <v>-2577.287144715825</v>
       </c>
       <c r="D94">
-        <v>1703.971263832233</v>
+        <v>1831.968855284175</v>
       </c>
       <c r="E94">
         <v>3790.956</v>
@@ -9001,37 +9129,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M94">
-        <v>1235.250158820828</v>
+        <v>1156.289318820828</v>
       </c>
       <c r="N94">
-        <v>-552.141995555522</v>
+        <v>-473.1811555555221</v>
       </c>
       <c r="O94">
-        <v>-165.6425986666566</v>
+        <v>-141.9543466666566</v>
       </c>
       <c r="P94">
-        <v>-386.4993968888655</v>
+        <v>-331.2268088888654</v>
       </c>
       <c r="Q94">
-        <v>-309.1993968888654</v>
+        <v>-253.9268088888654</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5384335996790668</v>
+        <v>0.5322642322108276</v>
       </c>
       <c r="T94">
-        <v>7.166801279248433</v>
+        <v>7.078647317306913</v>
       </c>
       <c r="U94">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V94">
-        <v>0.1659036005914953</v>
+        <v>0.1772328479074595</v>
       </c>
       <c r="W94">
-        <v>0.1957269660203532</v>
+        <v>0.1807269660203532</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5530120019716511</v>
+        <v>0.5907761596915317</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9178,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2250320715952719</v>
+        <v>0.2105885221978128</v>
       </c>
       <c r="C95">
-        <v>-2778.100871875234</v>
+        <v>-2651.104384358591</v>
       </c>
       <c r="D95">
-        <v>1688.373128124765</v>
+        <v>1815.369615641408</v>
       </c>
       <c r="E95">
         <v>3848.174</v>
@@ -9083,37 +9211,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M95">
-        <v>1248.676790981924</v>
+        <v>1168.857680981924</v>
       </c>
       <c r="N95">
-        <v>-565.568627716618</v>
+        <v>-485.7495177166179</v>
       </c>
       <c r="O95">
-        <v>-169.6705883149854</v>
+        <v>-145.7248553149854</v>
       </c>
       <c r="P95">
-        <v>-395.8980394016327</v>
+        <v>-340.0246624016326</v>
       </c>
       <c r="Q95">
-        <v>-318.5980394016326</v>
+        <v>-262.7246624016325</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6088098282046478</v>
+        <v>0.6017591225266602</v>
       </c>
       <c r="T95">
-        <v>8.190630033426782</v>
+        <v>8.089882648350759</v>
       </c>
       <c r="U95">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V95">
-        <v>0.1641196909077158</v>
+        <v>0.1753271183600675</v>
       </c>
       <c r="W95">
-        <v>0.1961455737859641</v>
+        <v>0.1811455737859641</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5470656363590527</v>
+        <v>0.5844237278668918</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9260,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2269206464774936</v>
+        <v>0.2123270970800345</v>
       </c>
       <c r="C96">
-        <v>-2850.634027625494</v>
+        <v>-2724.623517853713</v>
       </c>
       <c r="D96">
-        <v>1673.057972374505</v>
+        <v>1799.068482146286</v>
       </c>
       <c r="E96">
         <v>3905.391999999999</v>
@@ -9165,37 +9293,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M96">
-        <v>1262.10342314302</v>
+        <v>1181.42604314302</v>
       </c>
       <c r="N96">
-        <v>-578.995259877714</v>
+        <v>-498.3178798777139</v>
       </c>
       <c r="O96">
-        <v>-173.6985779633142</v>
+        <v>-149.4953639633142</v>
       </c>
       <c r="P96">
-        <v>-405.2966819143999</v>
+        <v>-348.8225159143998</v>
       </c>
       <c r="Q96">
-        <v>-327.9966819143998</v>
+        <v>-271.5225159143997</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7026447995720893</v>
+        <v>0.6944189762811036</v>
       </c>
       <c r="T96">
-        <v>9.555735038997915</v>
+        <v>9.438196423075887</v>
       </c>
       <c r="U96">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V96">
-        <v>0.1623737367491231</v>
+        <v>0.173461936249854</v>
       </c>
       <c r="W96">
-        <v>0.1965552750033705</v>
+        <v>0.1815552750033705</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5412457891637436</v>
+        <v>0.57820645416618</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9342,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2288092213597153</v>
+        <v>0.2140656719622561</v>
       </c>
       <c r="C97">
-        <v>-2922.89183488874</v>
+        <v>-2797.852504275897</v>
       </c>
       <c r="D97">
-        <v>1658.01816511126</v>
+        <v>1783.057495724104</v>
       </c>
       <c r="E97">
         <v>3962.61</v>
@@ -9247,37 +9375,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M97">
-        <v>1275.530055304116</v>
+        <v>1193.994405304116</v>
       </c>
       <c r="N97">
-        <v>-592.42189203881</v>
+        <v>-510.88624203881</v>
       </c>
       <c r="O97">
-        <v>-177.726567611643</v>
+        <v>-153.265872611643</v>
       </c>
       <c r="P97">
-        <v>-414.6953244271671</v>
+        <v>-357.620369427167</v>
       </c>
       <c r="Q97">
-        <v>-337.395324427167</v>
+        <v>-280.320369427167</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8340137594865076</v>
+        <v>0.8241427715373248</v>
       </c>
       <c r="T97">
-        <v>11.4668820467975</v>
+        <v>11.32583570769107</v>
       </c>
       <c r="U97">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V97">
-        <v>0.1606645395201849</v>
+        <v>0.1716360211314345</v>
       </c>
       <c r="W97">
-        <v>0.1969563509319895</v>
+        <v>0.1819563509319894</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.535548465067283</v>
+        <v>0.572120070438115</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9424,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.230697796241937</v>
+        <v>0.2158042468444778</v>
       </c>
       <c r="C98">
-        <v>-2994.881653170251</v>
+        <v>-2870.799021868861</v>
       </c>
       <c r="D98">
-        <v>1643.246346829748</v>
+        <v>1767.328978131138</v>
       </c>
       <c r="E98">
         <v>4019.827999999999</v>
@@ -9329,37 +9457,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M98">
-        <v>1288.956687465212</v>
+        <v>1206.562767465212</v>
       </c>
       <c r="N98">
-        <v>-605.8485241999058</v>
+        <v>-523.4546041999058</v>
       </c>
       <c r="O98">
-        <v>-181.7545572599717</v>
+        <v>-157.0363812599717</v>
       </c>
       <c r="P98">
-        <v>-424.093966939934</v>
+        <v>-366.4182229399341</v>
       </c>
       <c r="Q98">
-        <v>-346.793966939934</v>
+        <v>-289.118222939934</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.031067199358132</v>
+        <v>1.018728464421654</v>
       </c>
       <c r="T98">
-        <v>14.33360255849685</v>
+        <v>14.15729463461381</v>
       </c>
       <c r="U98">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V98">
-        <v>0.1589909505668497</v>
+        <v>0.1698481459113154</v>
       </c>
       <c r="W98">
-        <v>0.1973490711120955</v>
+        <v>0.1823490711120954</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5299698352228324</v>
+        <v>0.5661604863710513</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9506,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2325863711241586</v>
+        <v>0.2175428217266995</v>
       </c>
       <c r="C99">
-        <v>-3066.610582018531</v>
+        <v>-2943.470480323228</v>
       </c>
       <c r="D99">
-        <v>1628.735417981468</v>
+        <v>1751.875519676771</v>
       </c>
       <c r="E99">
         <v>4077.045999999999</v>
@@ -9411,37 +9539,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M99">
-        <v>1302.383319626308</v>
+        <v>1219.131129626308</v>
       </c>
       <c r="N99">
-        <v>-619.2751563610018</v>
+        <v>-536.0229663610016</v>
       </c>
       <c r="O99">
-        <v>-185.7825469083005</v>
+        <v>-160.8068899083005</v>
       </c>
       <c r="P99">
-        <v>-433.4926094527012</v>
+        <v>-375.2160764527011</v>
       </c>
       <c r="Q99">
-        <v>-356.1926094527012</v>
+        <v>-297.9160764527011</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.359489599144176</v>
+        <v>1.343037952562205</v>
       </c>
       <c r="T99">
-        <v>19.11147007799579</v>
+        <v>18.87639284615175</v>
       </c>
       <c r="U99">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V99">
-        <v>0.157351868602243</v>
+        <v>0.1680971340977967</v>
       </c>
       <c r="W99">
-        <v>0.1977336939689003</v>
+        <v>0.1827336939689003</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5245062286741433</v>
+        <v>0.5603237803259891</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9588,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2344749460063803</v>
+        <v>0.2192813966089212</v>
       </c>
       <c r="C100">
-        <v>-3138.085472402762</v>
+        <v>-3015.874032415833</v>
       </c>
       <c r="D100">
-        <v>1614.478527597237</v>
+        <v>1736.689967584167</v>
       </c>
       <c r="E100">
         <v>4134.263999999999</v>
@@ -9493,37 +9621,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M100">
-        <v>1315.809951787404</v>
+        <v>1231.699491787404</v>
       </c>
       <c r="N100">
-        <v>-632.7017885220978</v>
+        <v>-548.5913285220979</v>
       </c>
       <c r="O100">
-        <v>-189.8105365566293</v>
+        <v>-164.5773985566294</v>
       </c>
       <c r="P100">
-        <v>-442.8912519654684</v>
+        <v>-384.0139299654685</v>
       </c>
       <c r="Q100">
-        <v>-365.5912519654684</v>
+        <v>-306.7139299654685</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.016334398716265</v>
+        <v>1.991656928843308</v>
       </c>
       <c r="T100">
-        <v>28.66720511699369</v>
+        <v>28.31458926922762</v>
       </c>
       <c r="U100">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V100">
-        <v>0.1557462372899752</v>
+        <v>0.1663818572192477</v>
       </c>
       <c r="W100">
-        <v>0.1981104673796479</v>
+        <v>0.1831104673796479</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9659,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5191541242999174</v>
+        <v>0.5546061907308257</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9670,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.236363520888602</v>
+        <v>0.2210199714911429</v>
       </c>
       <c r="C101">
-        <v>-3209.312937497912</v>
+        <v>-3088.016585048893</v>
       </c>
       <c r="D101">
-        <v>1600.469062502088</v>
+        <v>1721.765414951107</v>
       </c>
       <c r="E101">
         <v>4191.482</v>
@@ -9575,37 +9703,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M101">
-        <v>1329.2365839485</v>
+        <v>1244.2678539485</v>
       </c>
       <c r="N101">
-        <v>-646.1284206831938</v>
+        <v>-561.1596906831937</v>
       </c>
       <c r="O101">
-        <v>-193.8385262049581</v>
+        <v>-168.3479072049581</v>
       </c>
       <c r="P101">
-        <v>-452.2898944782356</v>
+        <v>-392.8117834782356</v>
       </c>
       <c r="Q101">
-        <v>-374.9898944782356</v>
+        <v>-315.5117834782355</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.986868797432529</v>
+        <v>3.937513857686616</v>
       </c>
       <c r="T101">
-        <v>57.33441023398739</v>
+        <v>56.62917853845524</v>
       </c>
       <c r="U101">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V101">
-        <v>0.1541730429739148</v>
+        <v>0.1647012323988513</v>
       </c>
       <c r="W101">
-        <v>0.1984796292063401</v>
+        <v>0.1834796292063401</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9741,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.5139101432463828</v>
+        <v>0.5490041079961709</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/mexico/mexico_household_products.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_household_products.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09229899612415422</v>
+        <v>0.09218560155333692</v>
       </c>
       <c r="C2">
-        <v>5588.312062476969</v>
+        <v>5538.399405683585</v>
       </c>
       <c r="D2">
-        <v>4733.512062476969</v>
+        <v>4740.817405683584</v>
       </c>
       <c r="E2">
-        <v>-1473.1</v>
+        <v>-1415.882</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>57.218</v>
       </c>
       <c r="G2">
         <v>854.8</v>
@@ -1585,28 +1585,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.957053161095958</v>
       </c>
       <c r="N2">
-        <v>683.1081632653061</v>
+        <v>679.1511101042101</v>
       </c>
       <c r="O2">
-        <v>204.9324489795918</v>
+        <v>203.745333031263</v>
       </c>
       <c r="P2">
-        <v>478.1757142857143</v>
+        <v>475.4057770729471</v>
       </c>
       <c r="Q2">
-        <v>555.4757142857143</v>
+        <v>552.7057770729472</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09229899612415422</v>
+        <v>0.09262777690483005</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6814012118760742</v>
       </c>
       <c r="U2">
         <v>0.06915748822216712</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>172.6305246493353</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09218560155333692</v>
+        <v>0.09207220698251964</v>
       </c>
       <c r="C3">
-        <v>5538.399405683585</v>
+        <v>5488.509332768788</v>
       </c>
       <c r="D3">
-        <v>4740.817405683584</v>
+        <v>4748.145332768788</v>
       </c>
       <c r="E3">
-        <v>-1415.882</v>
+        <v>-1358.664</v>
       </c>
       <c r="F3">
-        <v>57.218</v>
+        <v>114.436</v>
       </c>
       <c r="G3">
         <v>854.8</v>
@@ -1667,28 +1667,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M3">
-        <v>3.957053161095958</v>
+        <v>7.914106322191916</v>
       </c>
       <c r="N3">
-        <v>679.1511101042101</v>
+        <v>675.1940569431141</v>
       </c>
       <c r="O3">
-        <v>203.745333031263</v>
+        <v>202.5582170829342</v>
       </c>
       <c r="P3">
-        <v>475.4057770729471</v>
+        <v>472.6358398601799</v>
       </c>
       <c r="Q3">
-        <v>552.7057770729472</v>
+        <v>549.93583986018</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09262777690483005</v>
+        <v>0.09296326749735642</v>
       </c>
       <c r="T3">
-        <v>0.6814012118760742</v>
+        <v>0.6862830087801871</v>
       </c>
       <c r="U3">
         <v>0.06915748822216712</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>172.6305246493353</v>
+        <v>86.31526232466766</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09207220698251964</v>
+        <v>0.09195881241170234</v>
       </c>
       <c r="C4">
-        <v>5488.509332768788</v>
+        <v>5438.641948619061</v>
       </c>
       <c r="D4">
-        <v>4748.145332768788</v>
+        <v>4755.49594861906</v>
       </c>
       <c r="E4">
-        <v>-1358.664</v>
+        <v>-1301.446</v>
       </c>
       <c r="F4">
-        <v>114.436</v>
+        <v>171.654</v>
       </c>
       <c r="G4">
         <v>854.8</v>
@@ -1749,28 +1749,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M4">
-        <v>7.914106322191916</v>
+        <v>11.87115948328787</v>
       </c>
       <c r="N4">
-        <v>675.1940569431141</v>
+        <v>671.2370037820182</v>
       </c>
       <c r="O4">
-        <v>202.5582170829342</v>
+        <v>201.3711011346055</v>
       </c>
       <c r="P4">
-        <v>472.6358398601799</v>
+        <v>469.8659026474127</v>
       </c>
       <c r="Q4">
-        <v>549.93583986018</v>
+        <v>547.1659026474128</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09296326749735642</v>
+        <v>0.09330567542168745</v>
       </c>
       <c r="T4">
-        <v>0.6862830087801871</v>
+        <v>0.6912654612905703</v>
       </c>
       <c r="U4">
         <v>0.06915748822216712</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.31526232466766</v>
+        <v>57.54350821644512</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09195881241170234</v>
+        <v>0.09184541784088505</v>
       </c>
       <c r="C5">
-        <v>5438.641948619061</v>
+        <v>5388.797358771387</v>
       </c>
       <c r="D5">
-        <v>4755.49594861906</v>
+        <v>4762.869358771387</v>
       </c>
       <c r="E5">
-        <v>-1301.446</v>
+        <v>-1244.228</v>
       </c>
       <c r="F5">
-        <v>171.654</v>
+        <v>228.872</v>
       </c>
       <c r="G5">
         <v>854.8</v>
@@ -1831,28 +1831,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M5">
-        <v>11.87115948328787</v>
+        <v>15.82821264438383</v>
       </c>
       <c r="N5">
-        <v>671.2370037820182</v>
+        <v>667.2799506209222</v>
       </c>
       <c r="O5">
-        <v>201.3711011346055</v>
+        <v>200.1839851862767</v>
       </c>
       <c r="P5">
-        <v>469.8659026474127</v>
+        <v>467.0959654346456</v>
       </c>
       <c r="Q5">
-        <v>547.1659026474128</v>
+        <v>544.3959654346456</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09330567542168745</v>
+        <v>0.09365521684444206</v>
       </c>
       <c r="T5">
-        <v>0.6912654612905703</v>
+        <v>0.6963517148949199</v>
       </c>
       <c r="U5">
         <v>0.06915748822216712</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.54350821644512</v>
+        <v>43.15763116233384</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09184541784088505</v>
+        <v>0.09173202327006776</v>
       </c>
       <c r="C6">
-        <v>5388.797358771387</v>
+        <v>5338.975669418313</v>
       </c>
       <c r="D6">
-        <v>4762.869358771387</v>
+        <v>4770.265669418313</v>
       </c>
       <c r="E6">
-        <v>-1244.228</v>
+        <v>-1187.01</v>
       </c>
       <c r="F6">
-        <v>228.872</v>
+        <v>286.09</v>
       </c>
       <c r="G6">
         <v>854.8</v>
@@ -1913,28 +1913,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M6">
-        <v>15.82821264438383</v>
+        <v>19.78526580547979</v>
       </c>
       <c r="N6">
-        <v>667.2799506209222</v>
+        <v>663.3228974598263</v>
       </c>
       <c r="O6">
-        <v>200.1839851862767</v>
+        <v>198.9968692379479</v>
       </c>
       <c r="P6">
-        <v>467.0959654346456</v>
+        <v>464.3260282218785</v>
       </c>
       <c r="Q6">
-        <v>544.3959654346456</v>
+        <v>541.6260282218785</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09365521684444206</v>
+        <v>0.09401211703399148</v>
       </c>
       <c r="T6">
-        <v>0.6963517148949199</v>
+        <v>0.7015450475225189</v>
       </c>
       <c r="U6">
         <v>0.06915748822216712</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.15763116233384</v>
+        <v>34.52610492986707</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09173202327006776</v>
+        <v>0.09161862869925044</v>
       </c>
       <c r="C7">
-        <v>5338.975669418313</v>
+        <v>5289.17698741304</v>
       </c>
       <c r="D7">
-        <v>4770.265669418313</v>
+        <v>4777.68498741304</v>
       </c>
       <c r="E7">
-        <v>-1187.01</v>
+        <v>-1129.792</v>
       </c>
       <c r="F7">
-        <v>286.09</v>
+        <v>343.308</v>
       </c>
       <c r="G7">
         <v>854.8</v>
@@ -1995,28 +1995,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M7">
-        <v>19.78526580547979</v>
+        <v>23.74231896657575</v>
       </c>
       <c r="N7">
-        <v>663.3228974598263</v>
+        <v>659.3658442987303</v>
       </c>
       <c r="O7">
-        <v>198.9968692379479</v>
+        <v>197.8097532896191</v>
       </c>
       <c r="P7">
-        <v>464.3260282218785</v>
+        <v>461.5560910091112</v>
       </c>
       <c r="Q7">
-        <v>541.6260282218785</v>
+        <v>538.8560910091113</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09401211703399148</v>
+        <v>0.09437661084459514</v>
       </c>
       <c r="T7">
-        <v>0.7015450475225189</v>
+        <v>0.706848876589003</v>
       </c>
       <c r="U7">
         <v>0.06915748822216712</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.52610492986707</v>
+        <v>28.77175410822255</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09161862869925044</v>
+        <v>0.09150523412843317</v>
       </c>
       <c r="C8">
-        <v>5289.17698741304</v>
+        <v>5239.401420274567</v>
       </c>
       <c r="D8">
-        <v>4777.68498741304</v>
+        <v>4785.127420274567</v>
       </c>
       <c r="E8">
-        <v>-1129.792</v>
+        <v>-1072.574</v>
       </c>
       <c r="F8">
-        <v>343.3079999999999</v>
+        <v>400.5259999999999</v>
       </c>
       <c r="G8">
         <v>854.8</v>
@@ -2077,28 +2077,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M8">
-        <v>23.74231896657574</v>
+        <v>27.6993721276717</v>
       </c>
       <c r="N8">
-        <v>659.3658442987303</v>
+        <v>655.4087911376344</v>
       </c>
       <c r="O8">
-        <v>197.8097532896191</v>
+        <v>196.6226373412903</v>
       </c>
       <c r="P8">
-        <v>461.5560910091112</v>
+        <v>458.786153796344</v>
       </c>
       <c r="Q8">
-        <v>538.8560910091113</v>
+        <v>536.0861537963441</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09437661084459514</v>
+        <v>0.09474894323177095</v>
       </c>
       <c r="T8">
-        <v>0.706848876589003</v>
+        <v>0.7122667664956266</v>
       </c>
       <c r="U8">
         <v>0.06915748822216712</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.77175410822256</v>
+        <v>24.66150352133362</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09150523412843316</v>
+        <v>0.09139183955761587</v>
       </c>
       <c r="C9">
-        <v>5239.401420274568</v>
+        <v>5189.649076192898</v>
       </c>
       <c r="D9">
-        <v>4785.127420274568</v>
+        <v>4792.593076192898</v>
       </c>
       <c r="E9">
-        <v>-1072.574</v>
+        <v>-1015.356</v>
       </c>
       <c r="F9">
-        <v>400.526</v>
+        <v>457.744</v>
       </c>
       <c r="G9">
         <v>854.8</v>
@@ -2159,28 +2159,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M9">
-        <v>27.69937212767171</v>
+        <v>31.65642528876766</v>
       </c>
       <c r="N9">
-        <v>655.4087911376344</v>
+        <v>651.4517379765384</v>
       </c>
       <c r="O9">
-        <v>196.6226373412903</v>
+        <v>195.4355213929615</v>
       </c>
       <c r="P9">
-        <v>458.786153796344</v>
+        <v>456.0162165835769</v>
       </c>
       <c r="Q9">
-        <v>536.0861537963441</v>
+        <v>533.316216583577</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09474894323177095</v>
+        <v>0.09512936980127665</v>
       </c>
       <c r="T9">
-        <v>0.7122667664956266</v>
+        <v>0.7178024366176116</v>
       </c>
       <c r="U9">
         <v>0.06915748822216712</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.66150352133362</v>
+        <v>21.57881558116692</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09139183955761587</v>
+        <v>0.09127844498679859</v>
       </c>
       <c r="C10">
-        <v>5189.649076192898</v>
+        <v>5139.920064034262</v>
       </c>
       <c r="D10">
-        <v>4792.593076192898</v>
+        <v>4800.082064034262</v>
       </c>
       <c r="E10">
-        <v>-1015.356</v>
+        <v>-958.138</v>
       </c>
       <c r="F10">
-        <v>457.744</v>
+        <v>514.9619999999999</v>
       </c>
       <c r="G10">
         <v>854.8</v>
@@ -2241,28 +2241,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M10">
-        <v>31.65642528876766</v>
+        <v>35.61347844986361</v>
       </c>
       <c r="N10">
-        <v>651.4517379765384</v>
+        <v>647.4946848154425</v>
       </c>
       <c r="O10">
-        <v>195.4355213929615</v>
+        <v>194.2484054446327</v>
       </c>
       <c r="P10">
-        <v>456.0162165835769</v>
+        <v>453.2462793708098</v>
       </c>
       <c r="Q10">
-        <v>533.316216583577</v>
+        <v>530.5462793708098</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09512936980127665</v>
+        <v>0.09551815739428797</v>
       </c>
       <c r="T10">
-        <v>0.7178024366176116</v>
+        <v>0.7234597698192005</v>
       </c>
       <c r="U10">
         <v>0.06915748822216712</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.57881558116692</v>
+        <v>19.18116940548171</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09127844498679859</v>
+        <v>0.09116505041598129</v>
       </c>
       <c r="C11">
-        <v>5139.920064034262</v>
+        <v>5090.214493346431</v>
       </c>
       <c r="D11">
-        <v>4800.082064034262</v>
+        <v>4807.594493346432</v>
       </c>
       <c r="E11">
-        <v>-958.138</v>
+        <v>-900.9200000000001</v>
       </c>
       <c r="F11">
-        <v>514.9619999999999</v>
+        <v>572.1799999999998</v>
       </c>
       <c r="G11">
         <v>854.8</v>
@@ -2323,28 +2323,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M11">
-        <v>35.61347844986361</v>
+        <v>39.57053161095957</v>
       </c>
       <c r="N11">
-        <v>647.4946848154425</v>
+        <v>643.5376316543465</v>
       </c>
       <c r="O11">
-        <v>194.2484054446327</v>
+        <v>193.0612894963039</v>
       </c>
       <c r="P11">
-        <v>453.2462793708098</v>
+        <v>450.4763421580425</v>
       </c>
       <c r="Q11">
-        <v>530.5462793708098</v>
+        <v>527.7763421580426</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09551815739428797</v>
+        <v>0.09591558471158843</v>
       </c>
       <c r="T11">
-        <v>0.7234597698192005</v>
+        <v>0.7292428215363803</v>
       </c>
       <c r="U11">
         <v>0.06915748822216712</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.18116940548171</v>
+        <v>17.26305246493354</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09116505041598129</v>
+        <v>0.091051655845164</v>
       </c>
       <c r="C12">
-        <v>5090.214493346431</v>
+        <v>5040.53247436404</v>
       </c>
       <c r="D12">
-        <v>4807.594493346432</v>
+        <v>4815.13047436404</v>
       </c>
       <c r="E12">
-        <v>-900.92</v>
+        <v>-843.702</v>
       </c>
       <c r="F12">
-        <v>572.1799999999999</v>
+        <v>629.3979999999999</v>
       </c>
       <c r="G12">
         <v>854.8</v>
@@ -2405,28 +2405,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M12">
-        <v>39.57053161095958</v>
+        <v>43.52758477205553</v>
       </c>
       <c r="N12">
-        <v>643.5376316543465</v>
+        <v>639.5805784932505</v>
       </c>
       <c r="O12">
-        <v>193.0612894963039</v>
+        <v>191.8741735479751</v>
       </c>
       <c r="P12">
-        <v>450.4763421580425</v>
+        <v>447.7064049452754</v>
       </c>
       <c r="Q12">
-        <v>527.7763421580426</v>
+        <v>525.0064049452754</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09591558471158843</v>
+        <v>0.09632194297983948</v>
       </c>
       <c r="T12">
-        <v>0.7292428215363803</v>
+        <v>0.7351558294719238</v>
       </c>
       <c r="U12">
         <v>0.06915748822216712</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.26305246493353</v>
+        <v>15.69368405903049</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.091051655845164</v>
+        <v>0.0909382612743467</v>
       </c>
       <c r="C13">
-        <v>5040.53247436404</v>
+        <v>4990.874118013992</v>
       </c>
       <c r="D13">
-        <v>4815.13047436404</v>
+        <v>4822.690118013992</v>
       </c>
       <c r="E13">
-        <v>-843.702</v>
+        <v>-786.484</v>
       </c>
       <c r="F13">
-        <v>629.3979999999999</v>
+        <v>686.6159999999999</v>
       </c>
       <c r="G13">
         <v>854.8</v>
@@ -2487,28 +2487,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M13">
-        <v>43.52758477205553</v>
+        <v>47.48463793315149</v>
       </c>
       <c r="N13">
-        <v>639.5805784932505</v>
+        <v>635.6235253321546</v>
       </c>
       <c r="O13">
-        <v>191.8741735479751</v>
+        <v>190.6870575996464</v>
       </c>
       <c r="P13">
-        <v>447.7064049452754</v>
+        <v>444.9364677325082</v>
       </c>
       <c r="Q13">
-        <v>525.0064049452754</v>
+        <v>522.2364677325083</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09632194297983948</v>
+        <v>0.09673753666327803</v>
       </c>
       <c r="T13">
-        <v>0.7351558294719238</v>
+        <v>0.7412032239514569</v>
       </c>
       <c r="U13">
         <v>0.06915748822216712</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.69368405903049</v>
+        <v>14.38587705411128</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0909382612743467</v>
+        <v>0.09082486670352941</v>
       </c>
       <c r="C14">
-        <v>4990.874118013992</v>
+        <v>4941.239535920892</v>
       </c>
       <c r="D14">
-        <v>4822.690118013992</v>
+        <v>4830.273535920892</v>
       </c>
       <c r="E14">
-        <v>-786.484</v>
+        <v>-729.266</v>
       </c>
       <c r="F14">
-        <v>686.6159999999999</v>
+        <v>743.8339999999999</v>
       </c>
       <c r="G14">
         <v>854.8</v>
@@ -2569,28 +2569,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M14">
-        <v>47.48463793315149</v>
+        <v>51.44169109424745</v>
       </c>
       <c r="N14">
-        <v>635.6235253321546</v>
+        <v>631.6664721710587</v>
       </c>
       <c r="O14">
-        <v>190.6870575996464</v>
+        <v>189.4999416513176</v>
       </c>
       <c r="P14">
-        <v>444.9364677325082</v>
+        <v>442.1665305197411</v>
       </c>
       <c r="Q14">
-        <v>522.2364677325083</v>
+        <v>519.4665305197411</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09673753666327803</v>
+        <v>0.09716268422449678</v>
       </c>
       <c r="T14">
-        <v>0.7412032239514569</v>
+        <v>0.7473896389937378</v>
       </c>
       <c r="U14">
         <v>0.06915748822216712</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.38587705411128</v>
+        <v>13.27927112687195</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09082486670352941</v>
+        <v>0.09085847213271211</v>
       </c>
       <c r="C15">
-        <v>4941.239535920892</v>
+        <v>4881.77164115601</v>
       </c>
       <c r="D15">
-        <v>4830.273535920892</v>
+        <v>4828.02364115601</v>
       </c>
       <c r="E15">
-        <v>-729.266</v>
+        <v>-672.0479999999999</v>
       </c>
       <c r="F15">
-        <v>743.8339999999999</v>
+        <v>801.052</v>
       </c>
       <c r="G15">
         <v>854.8</v>
@@ -2651,45 +2651,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M15">
-        <v>51.44169109424745</v>
+        <v>56.60032225534341</v>
       </c>
       <c r="N15">
-        <v>631.6664721710587</v>
+        <v>626.5078410099627</v>
       </c>
       <c r="O15">
-        <v>189.4999416513176</v>
+        <v>187.9523523029888</v>
       </c>
       <c r="P15">
-        <v>442.1665305197411</v>
+        <v>438.5554887069739</v>
       </c>
       <c r="Q15">
-        <v>519.4665305197411</v>
+        <v>515.855488706974</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09716268422449678</v>
+        <v>0.09759771893830202</v>
       </c>
       <c r="T15">
-        <v>0.7473896389937378</v>
+        <v>0.7537199241532812</v>
       </c>
       <c r="U15">
-        <v>0.06915748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.04841024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.27927112687195</v>
+        <v>12.06898010551197</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09085847213271211</v>
+        <v>0.09075557756189483</v>
       </c>
       <c r="C16">
-        <v>4881.77164115601</v>
+        <v>4831.449092600275</v>
       </c>
       <c r="D16">
-        <v>4828.02364115601</v>
+        <v>4834.919092600275</v>
       </c>
       <c r="E16">
-        <v>-672.0479999999999</v>
+        <v>-614.8299999999999</v>
       </c>
       <c r="F16">
-        <v>801.052</v>
+        <v>858.27</v>
       </c>
       <c r="G16">
         <v>854.8</v>
@@ -2733,28 +2733,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M16">
-        <v>56.60032225534341</v>
+        <v>60.64320241643937</v>
       </c>
       <c r="N16">
-        <v>626.5078410099627</v>
+        <v>622.4649608488667</v>
       </c>
       <c r="O16">
-        <v>187.9523523029888</v>
+        <v>186.73948825466</v>
       </c>
       <c r="P16">
-        <v>438.5554887069739</v>
+        <v>435.7254725942067</v>
       </c>
       <c r="Q16">
-        <v>515.855488706974</v>
+        <v>513.0254725942068</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09759771893830202</v>
+        <v>0.09804298976302034</v>
       </c>
       <c r="T16">
-        <v>0.7537199241532812</v>
+        <v>0.7601991571989314</v>
       </c>
       <c r="U16">
         <v>0.07065748822216711</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.06898010551197</v>
+        <v>11.26438143181117</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09075557756189483</v>
+        <v>0.09065268299107752</v>
       </c>
       <c r="C17">
-        <v>4831.449092600275</v>
+        <v>4781.146268577367</v>
       </c>
       <c r="D17">
-        <v>4834.919092600275</v>
+        <v>4841.834268577367</v>
       </c>
       <c r="E17">
-        <v>-614.83</v>
+        <v>-557.612</v>
       </c>
       <c r="F17">
-        <v>858.2699999999999</v>
+        <v>915.4879999999999</v>
       </c>
       <c r="G17">
         <v>854.8</v>
@@ -2815,28 +2815,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M17">
-        <v>60.64320241643936</v>
+        <v>64.68608257753532</v>
       </c>
       <c r="N17">
-        <v>622.4649608488667</v>
+        <v>618.4220806877707</v>
       </c>
       <c r="O17">
-        <v>186.73948825466</v>
+        <v>185.5266242063312</v>
       </c>
       <c r="P17">
-        <v>435.7254725942067</v>
+        <v>432.8954564814395</v>
       </c>
       <c r="Q17">
-        <v>513.0254725942068</v>
+        <v>510.1954564814396</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09804298976302034</v>
+        <v>0.09849886227404145</v>
       </c>
       <c r="T17">
-        <v>0.7601991571989314</v>
+        <v>0.7668326576980494</v>
       </c>
       <c r="U17">
         <v>0.07065748822216711</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.26438143181117</v>
+        <v>10.56035759232298</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09065268299107752</v>
+        <v>0.09054978842026024</v>
       </c>
       <c r="C18">
-        <v>4781.146268577367</v>
+        <v>4730.863253841947</v>
       </c>
       <c r="D18">
-        <v>4841.834268577367</v>
+        <v>4848.769253841947</v>
       </c>
       <c r="E18">
-        <v>-557.612</v>
+        <v>-500.394</v>
       </c>
       <c r="F18">
-        <v>915.4879999999999</v>
+        <v>972.7059999999999</v>
       </c>
       <c r="G18">
         <v>854.8</v>
@@ -2897,28 +2897,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M18">
-        <v>64.68608257753532</v>
+        <v>68.72896273863127</v>
       </c>
       <c r="N18">
-        <v>618.4220806877707</v>
+        <v>614.3792005266748</v>
       </c>
       <c r="O18">
-        <v>185.5266242063312</v>
+        <v>184.3137601580025</v>
       </c>
       <c r="P18">
-        <v>432.8954564814395</v>
+        <v>430.0654403686724</v>
       </c>
       <c r="Q18">
-        <v>510.1954564814396</v>
+        <v>507.3654403686725</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09849886227404145</v>
+        <v>0.09896571966484621</v>
       </c>
       <c r="T18">
-        <v>0.7668326576980494</v>
+        <v>0.7736260015826886</v>
       </c>
       <c r="U18">
         <v>0.07065748822216711</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.56035759232298</v>
+        <v>9.939160086892214</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09054978842026024</v>
+        <v>0.09066109384944293</v>
       </c>
       <c r="C19">
-        <v>4730.863253841947</v>
+        <v>4666.144262579351</v>
       </c>
       <c r="D19">
-        <v>4848.769253841947</v>
+        <v>4841.26826257935</v>
       </c>
       <c r="E19">
-        <v>-500.394</v>
+        <v>-443.1759999999999</v>
       </c>
       <c r="F19">
-        <v>972.7059999999999</v>
+        <v>1029.924</v>
       </c>
       <c r="G19">
         <v>854.8</v>
@@ -2979,45 +2979,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M19">
-        <v>68.72896273863127</v>
+        <v>74.52271369972725</v>
       </c>
       <c r="N19">
-        <v>614.3792005266748</v>
+        <v>608.5854495655789</v>
       </c>
       <c r="O19">
-        <v>184.3137601580025</v>
+        <v>182.5756348696736</v>
       </c>
       <c r="P19">
-        <v>430.0654403686724</v>
+        <v>426.0098146959052</v>
       </c>
       <c r="Q19">
-        <v>507.3654403686725</v>
+        <v>503.3098146959053</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09896571966484621</v>
+        <v>0.09944396382128035</v>
       </c>
       <c r="T19">
-        <v>0.7736260015826886</v>
+        <v>0.7805850367815869</v>
       </c>
       <c r="U19">
-        <v>0.07065748822216711</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.04946024175551697</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.939160086892214</v>
+        <v>9.166442408655957</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09066109384944294</v>
+        <v>0.09057009927862565</v>
       </c>
       <c r="C20">
-        <v>4666.14426257935</v>
+        <v>4615.056750222102</v>
       </c>
       <c r="D20">
-        <v>4841.26826257935</v>
+        <v>4847.398750222102</v>
       </c>
       <c r="E20">
-        <v>-443.1760000000002</v>
+        <v>-385.9580000000001</v>
       </c>
       <c r="F20">
-        <v>1029.924</v>
+        <v>1087.142</v>
       </c>
       <c r="G20">
         <v>854.8</v>
@@ -3061,28 +3061,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M20">
-        <v>74.52271369972722</v>
+        <v>78.66286446082319</v>
       </c>
       <c r="N20">
-        <v>608.5854495655789</v>
+        <v>604.4452988044829</v>
       </c>
       <c r="O20">
-        <v>182.5756348696736</v>
+        <v>181.3335896413449</v>
       </c>
       <c r="P20">
-        <v>426.0098146959052</v>
+        <v>423.1117091631381</v>
       </c>
       <c r="Q20">
-        <v>503.3098146959053</v>
+        <v>500.4117091631381</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09944396382128035</v>
+        <v>0.09993401647540423</v>
       </c>
       <c r="T20">
-        <v>0.7805850367815869</v>
+        <v>0.7877159000100877</v>
       </c>
       <c r="U20">
         <v>0.07235748822216712</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.166442408655961</v>
+        <v>8.683998071358278</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09057009927862565</v>
+        <v>0.09047910470780837</v>
       </c>
       <c r="C21">
-        <v>4615.056750222102</v>
+        <v>4563.984783597151</v>
       </c>
       <c r="D21">
-        <v>4847.398750222102</v>
+        <v>4853.544783597151</v>
       </c>
       <c r="E21">
-        <v>-385.9580000000001</v>
+        <v>-328.74</v>
       </c>
       <c r="F21">
-        <v>1087.142</v>
+        <v>1144.36</v>
       </c>
       <c r="G21">
         <v>854.8</v>
@@ -3143,28 +3143,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M21">
-        <v>78.66286446082319</v>
+        <v>82.80301522191915</v>
       </c>
       <c r="N21">
-        <v>604.4452988044829</v>
+        <v>600.3051480433869</v>
       </c>
       <c r="O21">
-        <v>181.3335896413449</v>
+        <v>180.0915444130161</v>
       </c>
       <c r="P21">
-        <v>423.1117091631381</v>
+        <v>420.2136036303708</v>
       </c>
       <c r="Q21">
-        <v>500.4117091631381</v>
+        <v>497.5136036303709</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09993401647540423</v>
+        <v>0.1004363204458812</v>
       </c>
       <c r="T21">
-        <v>0.7877159000100877</v>
+        <v>0.7950250348193013</v>
       </c>
       <c r="U21">
         <v>0.07235748822216712</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.683998071358278</v>
+        <v>8.249798167790361</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09047910470780837</v>
+        <v>0.09038811013699108</v>
       </c>
       <c r="C22">
-        <v>4563.984783597151</v>
+        <v>4512.928421911029</v>
       </c>
       <c r="D22">
-        <v>4853.544783597151</v>
+        <v>4859.706421911029</v>
       </c>
       <c r="E22">
-        <v>-328.74</v>
+        <v>-271.5219999999999</v>
       </c>
       <c r="F22">
-        <v>1144.36</v>
+        <v>1201.578</v>
       </c>
       <c r="G22">
         <v>854.8</v>
@@ -3225,28 +3225,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M22">
-        <v>82.80301522191915</v>
+        <v>86.94316598301512</v>
       </c>
       <c r="N22">
-        <v>600.3051480433869</v>
+        <v>596.164997282291</v>
       </c>
       <c r="O22">
-        <v>180.0915444130161</v>
+        <v>178.8494991846873</v>
       </c>
       <c r="P22">
-        <v>420.2136036303708</v>
+        <v>417.3154980976037</v>
       </c>
       <c r="Q22">
-        <v>497.5136036303709</v>
+        <v>494.6154980976038</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1004363204458812</v>
+        <v>0.1009513409725728</v>
       </c>
       <c r="T22">
-        <v>0.7950250348193013</v>
+        <v>0.8025192110160898</v>
       </c>
       <c r="U22">
         <v>0.07235748822216712</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.249798167790361</v>
+        <v>7.85695063599082</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09038811013699107</v>
+        <v>0.09042031556617378</v>
       </c>
       <c r="C23">
-        <v>4512.92842191103</v>
+        <v>4453.527864312911</v>
       </c>
       <c r="D23">
-        <v>4859.706421911029</v>
+        <v>4857.523864312911</v>
       </c>
       <c r="E23">
-        <v>-271.5220000000002</v>
+        <v>-214.3040000000001</v>
       </c>
       <c r="F23">
-        <v>1201.578</v>
+        <v>1258.796</v>
       </c>
       <c r="G23">
         <v>854.8</v>
@@ -3307,45 +3307,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M23">
-        <v>86.94316598301511</v>
+        <v>92.09035354411105</v>
       </c>
       <c r="N23">
-        <v>596.164997282291</v>
+        <v>591.017809721195</v>
       </c>
       <c r="O23">
-        <v>178.8494991846873</v>
+        <v>177.3053429163585</v>
       </c>
       <c r="P23">
-        <v>417.3154980976037</v>
+        <v>413.7124668048365</v>
       </c>
       <c r="Q23">
-        <v>494.6154980976038</v>
+        <v>491.0124668048365</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1009513409725728</v>
+        <v>0.1014795671537949</v>
       </c>
       <c r="T23">
-        <v>0.8025192110160897</v>
+        <v>0.8102055455768984</v>
       </c>
       <c r="U23">
-        <v>0.07235748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05065024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.856950635990821</v>
+        <v>7.417803678406978</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09042031556617378</v>
+        <v>0.09033492099535649</v>
       </c>
       <c r="C24">
-        <v>4453.527864312911</v>
+        <v>4402.101340554482</v>
       </c>
       <c r="D24">
-        <v>4857.523864312911</v>
+        <v>4863.315340554482</v>
       </c>
       <c r="E24">
-        <v>-214.3040000000001</v>
+        <v>-157.086</v>
       </c>
       <c r="F24">
-        <v>1258.796</v>
+        <v>1316.014</v>
       </c>
       <c r="G24">
         <v>854.8</v>
@@ -3389,28 +3389,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M24">
-        <v>92.09035354411105</v>
+        <v>96.27627870520702</v>
       </c>
       <c r="N24">
-        <v>591.017809721195</v>
+        <v>586.8318845600991</v>
       </c>
       <c r="O24">
-        <v>177.3053429163585</v>
+        <v>176.0495653680297</v>
       </c>
       <c r="P24">
-        <v>413.7124668048365</v>
+        <v>410.7823191920694</v>
       </c>
       <c r="Q24">
-        <v>491.0124668048365</v>
+        <v>488.0823191920695</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1014795671537949</v>
+        <v>0.1020215134955683</v>
       </c>
       <c r="T24">
-        <v>0.8102055455768984</v>
+        <v>0.8180915251912345</v>
       </c>
       <c r="U24">
         <v>0.07315748822216711</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.417803678406978</v>
+        <v>7.095290474997979</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09033492099535649</v>
+        <v>0.09024952642453919</v>
       </c>
       <c r="C25">
-        <v>4402.101340554482</v>
+        <v>4350.688643278791</v>
       </c>
       <c r="D25">
-        <v>4863.315340554482</v>
+        <v>4869.12064327879</v>
       </c>
       <c r="E25">
-        <v>-157.086</v>
+        <v>-99.86799999999994</v>
       </c>
       <c r="F25">
-        <v>1316.014</v>
+        <v>1373.232</v>
       </c>
       <c r="G25">
         <v>854.8</v>
@@ -3471,28 +3471,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M25">
-        <v>96.27627870520702</v>
+        <v>100.462203866303</v>
       </c>
       <c r="N25">
-        <v>586.8318845600991</v>
+        <v>582.6459593990031</v>
       </c>
       <c r="O25">
-        <v>176.0495653680297</v>
+        <v>174.7937878197009</v>
       </c>
       <c r="P25">
-        <v>410.7823191920694</v>
+        <v>407.8521715793022</v>
       </c>
       <c r="Q25">
-        <v>488.0823191920695</v>
+        <v>485.1521715793023</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1020215134955683</v>
+        <v>0.1025777215831778</v>
       </c>
       <c r="T25">
-        <v>0.8180915251912345</v>
+        <v>0.8261850305848955</v>
       </c>
       <c r="U25">
         <v>0.07315748822216711</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.095290474997979</v>
+        <v>6.799653371873062</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09024952642453919</v>
+        <v>0.09016413185372191</v>
       </c>
       <c r="C26">
-        <v>4350.688643278791</v>
+        <v>4299.289822058716</v>
       </c>
       <c r="D26">
-        <v>4869.12064327879</v>
+        <v>4874.939822058715</v>
       </c>
       <c r="E26">
-        <v>-99.86800000000017</v>
+        <v>-42.65000000000009</v>
       </c>
       <c r="F26">
-        <v>1373.232</v>
+        <v>1430.45</v>
       </c>
       <c r="G26">
         <v>854.8</v>
@@ -3553,28 +3553,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M26">
-        <v>100.462203866303</v>
+        <v>104.6481290273989</v>
       </c>
       <c r="N26">
-        <v>582.6459593990031</v>
+        <v>578.4600342379072</v>
       </c>
       <c r="O26">
-        <v>174.7937878197009</v>
+        <v>173.5380102713721</v>
       </c>
       <c r="P26">
-        <v>407.8521715793022</v>
+        <v>404.922023966535</v>
       </c>
       <c r="Q26">
-        <v>485.1521715793023</v>
+        <v>482.2220239665351</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1025777215831778</v>
+        <v>0.1031487618864569</v>
       </c>
       <c r="T26">
-        <v>0.8261850305848955</v>
+        <v>0.8344943627890539</v>
       </c>
       <c r="U26">
         <v>0.07315748822216711</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.799653371873063</v>
+        <v>6.52766723699814</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09016413185372191</v>
+        <v>0.09007873728290461</v>
       </c>
       <c r="C27">
-        <v>4299.289822058716</v>
+        <v>4247.904926704401</v>
       </c>
       <c r="D27">
-        <v>4874.939822058715</v>
+        <v>4880.772926704401</v>
       </c>
       <c r="E27">
-        <v>-42.65000000000009</v>
+        <v>14.56799999999998</v>
       </c>
       <c r="F27">
-        <v>1430.45</v>
+        <v>1487.668</v>
       </c>
       <c r="G27">
         <v>854.8</v>
@@ -3635,28 +3635,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M27">
-        <v>104.6481290273989</v>
+        <v>108.8340541884949</v>
       </c>
       <c r="N27">
-        <v>578.4600342379072</v>
+        <v>574.2741090768112</v>
       </c>
       <c r="O27">
-        <v>173.5380102713721</v>
+        <v>172.2822327230434</v>
       </c>
       <c r="P27">
-        <v>404.922023966535</v>
+        <v>401.9918763537679</v>
       </c>
       <c r="Q27">
-        <v>482.2220239665351</v>
+        <v>479.2918763537679</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1031487618864569</v>
+        <v>0.1037352357114462</v>
       </c>
       <c r="T27">
-        <v>0.8344943627890539</v>
+        <v>0.8430282715392705</v>
       </c>
       <c r="U27">
         <v>0.07315748822216711</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.52766723699814</v>
+        <v>6.276603112498212</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09007873728290461</v>
+        <v>0.0901823427120873</v>
       </c>
       <c r="C28">
-        <v>4247.904926704401</v>
+        <v>4183.611683888599</v>
       </c>
       <c r="D28">
-        <v>4880.772926704401</v>
+        <v>4873.697683888598</v>
       </c>
       <c r="E28">
-        <v>14.56799999999998</v>
+        <v>71.78600000000006</v>
       </c>
       <c r="F28">
-        <v>1487.668</v>
+        <v>1544.886</v>
       </c>
       <c r="G28">
         <v>854.8</v>
@@ -3717,45 +3717,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M28">
-        <v>108.8340541884949</v>
+        <v>114.5648653495909</v>
       </c>
       <c r="N28">
-        <v>574.2741090768112</v>
+        <v>568.5432979157152</v>
       </c>
       <c r="O28">
-        <v>172.2822327230434</v>
+        <v>170.5629893747146</v>
       </c>
       <c r="P28">
-        <v>401.9918763537679</v>
+        <v>397.9803085410007</v>
       </c>
       <c r="Q28">
-        <v>479.2918763537679</v>
+        <v>475.2803085410007</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1037352357114462</v>
+        <v>0.1043377773124626</v>
       </c>
       <c r="T28">
-        <v>0.8430282715392705</v>
+        <v>0.8517959860086715</v>
       </c>
       <c r="U28">
-        <v>0.07315748822216711</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.05121024175551697</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.276603112498212</v>
+        <v>5.962632271079134</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0901823427120873</v>
+        <v>0.09010394814127003</v>
       </c>
       <c r="C29">
-        <v>4183.611683888599</v>
+        <v>4131.745379847932</v>
       </c>
       <c r="D29">
-        <v>4873.697683888598</v>
+        <v>4879.049379847932</v>
       </c>
       <c r="E29">
-        <v>71.78600000000006</v>
+        <v>129.0040000000001</v>
       </c>
       <c r="F29">
-        <v>1544.886</v>
+        <v>1602.104</v>
       </c>
       <c r="G29">
         <v>854.8</v>
@@ -3799,28 +3799,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M29">
-        <v>114.5648653495909</v>
+        <v>118.8080085106868</v>
       </c>
       <c r="N29">
-        <v>568.5432979157152</v>
+        <v>564.3001547546193</v>
       </c>
       <c r="O29">
-        <v>170.5629893747146</v>
+        <v>169.2900464263858</v>
       </c>
       <c r="P29">
-        <v>397.9803085410007</v>
+        <v>395.0101083282335</v>
       </c>
       <c r="Q29">
-        <v>475.2803085410007</v>
+        <v>472.3101083282336</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1043377773124626</v>
+        <v>0.104957056180174</v>
       </c>
       <c r="T29">
-        <v>0.8517959860086715</v>
+        <v>0.8608072481022222</v>
       </c>
       <c r="U29">
         <v>0.07415748822216711</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.962632271079134</v>
+        <v>5.749681118540593</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09010394814127003</v>
+        <v>0.09002555357045272</v>
       </c>
       <c r="C30">
-        <v>4131.745379847932</v>
+        <v>4079.890841877187</v>
       </c>
       <c r="D30">
-        <v>4879.049379847932</v>
+        <v>4884.412841877187</v>
       </c>
       <c r="E30">
-        <v>129.0040000000001</v>
+        <v>186.222</v>
       </c>
       <c r="F30">
-        <v>1602.104</v>
+        <v>1659.322</v>
       </c>
       <c r="G30">
         <v>854.8</v>
@@ -3881,28 +3881,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M30">
-        <v>118.8080085106868</v>
+        <v>123.0511516717828</v>
       </c>
       <c r="N30">
-        <v>564.3001547546193</v>
+        <v>560.0570115935233</v>
       </c>
       <c r="O30">
-        <v>169.2900464263858</v>
+        <v>168.017103478057</v>
       </c>
       <c r="P30">
-        <v>395.0101083282335</v>
+        <v>392.0399081154663</v>
       </c>
       <c r="Q30">
-        <v>472.3101083282336</v>
+        <v>469.3399081154664</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.104957056180174</v>
+        <v>0.1055937795230321</v>
       </c>
       <c r="T30">
-        <v>0.8608072481022222</v>
+        <v>0.8700723485646055</v>
       </c>
       <c r="U30">
         <v>0.07415748822216711</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.749681118540593</v>
+        <v>5.551416252384021</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09002555357045272</v>
+        <v>0.08994715899963543</v>
       </c>
       <c r="C31">
-        <v>4079.890841877188</v>
+        <v>4028.048108821828</v>
       </c>
       <c r="D31">
-        <v>4884.412841877187</v>
+        <v>4889.788108821827</v>
       </c>
       <c r="E31">
-        <v>186.2219999999998</v>
+        <v>243.4399999999998</v>
       </c>
       <c r="F31">
-        <v>1659.322</v>
+        <v>1716.54</v>
       </c>
       <c r="G31">
         <v>854.8</v>
@@ -3963,28 +3963,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M31">
-        <v>123.0511516717827</v>
+        <v>127.2942948328787</v>
       </c>
       <c r="N31">
-        <v>560.0570115935234</v>
+        <v>555.8138684324274</v>
       </c>
       <c r="O31">
-        <v>168.017103478057</v>
+        <v>166.7441605297282</v>
       </c>
       <c r="P31">
-        <v>392.0399081154663</v>
+        <v>389.0697079026992</v>
       </c>
       <c r="Q31">
-        <v>469.3399081154664</v>
+        <v>466.3697079026992</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1055937795230321</v>
+        <v>0.1062486949614005</v>
       </c>
       <c r="T31">
-        <v>0.8700723485646055</v>
+        <v>0.8796021661830568</v>
       </c>
       <c r="U31">
         <v>0.07415748822216711</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.551416252384023</v>
+        <v>5.366369043971221</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08994715899963543</v>
+        <v>0.08986876442881814</v>
       </c>
       <c r="C32">
-        <v>4028.048108821828</v>
+        <v>3976.217219698506</v>
       </c>
       <c r="D32">
-        <v>4889.788108821827</v>
+        <v>4895.175219698505</v>
       </c>
       <c r="E32">
-        <v>243.4399999999998</v>
+        <v>300.6579999999999</v>
       </c>
       <c r="F32">
-        <v>1716.54</v>
+        <v>1773.758</v>
       </c>
       <c r="G32">
         <v>854.8</v>
@@ -4045,28 +4045,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M32">
-        <v>127.2942948328787</v>
+        <v>131.5374379939747</v>
       </c>
       <c r="N32">
-        <v>555.8138684324274</v>
+        <v>551.5707252713314</v>
       </c>
       <c r="O32">
-        <v>166.7441605297282</v>
+        <v>165.4712175813994</v>
       </c>
       <c r="P32">
-        <v>389.0697079026992</v>
+        <v>386.099507689932</v>
       </c>
       <c r="Q32">
-        <v>466.3697079026992</v>
+        <v>463.3995076899321</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1062486949614005</v>
+        <v>0.1069225934559535</v>
       </c>
       <c r="T32">
-        <v>0.8796021661830568</v>
+        <v>0.8894082103991443</v>
       </c>
       <c r="U32">
         <v>0.07415748822216711</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.366369043971221</v>
+        <v>5.193260365133439</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08986876442881814</v>
+        <v>0.08979036985800085</v>
       </c>
       <c r="C33">
-        <v>3976.217219698506</v>
+        <v>3924.398213696006</v>
       </c>
       <c r="D33">
-        <v>4895.175219698505</v>
+        <v>4900.574213696005</v>
       </c>
       <c r="E33">
-        <v>300.6579999999999</v>
+        <v>357.876</v>
       </c>
       <c r="F33">
-        <v>1773.758</v>
+        <v>1830.976</v>
       </c>
       <c r="G33">
         <v>854.8</v>
@@ -4127,28 +4127,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M33">
-        <v>131.5374379939747</v>
+        <v>135.7805811550706</v>
       </c>
       <c r="N33">
-        <v>551.5707252713314</v>
+        <v>547.3275821102354</v>
       </c>
       <c r="O33">
-        <v>165.4712175813994</v>
+        <v>164.1982746330706</v>
       </c>
       <c r="P33">
-        <v>386.099507689932</v>
+        <v>383.1293074771648</v>
       </c>
       <c r="Q33">
-        <v>463.3995076899321</v>
+        <v>460.4293074771649</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1069225934559535</v>
+        <v>0.1076163124944639</v>
       </c>
       <c r="T33">
-        <v>0.8894082103991443</v>
+        <v>0.899502667680411</v>
       </c>
       <c r="U33">
         <v>0.07415748822216711</v>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.193260365133439</v>
+        <v>5.030970978723019</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08979036985800085</v>
+        <v>0.08971197528718355</v>
       </c>
       <c r="C34">
-        <v>3924.398213696006</v>
+        <v>3872.591130176187</v>
       </c>
       <c r="D34">
-        <v>4900.574213696005</v>
+        <v>4905.985130176186</v>
       </c>
       <c r="E34">
-        <v>357.876</v>
+        <v>415.0940000000001</v>
       </c>
       <c r="F34">
-        <v>1830.976</v>
+        <v>1888.194</v>
       </c>
       <c r="G34">
         <v>854.8</v>
@@ -4209,28 +4209,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M34">
-        <v>135.7805811550706</v>
+        <v>140.0237243161666</v>
       </c>
       <c r="N34">
-        <v>547.3275821102354</v>
+        <v>543.0844389491394</v>
       </c>
       <c r="O34">
-        <v>164.1982746330706</v>
+        <v>162.9253316847418</v>
       </c>
       <c r="P34">
-        <v>383.1293074771648</v>
+        <v>380.1591072643976</v>
       </c>
       <c r="Q34">
-        <v>460.4293074771649</v>
+        <v>457.4591072643977</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1076163124944639</v>
+        <v>0.1083307395639746</v>
       </c>
       <c r="T34">
-        <v>0.899502667680411</v>
+        <v>0.9098984520447007</v>
       </c>
       <c r="U34">
         <v>0.07415748822216711</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.030970978723019</v>
+        <v>4.878517312701109</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08971197528718355</v>
+        <v>0.08963358071636625</v>
       </c>
       <c r="C35">
-        <v>3872.591130176187</v>
+        <v>3820.796008674949</v>
       </c>
       <c r="D35">
-        <v>4905.985130176186</v>
+        <v>4911.408008674948</v>
       </c>
       <c r="E35">
-        <v>415.0940000000001</v>
+        <v>472.3119999999999</v>
       </c>
       <c r="F35">
-        <v>1888.194</v>
+        <v>1945.412</v>
       </c>
       <c r="G35">
         <v>854.8</v>
@@ -4291,28 +4291,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M35">
-        <v>140.0237243161666</v>
+        <v>144.2668674772625</v>
       </c>
       <c r="N35">
-        <v>543.0844389491394</v>
+        <v>538.8412957880436</v>
       </c>
       <c r="O35">
-        <v>162.9253316847418</v>
+        <v>161.6523887364131</v>
       </c>
       <c r="P35">
-        <v>380.1591072643976</v>
+        <v>377.1889070516305</v>
       </c>
       <c r="Q35">
-        <v>457.4591072643977</v>
+        <v>454.4889070516306</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1083307395639746</v>
+        <v>0.1090668159386219</v>
       </c>
       <c r="T35">
-        <v>0.9098984520447007</v>
+        <v>0.9206092601776048</v>
       </c>
       <c r="U35">
         <v>0.07415748822216711</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.878517312701109</v>
+        <v>4.735031509386372</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08963358071636625</v>
+        <v>0.08955518614554897</v>
       </c>
       <c r="C36">
-        <v>3820.796008674949</v>
+        <v>3769.012888903185</v>
       </c>
       <c r="D36">
-        <v>4911.408008674948</v>
+        <v>4916.842888903185</v>
       </c>
       <c r="E36">
-        <v>472.3119999999999</v>
+        <v>529.53</v>
       </c>
       <c r="F36">
-        <v>1945.412</v>
+        <v>2002.63</v>
       </c>
       <c r="G36">
         <v>854.8</v>
@@ -4373,28 +4373,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M36">
-        <v>144.2668674772625</v>
+        <v>148.5100106383585</v>
       </c>
       <c r="N36">
-        <v>538.8412957880436</v>
+        <v>534.5981526269476</v>
       </c>
       <c r="O36">
-        <v>161.6523887364131</v>
+        <v>160.3794457880843</v>
       </c>
       <c r="P36">
-        <v>377.1889070516305</v>
+        <v>374.2187068388633</v>
       </c>
       <c r="Q36">
-        <v>454.4889070516306</v>
+        <v>451.5187068388634</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1090668159386219</v>
+        <v>0.1098255408171047</v>
       </c>
       <c r="T36">
-        <v>0.9206092601776048</v>
+        <v>0.9316496316376754</v>
       </c>
       <c r="U36">
         <v>0.07415748822216711</v>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.735031509386372</v>
+        <v>4.599744894832474</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08955518614554897</v>
+        <v>0.09010679157473167</v>
       </c>
       <c r="C37">
-        <v>3769.012888903185</v>
+        <v>3673.807064168356</v>
       </c>
       <c r="D37">
-        <v>4916.842888903185</v>
+        <v>4878.855064168356</v>
       </c>
       <c r="E37">
-        <v>529.53</v>
+        <v>586.748</v>
       </c>
       <c r="F37">
-        <v>2002.63</v>
+        <v>2059.848</v>
       </c>
       <c r="G37">
         <v>854.8</v>
@@ -4455,45 +4455,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M37">
-        <v>148.5100106383585</v>
+        <v>157.9027737994545</v>
       </c>
       <c r="N37">
-        <v>534.5981526269476</v>
+        <v>525.2053894658516</v>
       </c>
       <c r="O37">
-        <v>160.3794457880843</v>
+        <v>157.5616168397555</v>
       </c>
       <c r="P37">
-        <v>374.2187068388633</v>
+        <v>367.6437726260961</v>
       </c>
       <c r="Q37">
-        <v>451.5187068388634</v>
+        <v>444.9437726260962</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1098255408171047</v>
+        <v>0.1106079758480399</v>
       </c>
       <c r="T37">
-        <v>0.9316496316376754</v>
+        <v>0.9430350147058734</v>
       </c>
       <c r="U37">
-        <v>0.07415748822216711</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.05191024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.599744894832474</v>
+        <v>4.326131497429502</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09010679157473167</v>
+        <v>0.09004589700391438</v>
       </c>
       <c r="C38">
-        <v>3673.807064168357</v>
+        <v>3620.753887937826</v>
       </c>
       <c r="D38">
-        <v>4878.855064168356</v>
+        <v>4883.019887937826</v>
       </c>
       <c r="E38">
-        <v>586.7479999999996</v>
+        <v>643.9659999999999</v>
       </c>
       <c r="F38">
-        <v>2059.848</v>
+        <v>2117.066</v>
       </c>
       <c r="G38">
         <v>854.8</v>
@@ -4537,28 +4537,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M38">
-        <v>157.9027737994545</v>
+        <v>162.2889619605504</v>
       </c>
       <c r="N38">
-        <v>525.2053894658516</v>
+        <v>520.8192013047557</v>
       </c>
       <c r="O38">
-        <v>157.5616168397555</v>
+        <v>156.2457603914267</v>
       </c>
       <c r="P38">
-        <v>367.6437726260961</v>
+        <v>364.573440913329</v>
       </c>
       <c r="Q38">
-        <v>444.9437726260962</v>
+        <v>441.873440913329</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1106079758480399</v>
+        <v>0.1114152500863065</v>
       </c>
       <c r="T38">
-        <v>0.9430350147058734</v>
+        <v>0.9547818385063949</v>
       </c>
       <c r="U38">
         <v>0.07665748822216711</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.326131497429503</v>
+        <v>4.209209024526003</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09004589700391438</v>
+        <v>0.08998500243309709</v>
       </c>
       <c r="C39">
-        <v>3620.753887937826</v>
+        <v>3567.707828367504</v>
       </c>
       <c r="D39">
-        <v>4883.019887937826</v>
+        <v>4887.191828367503</v>
       </c>
       <c r="E39">
-        <v>643.9659999999999</v>
+        <v>701.1839999999997</v>
       </c>
       <c r="F39">
-        <v>2117.066</v>
+        <v>2174.284</v>
       </c>
       <c r="G39">
         <v>854.8</v>
@@ -4619,28 +4619,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M39">
-        <v>162.2889619605504</v>
+        <v>166.6751501216464</v>
       </c>
       <c r="N39">
-        <v>520.8192013047557</v>
+        <v>516.4330131436598</v>
       </c>
       <c r="O39">
-        <v>156.2457603914267</v>
+        <v>154.9299039430979</v>
       </c>
       <c r="P39">
-        <v>364.573440913329</v>
+        <v>361.5031092005619</v>
       </c>
       <c r="Q39">
-        <v>441.873440913329</v>
+        <v>438.8031092005619</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1114152500863065</v>
+        <v>0.1122485654290333</v>
       </c>
       <c r="T39">
-        <v>0.9547818385063949</v>
+        <v>0.9669075921069333</v>
       </c>
       <c r="U39">
         <v>0.07665748822216711</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.209209024526003</v>
+        <v>4.098440365985846</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08998500243309709</v>
+        <v>0.0908796078622798</v>
       </c>
       <c r="C40">
-        <v>3567.707828367504</v>
+        <v>3449.907670307575</v>
       </c>
       <c r="D40">
-        <v>4887.191828367503</v>
+        <v>4826.609670307575</v>
       </c>
       <c r="E40">
-        <v>701.1839999999997</v>
+        <v>758.402</v>
       </c>
       <c r="F40">
-        <v>2174.284</v>
+        <v>2231.502</v>
       </c>
       <c r="G40">
         <v>854.8</v>
@@ -4701,45 +4701,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M40">
-        <v>166.6751501216464</v>
+        <v>178.8715952827424</v>
       </c>
       <c r="N40">
-        <v>516.4330131436598</v>
+        <v>504.2365679825637</v>
       </c>
       <c r="O40">
-        <v>154.9299039430979</v>
+        <v>151.2709703947691</v>
       </c>
       <c r="P40">
-        <v>361.5031092005619</v>
+        <v>352.9655975877946</v>
       </c>
       <c r="Q40">
-        <v>438.8031092005619</v>
+        <v>430.2655975877947</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1122485654290333</v>
+        <v>0.1131092025862757</v>
       </c>
       <c r="T40">
-        <v>0.9669075921069333</v>
+        <v>0.9794309113992927</v>
       </c>
       <c r="U40">
-        <v>0.07665748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.05366024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.098440365985846</v>
+        <v>3.81898625204028</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0908796078622798</v>
+        <v>0.09084321329146251</v>
       </c>
       <c r="C41">
-        <v>3449.907670307575</v>
+        <v>3395.124965862043</v>
       </c>
       <c r="D41">
-        <v>4826.609670307575</v>
+        <v>4829.044965862043</v>
       </c>
       <c r="E41">
-        <v>758.402</v>
+        <v>815.6199999999999</v>
       </c>
       <c r="F41">
-        <v>2231.502</v>
+        <v>2288.72</v>
       </c>
       <c r="G41">
         <v>854.8</v>
@@ -4783,28 +4783,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M41">
-        <v>178.8715952827424</v>
+        <v>183.4580464438383</v>
       </c>
       <c r="N41">
-        <v>504.2365679825637</v>
+        <v>499.6501168214678</v>
       </c>
       <c r="O41">
-        <v>151.2709703947691</v>
+        <v>149.8950350464403</v>
       </c>
       <c r="P41">
-        <v>352.9655975877946</v>
+        <v>349.7550817750275</v>
       </c>
       <c r="Q41">
-        <v>430.2655975877947</v>
+        <v>427.0550817750275</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1131092025862757</v>
+        <v>0.1139985276487595</v>
       </c>
       <c r="T41">
-        <v>0.9794309113992927</v>
+        <v>0.9923716746680641</v>
       </c>
       <c r="U41">
         <v>0.08015748822216712</v>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.81898625204028</v>
+        <v>3.723511595739274</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09084321329146251</v>
+        <v>0.09080681872064522</v>
       </c>
       <c r="C42">
-        <v>3395.124965862043</v>
+        <v>3340.344720143738</v>
       </c>
       <c r="D42">
-        <v>4829.044965862043</v>
+        <v>4831.482720143737</v>
       </c>
       <c r="E42">
-        <v>815.6199999999999</v>
+        <v>872.8380000000002</v>
       </c>
       <c r="F42">
-        <v>2288.72</v>
+        <v>2345.938</v>
       </c>
       <c r="G42">
         <v>854.8</v>
@@ -4865,28 +4865,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M42">
-        <v>183.4580464438383</v>
+        <v>188.0444976049343</v>
       </c>
       <c r="N42">
-        <v>499.6501168214678</v>
+        <v>495.0636656603718</v>
       </c>
       <c r="O42">
-        <v>149.8950350464403</v>
+        <v>148.5190996981115</v>
       </c>
       <c r="P42">
-        <v>349.7550817750275</v>
+        <v>346.5445659622603</v>
       </c>
       <c r="Q42">
-        <v>427.0550817750275</v>
+        <v>423.8445659622603</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1139985276487595</v>
+        <v>0.1149179993235309</v>
       </c>
       <c r="T42">
-        <v>0.9923716746680641</v>
+        <v>1.00575110787815</v>
       </c>
       <c r="U42">
         <v>0.08015748822216712</v>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.723511595739274</v>
+        <v>3.632694239745632</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09080681872064522</v>
+        <v>0.09077042414982793</v>
       </c>
       <c r="C43">
-        <v>3340.344720143738</v>
+        <v>3285.566936878115</v>
       </c>
       <c r="D43">
-        <v>4831.482720143737</v>
+        <v>4833.922936878114</v>
       </c>
       <c r="E43">
-        <v>872.8380000000002</v>
+        <v>930.056</v>
       </c>
       <c r="F43">
-        <v>2345.938</v>
+        <v>2403.156</v>
       </c>
       <c r="G43">
         <v>854.8</v>
@@ -4947,28 +4947,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M43">
-        <v>188.0444976049343</v>
+        <v>192.6309487660302</v>
       </c>
       <c r="N43">
-        <v>495.0636656603718</v>
+        <v>490.4772144992759</v>
       </c>
       <c r="O43">
-        <v>148.5190996981115</v>
+        <v>147.1431643497828</v>
       </c>
       <c r="P43">
-        <v>346.5445659622603</v>
+        <v>343.3340501494931</v>
       </c>
       <c r="Q43">
-        <v>423.8445659622603</v>
+        <v>420.6340501494932</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1149179993235309</v>
+        <v>0.1158691769181221</v>
       </c>
       <c r="T43">
-        <v>1.00575110787815</v>
+        <v>1.0195919008541</v>
       </c>
       <c r="U43">
         <v>0.08015748822216712</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.632694239745632</v>
+        <v>3.546201519751689</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09077042414982793</v>
+        <v>0.09157682957901064</v>
       </c>
       <c r="C44">
-        <v>3285.566936878115</v>
+        <v>3174.851696062644</v>
       </c>
       <c r="D44">
-        <v>4833.922936878114</v>
+        <v>4780.425696062644</v>
       </c>
       <c r="E44">
-        <v>930.0559999999996</v>
+        <v>987.2739999999999</v>
       </c>
       <c r="F44">
-        <v>2403.155999999999</v>
+        <v>2460.374</v>
       </c>
       <c r="G44">
         <v>854.8</v>
@@ -5029,45 +5029,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M44">
-        <v>192.6309487660302</v>
+        <v>204.1064471271262</v>
       </c>
       <c r="N44">
-        <v>490.4772144992759</v>
+        <v>479.0017161381799</v>
       </c>
       <c r="O44">
-        <v>147.1431643497828</v>
+        <v>143.700514841454</v>
       </c>
       <c r="P44">
-        <v>343.3340501494931</v>
+        <v>335.3012012967259</v>
       </c>
       <c r="Q44">
-        <v>420.6340501494932</v>
+        <v>412.601201296726</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.115869176918122</v>
+        <v>0.116853729165155</v>
       </c>
       <c r="T44">
-        <v>1.0195919008541</v>
+        <v>1.033918335688856</v>
       </c>
       <c r="U44">
-        <v>0.08015748822216712</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05611024175551698</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.546201519751689</v>
+        <v>3.346823056695692</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09157682957901064</v>
+        <v>0.09156003500819335</v>
       </c>
       <c r="C45">
-        <v>3174.851696062644</v>
+        <v>3118.735777813024</v>
       </c>
       <c r="D45">
-        <v>4780.425696062644</v>
+        <v>4781.527777813023</v>
       </c>
       <c r="E45">
-        <v>987.2739999999999</v>
+        <v>1044.492</v>
       </c>
       <c r="F45">
-        <v>2460.374</v>
+        <v>2517.592</v>
       </c>
       <c r="G45">
         <v>854.8</v>
@@ -5111,28 +5111,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M45">
-        <v>204.1064471271262</v>
+        <v>208.8531086882221</v>
       </c>
       <c r="N45">
-        <v>479.0017161381799</v>
+        <v>474.255054577084</v>
       </c>
       <c r="O45">
-        <v>143.700514841454</v>
+        <v>142.2765163731252</v>
       </c>
       <c r="P45">
-        <v>335.3012012967259</v>
+        <v>331.9785382039588</v>
       </c>
       <c r="Q45">
-        <v>412.601201296726</v>
+        <v>409.2785382039589</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.116853729165155</v>
+        <v>0.117873443992439</v>
       </c>
       <c r="T45">
-        <v>1.033918335688856</v>
+        <v>1.048756428910568</v>
       </c>
       <c r="U45">
         <v>0.08295748822216711</v>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.346823056695692</v>
+        <v>3.270758896316245</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09156003500819335</v>
+        <v>0.09154324043737605</v>
       </c>
       <c r="C46">
-        <v>3118.735777813024</v>
+        <v>3062.620367829544</v>
       </c>
       <c r="D46">
-        <v>4781.527777813023</v>
+        <v>4782.630367829544</v>
       </c>
       <c r="E46">
-        <v>1044.492</v>
+        <v>1101.71</v>
       </c>
       <c r="F46">
-        <v>2517.592</v>
+        <v>2574.81</v>
       </c>
       <c r="G46">
         <v>854.8</v>
@@ -5193,28 +5193,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M46">
-        <v>208.8531086882221</v>
+        <v>213.5997702493181</v>
       </c>
       <c r="N46">
-        <v>474.255054577084</v>
+        <v>469.508393015988</v>
       </c>
       <c r="O46">
-        <v>142.2765163731252</v>
+        <v>140.8525179047964</v>
       </c>
       <c r="P46">
-        <v>331.9785382039588</v>
+        <v>328.6558751111916</v>
       </c>
       <c r="Q46">
-        <v>409.2785382039589</v>
+        <v>405.9558751111916</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.117873443992439</v>
+        <v>0.1189302393588971</v>
       </c>
       <c r="T46">
-        <v>1.048756428910568</v>
+        <v>1.064134089158523</v>
       </c>
       <c r="U46">
         <v>0.08295748822216711</v>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.270758896316245</v>
+        <v>3.198075365286994</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09154324043737605</v>
+        <v>0.09152644586655875</v>
       </c>
       <c r="C47">
-        <v>3062.620367829544</v>
+        <v>3006.505466463896</v>
       </c>
       <c r="D47">
-        <v>4782.630367829544</v>
+        <v>4783.733466463896</v>
       </c>
       <c r="E47">
-        <v>1101.71</v>
+        <v>1158.928</v>
       </c>
       <c r="F47">
-        <v>2574.81</v>
+        <v>2632.028</v>
       </c>
       <c r="G47">
         <v>854.8</v>
@@ -5275,28 +5275,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M47">
-        <v>213.5997702493181</v>
+        <v>218.3464318104141</v>
       </c>
       <c r="N47">
-        <v>469.508393015988</v>
+        <v>464.761731454892</v>
       </c>
       <c r="O47">
-        <v>140.8525179047964</v>
+        <v>139.4285194364676</v>
       </c>
       <c r="P47">
-        <v>328.6558751111916</v>
+        <v>325.3332120184244</v>
       </c>
       <c r="Q47">
-        <v>405.9558751111916</v>
+        <v>402.6332120184245</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1189302393588971</v>
+        <v>0.1200261752944832</v>
       </c>
       <c r="T47">
-        <v>1.064134089158523</v>
+        <v>1.080081292378625</v>
       </c>
       <c r="U47">
         <v>0.08295748822216711</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.198075365286994</v>
+        <v>3.128551987780755</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09152644586655875</v>
+        <v>0.09150965129574147</v>
       </c>
       <c r="C48">
-        <v>3006.505466463896</v>
+        <v>2950.391074068092</v>
       </c>
       <c r="D48">
-        <v>4783.733466463896</v>
+        <v>4784.837074068091</v>
       </c>
       <c r="E48">
-        <v>1158.928</v>
+        <v>1216.146</v>
       </c>
       <c r="F48">
-        <v>2632.028</v>
+        <v>2689.246</v>
       </c>
       <c r="G48">
         <v>854.8</v>
@@ -5357,28 +5357,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M48">
-        <v>218.3464318104141</v>
+        <v>223.09309337151</v>
       </c>
       <c r="N48">
-        <v>464.761731454892</v>
+        <v>460.0150698937961</v>
       </c>
       <c r="O48">
-        <v>139.4285194364676</v>
+        <v>138.0045209681388</v>
       </c>
       <c r="P48">
-        <v>325.3332120184244</v>
+        <v>322.0105489256572</v>
       </c>
       <c r="Q48">
-        <v>402.6332120184245</v>
+        <v>399.3105489256573</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1200261752944832</v>
+        <v>0.1211634673031103</v>
       </c>
       <c r="T48">
-        <v>1.080081292378625</v>
+        <v>1.096630276852316</v>
       </c>
       <c r="U48">
         <v>0.08295748822216711</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.128551987780755</v>
+        <v>3.061987051870527</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09150965129574147</v>
+        <v>0.09411365672492417</v>
       </c>
       <c r="C49">
-        <v>2950.391074068092</v>
+        <v>2727.929548784971</v>
       </c>
       <c r="D49">
-        <v>4784.837074068091</v>
+        <v>4619.593548784971</v>
       </c>
       <c r="E49">
-        <v>1216.146</v>
+        <v>1273.364</v>
       </c>
       <c r="F49">
-        <v>2689.246</v>
+        <v>2746.464</v>
       </c>
       <c r="G49">
         <v>854.8</v>
@@ -5439,45 +5439,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M49">
-        <v>223.09309337151</v>
+        <v>249.262174132606</v>
       </c>
       <c r="N49">
-        <v>460.0150698937961</v>
+        <v>433.8459891327001</v>
       </c>
       <c r="O49">
-        <v>138.0045209681388</v>
+        <v>130.15379673981</v>
       </c>
       <c r="P49">
-        <v>322.0105489256572</v>
+        <v>303.6921923928901</v>
       </c>
       <c r="Q49">
-        <v>399.3105489256573</v>
+        <v>380.9921923928902</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1211634673031103</v>
+        <v>0.1223445013120693</v>
       </c>
       <c r="T49">
-        <v>1.096630276852316</v>
+        <v>1.113815760728841</v>
       </c>
       <c r="U49">
-        <v>0.08295748822216711</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.05807024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.061987051870527</v>
+        <v>2.740520761493064</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09411365672492417</v>
+        <v>0.09415146215410686</v>
       </c>
       <c r="C50">
-        <v>2727.929548784972</v>
+        <v>2668.396523933948</v>
       </c>
       <c r="D50">
-        <v>4619.593548784971</v>
+        <v>4617.278523933947</v>
       </c>
       <c r="E50">
-        <v>1273.364</v>
+        <v>1330.582</v>
       </c>
       <c r="F50">
-        <v>2746.463999999999</v>
+        <v>2803.682</v>
       </c>
       <c r="G50">
         <v>854.8</v>
@@ -5521,28 +5521,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M50">
-        <v>249.2621741326059</v>
+        <v>254.4551360937019</v>
       </c>
       <c r="N50">
-        <v>433.8459891327001</v>
+        <v>428.6530271716042</v>
       </c>
       <c r="O50">
-        <v>130.15379673981</v>
+        <v>128.5959081514812</v>
       </c>
       <c r="P50">
-        <v>303.6921923928901</v>
+        <v>300.0571190201229</v>
       </c>
       <c r="Q50">
-        <v>380.9921923928902</v>
+        <v>377.357119020123</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1223445013120693</v>
+        <v>0.123571850380203</v>
       </c>
       <c r="T50">
-        <v>1.113815760728841</v>
+        <v>1.131675185149543</v>
       </c>
       <c r="U50">
         <v>0.09075748822216712</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.740520761493064</v>
+        <v>2.684591766360553</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09415146215410686</v>
+        <v>0.09418926758328958</v>
       </c>
       <c r="C51">
-        <v>2668.396523933948</v>
+        <v>2608.865818185507</v>
       </c>
       <c r="D51">
-        <v>4617.278523933947</v>
+        <v>4614.965818185507</v>
       </c>
       <c r="E51">
-        <v>1330.582</v>
+        <v>1387.8</v>
       </c>
       <c r="F51">
-        <v>2803.682</v>
+        <v>2860.9</v>
       </c>
       <c r="G51">
         <v>854.8</v>
@@ -5603,28 +5603,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M51">
-        <v>254.4551360937019</v>
+        <v>259.6480980547979</v>
       </c>
       <c r="N51">
-        <v>428.6530271716042</v>
+        <v>423.4600652105082</v>
       </c>
       <c r="O51">
-        <v>128.5959081514812</v>
+        <v>127.0380195631525</v>
       </c>
       <c r="P51">
-        <v>300.0571190201229</v>
+        <v>296.4220456473557</v>
       </c>
       <c r="Q51">
-        <v>377.357119020123</v>
+        <v>373.7220456473558</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.123571850380203</v>
+        <v>0.1248482934110622</v>
       </c>
       <c r="T51">
-        <v>1.131675185149543</v>
+        <v>1.150248986547074</v>
       </c>
       <c r="U51">
         <v>0.09075748822216712</v>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.684591766360553</v>
+        <v>2.630899931033342</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09418926758328958</v>
+        <v>0.09422707301247228</v>
       </c>
       <c r="C52">
-        <v>2608.865818185507</v>
+        <v>2549.337428056616</v>
       </c>
       <c r="D52">
-        <v>4614.965818185507</v>
+        <v>4612.655428056615</v>
       </c>
       <c r="E52">
-        <v>1387.8</v>
+        <v>1445.018</v>
       </c>
       <c r="F52">
-        <v>2860.9</v>
+        <v>2918.117999999999</v>
       </c>
       <c r="G52">
         <v>854.8</v>
@@ -5685,28 +5685,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M52">
-        <v>259.6480980547979</v>
+        <v>264.8410600158938</v>
       </c>
       <c r="N52">
-        <v>423.4600652105082</v>
+        <v>418.2671032494123</v>
       </c>
       <c r="O52">
-        <v>127.0380195631525</v>
+        <v>125.4801309748237</v>
       </c>
       <c r="P52">
-        <v>296.4220456473557</v>
+        <v>292.7869722745886</v>
       </c>
       <c r="Q52">
-        <v>373.7220456473558</v>
+        <v>370.0869722745887</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1248482934110622</v>
+        <v>0.1261768361574666</v>
       </c>
       <c r="T52">
-        <v>1.150248986547074</v>
+        <v>1.169580902287361</v>
       </c>
       <c r="U52">
         <v>0.09075748822216712</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.630899931033342</v>
+        <v>2.579313657875826</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09422707301247228</v>
+        <v>0.09426487844165499</v>
       </c>
       <c r="C53">
-        <v>2549.337428056616</v>
+        <v>2489.811350071207</v>
       </c>
       <c r="D53">
-        <v>4612.655428056615</v>
+        <v>4610.347350071207</v>
       </c>
       <c r="E53">
-        <v>1445.018</v>
+        <v>1502.236</v>
       </c>
       <c r="F53">
-        <v>2918.117999999999</v>
+        <v>2975.336</v>
       </c>
       <c r="G53">
         <v>854.8</v>
@@ -5767,28 +5767,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M53">
-        <v>264.8410600158938</v>
+        <v>270.0340219769898</v>
       </c>
       <c r="N53">
-        <v>418.2671032494123</v>
+        <v>413.0741412883163</v>
       </c>
       <c r="O53">
-        <v>125.4801309748237</v>
+        <v>123.9222423864949</v>
       </c>
       <c r="P53">
-        <v>292.7869722745886</v>
+        <v>289.1518989018214</v>
       </c>
       <c r="Q53">
-        <v>370.0869722745887</v>
+        <v>366.4518989018215</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1261768361574666</v>
+        <v>0.1275607348516378</v>
       </c>
       <c r="T53">
-        <v>1.169580902287361</v>
+        <v>1.189718314516827</v>
       </c>
       <c r="U53">
         <v>0.09075748822216712</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.579313657875826</v>
+        <v>2.529711472147444</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09426487844165499</v>
+        <v>0.09574958387083771</v>
       </c>
       <c r="C54">
-        <v>2489.811350071207</v>
+        <v>2343.741255803884</v>
       </c>
       <c r="D54">
-        <v>4610.347350071207</v>
+        <v>4521.495255803883</v>
       </c>
       <c r="E54">
-        <v>1502.236</v>
+        <v>1559.454</v>
       </c>
       <c r="F54">
-        <v>2975.336</v>
+        <v>3032.554</v>
       </c>
       <c r="G54">
         <v>854.8</v>
@@ -5849,45 +5849,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M54">
-        <v>270.0340219769898</v>
+        <v>287.0539445380857</v>
       </c>
       <c r="N54">
-        <v>413.0741412883163</v>
+        <v>396.0542187272204</v>
       </c>
       <c r="O54">
-        <v>123.9222423864949</v>
+        <v>118.8162656181661</v>
       </c>
       <c r="P54">
-        <v>289.1518989018214</v>
+        <v>277.2379531090543</v>
       </c>
       <c r="Q54">
-        <v>366.4518989018215</v>
+        <v>354.5379531090543</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1275607348516378</v>
+        <v>0.1290035228519441</v>
       </c>
       <c r="T54">
-        <v>1.189718314516827</v>
+        <v>1.210712637904993</v>
       </c>
       <c r="U54">
-        <v>0.09075748822216712</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.06353024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.529711472147444</v>
+        <v>2.3797205238358</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09574958387083771</v>
+        <v>0.09581468930002041</v>
       </c>
       <c r="C55">
-        <v>2343.741255803884</v>
+        <v>2282.705341807682</v>
       </c>
       <c r="D55">
-        <v>4521.495255803883</v>
+        <v>4517.677341807682</v>
       </c>
       <c r="E55">
-        <v>1559.454</v>
+        <v>1616.672</v>
       </c>
       <c r="F55">
-        <v>3032.554</v>
+        <v>3089.772</v>
       </c>
       <c r="G55">
         <v>854.8</v>
@@ -5931,28 +5931,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M55">
-        <v>287.0539445380857</v>
+        <v>292.4700566991817</v>
       </c>
       <c r="N55">
-        <v>396.0542187272204</v>
+        <v>390.6381065661243</v>
       </c>
       <c r="O55">
-        <v>118.8162656181661</v>
+        <v>117.1914319698373</v>
       </c>
       <c r="P55">
-        <v>277.2379531090543</v>
+        <v>273.446674596287</v>
       </c>
       <c r="Q55">
-        <v>354.5379531090543</v>
+        <v>350.7466745962871</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1290035228519441</v>
+        <v>0.130509040765307</v>
       </c>
       <c r="T55">
-        <v>1.210712637904993</v>
+        <v>1.23261975796221</v>
       </c>
       <c r="U55">
         <v>0.09465748822216712</v>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.3797205238358</v>
+        <v>2.335651625246248</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09581468930002041</v>
+        <v>0.0958797947292031</v>
       </c>
       <c r="C56">
-        <v>2282.705341807682</v>
+        <v>2221.675870003098</v>
       </c>
       <c r="D56">
-        <v>4517.677341807682</v>
+        <v>4513.865870003097</v>
       </c>
       <c r="E56">
-        <v>1616.672</v>
+        <v>1673.89</v>
       </c>
       <c r="F56">
-        <v>3089.772</v>
+        <v>3146.99</v>
       </c>
       <c r="G56">
         <v>854.8</v>
@@ -6013,28 +6013,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M56">
-        <v>292.4700566991817</v>
+        <v>297.8861688602777</v>
       </c>
       <c r="N56">
-        <v>390.6381065661243</v>
+        <v>385.2219944050284</v>
       </c>
       <c r="O56">
-        <v>117.1914319698373</v>
+        <v>115.5665983215085</v>
       </c>
       <c r="P56">
-        <v>273.446674596287</v>
+        <v>269.6553960835199</v>
       </c>
       <c r="Q56">
-        <v>350.7466745962871</v>
+        <v>346.95539608352</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.130509040765307</v>
+        <v>0.1320814705859306</v>
       </c>
       <c r="T56">
-        <v>1.23261975796221</v>
+        <v>1.255500527799748</v>
       </c>
       <c r="U56">
         <v>0.09465748822216712</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.335651625246248</v>
+        <v>2.293185232059953</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0958797947292031</v>
+        <v>0.09594490015838583</v>
       </c>
       <c r="C57">
-        <v>2221.675870003098</v>
+        <v>2160.652824098439</v>
       </c>
       <c r="D57">
-        <v>4513.865870003097</v>
+        <v>4510.060824098439</v>
       </c>
       <c r="E57">
-        <v>1673.89</v>
+        <v>1731.108</v>
       </c>
       <c r="F57">
-        <v>3146.99</v>
+        <v>3204.208</v>
       </c>
       <c r="G57">
         <v>854.8</v>
@@ -6095,28 +6095,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M57">
-        <v>297.8861688602777</v>
+        <v>303.3022810213736</v>
       </c>
       <c r="N57">
-        <v>385.2219944050284</v>
+        <v>379.8058822439324</v>
       </c>
       <c r="O57">
-        <v>115.5665983215085</v>
+        <v>113.9417646731797</v>
       </c>
       <c r="P57">
-        <v>269.6553960835199</v>
+        <v>265.8641175707527</v>
       </c>
       <c r="Q57">
-        <v>346.95539608352</v>
+        <v>343.1641175707528</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1320814705859306</v>
+        <v>0.1337253744893098</v>
       </c>
       <c r="T57">
-        <v>1.255500527799748</v>
+        <v>1.279421332629901</v>
       </c>
       <c r="U57">
         <v>0.09465748822216712</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.293185232059953</v>
+        <v>2.252235495773168</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09594490015838583</v>
+        <v>0.09601000558756852</v>
       </c>
       <c r="C58">
-        <v>2160.652824098439</v>
+        <v>2099.636187856906</v>
       </c>
       <c r="D58">
-        <v>4510.060824098439</v>
+        <v>4506.262187856905</v>
       </c>
       <c r="E58">
-        <v>1731.108</v>
+        <v>1788.326</v>
       </c>
       <c r="F58">
-        <v>3204.208</v>
+        <v>3261.426</v>
       </c>
       <c r="G58">
         <v>854.8</v>
@@ -6177,28 +6177,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M58">
-        <v>303.3022810213736</v>
+        <v>308.7183931824696</v>
       </c>
       <c r="N58">
-        <v>379.8058822439324</v>
+        <v>374.3897700828365</v>
       </c>
       <c r="O58">
-        <v>113.9417646731797</v>
+        <v>112.3169310248509</v>
       </c>
       <c r="P58">
-        <v>265.8641175707527</v>
+        <v>262.0728390579856</v>
       </c>
       <c r="Q58">
-        <v>343.1641175707528</v>
+        <v>339.3728390579856</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1337253744893098</v>
+        <v>0.1354457390393578</v>
       </c>
       <c r="T58">
-        <v>1.279421332629901</v>
+        <v>1.304454733033549</v>
       </c>
       <c r="U58">
         <v>0.09465748822216712</v>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.252235495773168</v>
+        <v>2.212722592338551</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09601000558756852</v>
+        <v>0.09607511101675123</v>
       </c>
       <c r="C59">
-        <v>2099.636187856906</v>
+        <v>2038.625945096347</v>
       </c>
       <c r="D59">
-        <v>4506.262187856905</v>
+        <v>4502.469945096346</v>
       </c>
       <c r="E59">
-        <v>1788.326</v>
+        <v>1845.544</v>
       </c>
       <c r="F59">
-        <v>3261.426</v>
+        <v>3318.644</v>
       </c>
       <c r="G59">
         <v>854.8</v>
@@ -6259,28 +6259,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M59">
-        <v>308.7183931824696</v>
+        <v>314.1345053435655</v>
       </c>
       <c r="N59">
-        <v>374.3897700828365</v>
+        <v>368.9736579217405</v>
       </c>
       <c r="O59">
-        <v>112.3169310248509</v>
+        <v>110.6920973765222</v>
       </c>
       <c r="P59">
-        <v>262.0728390579856</v>
+        <v>258.2815605452184</v>
       </c>
       <c r="Q59">
-        <v>339.3728390579856</v>
+        <v>335.5815605452185</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1354457390393578</v>
+        <v>0.1372480257108366</v>
       </c>
       <c r="T59">
-        <v>1.304454733033549</v>
+        <v>1.330680200123086</v>
       </c>
       <c r="U59">
         <v>0.09465748822216712</v>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.212722592338551</v>
+        <v>2.174572202815472</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09607511101675123</v>
+        <v>0.09614021644593393</v>
       </c>
       <c r="C60">
-        <v>2038.625945096347</v>
+        <v>1977.622079689047</v>
       </c>
       <c r="D60">
-        <v>4502.469945096346</v>
+        <v>4498.684079689046</v>
       </c>
       <c r="E60">
-        <v>1845.543999999999</v>
+        <v>1902.761999999999</v>
       </c>
       <c r="F60">
-        <v>3318.643999999999</v>
+        <v>3375.861999999999</v>
       </c>
       <c r="G60">
         <v>854.8</v>
@@ -6341,28 +6341,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M60">
-        <v>314.1345053435655</v>
+        <v>319.5506175046614</v>
       </c>
       <c r="N60">
-        <v>368.9736579217406</v>
+        <v>363.5575457606446</v>
       </c>
       <c r="O60">
-        <v>110.6920973765222</v>
+        <v>109.0672637281934</v>
       </c>
       <c r="P60">
-        <v>258.2815605452184</v>
+        <v>254.4902820324513</v>
       </c>
       <c r="Q60">
-        <v>335.5815605452185</v>
+        <v>331.7902820324513</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1372480257108366</v>
+        <v>0.1391382288053144</v>
       </c>
       <c r="T60">
-        <v>1.330680200123086</v>
+        <v>1.35818495829016</v>
       </c>
       <c r="U60">
         <v>0.09465748822216712</v>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.174572202815473</v>
+        <v>2.13771504683555</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09614021644593393</v>
+        <v>0.09620532187511666</v>
       </c>
       <c r="C61">
-        <v>1977.622079689047</v>
+        <v>1916.624575561477</v>
       </c>
       <c r="D61">
-        <v>4498.684079689046</v>
+        <v>4494.904575561476</v>
       </c>
       <c r="E61">
-        <v>1902.761999999999</v>
+        <v>1959.98</v>
       </c>
       <c r="F61">
-        <v>3375.861999999999</v>
+        <v>3433.079999999999</v>
       </c>
       <c r="G61">
         <v>854.8</v>
@@ -6423,28 +6423,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M61">
-        <v>319.5506175046614</v>
+        <v>324.9667296657574</v>
       </c>
       <c r="N61">
-        <v>363.5575457606446</v>
+        <v>358.1414335995486</v>
       </c>
       <c r="O61">
-        <v>109.0672637281934</v>
+        <v>107.4424300798646</v>
       </c>
       <c r="P61">
-        <v>254.4902820324513</v>
+        <v>250.699003519684</v>
       </c>
       <c r="Q61">
-        <v>331.7902820324513</v>
+        <v>327.9990035196841</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1391382288053144</v>
+        <v>0.1411229420545161</v>
       </c>
       <c r="T61">
-        <v>1.35818495829016</v>
+        <v>1.387064954365589</v>
       </c>
       <c r="U61">
         <v>0.09465748822216712</v>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.13771504683555</v>
+        <v>2.102086462721624</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09620532187511666</v>
+        <v>0.09627042730429936</v>
       </c>
       <c r="C62">
-        <v>1916.624575561477</v>
+        <v>1855.633416694093</v>
       </c>
       <c r="D62">
-        <v>4494.904575561476</v>
+        <v>4491.131416694092</v>
       </c>
       <c r="E62">
-        <v>1959.98</v>
+        <v>2017.197999999999</v>
       </c>
       <c r="F62">
-        <v>3433.079999999999</v>
+        <v>3490.297999999999</v>
       </c>
       <c r="G62">
         <v>854.8</v>
@@ -6505,28 +6505,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M62">
-        <v>324.9667296657574</v>
+        <v>330.3828418268534</v>
       </c>
       <c r="N62">
-        <v>358.1414335995486</v>
+        <v>352.7253214384527</v>
       </c>
       <c r="O62">
-        <v>107.4424300798646</v>
+        <v>105.8175964315358</v>
       </c>
       <c r="P62">
-        <v>250.699003519684</v>
+        <v>246.9077250069169</v>
       </c>
       <c r="Q62">
-        <v>327.9990035196841</v>
+        <v>324.2077250069169</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1411229420545161</v>
+        <v>0.1432094354703436</v>
       </c>
       <c r="T62">
-        <v>1.387064954365589</v>
+        <v>1.417425975880783</v>
       </c>
       <c r="U62">
         <v>0.09465748822216712</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.102086462721624</v>
+        <v>2.067626028906515</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09627042730429936</v>
+        <v>0.09633553273348205</v>
       </c>
       <c r="C63">
-        <v>1855.633416694093</v>
+        <v>1794.648587121083</v>
       </c>
       <c r="D63">
-        <v>4491.131416694092</v>
+        <v>4487.364587121082</v>
       </c>
       <c r="E63">
-        <v>2017.197999999999</v>
+        <v>2074.416</v>
       </c>
       <c r="F63">
-        <v>3490.297999999999</v>
+        <v>3547.516</v>
       </c>
       <c r="G63">
         <v>854.8</v>
@@ -6587,28 +6587,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M63">
-        <v>330.3828418268534</v>
+        <v>335.7989539879493</v>
       </c>
       <c r="N63">
-        <v>352.7253214384527</v>
+        <v>347.3092092773567</v>
       </c>
       <c r="O63">
-        <v>105.8175964315358</v>
+        <v>104.192762783207</v>
       </c>
       <c r="P63">
-        <v>246.9077250069169</v>
+        <v>243.1164464941497</v>
       </c>
       <c r="Q63">
-        <v>324.2077250069169</v>
+        <v>320.4164464941498</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1432094354703436</v>
+        <v>0.1454057443291093</v>
       </c>
       <c r="T63">
-        <v>1.417425975880783</v>
+        <v>1.449384945896778</v>
       </c>
       <c r="U63">
         <v>0.09465748822216712</v>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.067626028906515</v>
+        <v>2.034277221988668</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09633553273348205</v>
+        <v>0.09640063816266477</v>
       </c>
       <c r="C64">
-        <v>1794.648587121083</v>
+        <v>1733.670070930157</v>
       </c>
       <c r="D64">
-        <v>4487.364587121082</v>
+        <v>4483.604070930156</v>
       </c>
       <c r="E64">
-        <v>2074.416</v>
+        <v>2131.634</v>
       </c>
       <c r="F64">
-        <v>3547.516</v>
+        <v>3604.733999999999</v>
       </c>
       <c r="G64">
         <v>854.8</v>
@@ -6669,28 +6669,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M64">
-        <v>335.7989539879493</v>
+        <v>341.2150661490453</v>
       </c>
       <c r="N64">
-        <v>347.3092092773567</v>
+        <v>341.8930971162608</v>
       </c>
       <c r="O64">
-        <v>104.192762783207</v>
+        <v>102.5679291348782</v>
       </c>
       <c r="P64">
-        <v>243.1164464941497</v>
+        <v>239.3251679813825</v>
       </c>
       <c r="Q64">
-        <v>320.4164464941498</v>
+        <v>316.6251679813826</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1454057443291093</v>
+        <v>0.1477207725856461</v>
       </c>
       <c r="T64">
-        <v>1.449384945896778</v>
+        <v>1.483071427805528</v>
       </c>
       <c r="U64">
         <v>0.09465748822216712</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.034277221988668</v>
+        <v>2.001987107353927</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09640063816266477</v>
+        <v>0.1028273435918475</v>
       </c>
       <c r="C65">
-        <v>1733.670070930157</v>
+        <v>1333.891708688969</v>
       </c>
       <c r="D65">
-        <v>4483.604070930156</v>
+        <v>4141.043708688969</v>
       </c>
       <c r="E65">
-        <v>2131.634</v>
+        <v>2188.852</v>
       </c>
       <c r="F65">
-        <v>3604.733999999999</v>
+        <v>3661.952</v>
       </c>
       <c r="G65">
         <v>854.8</v>
@@ -6751,45 +6751,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M65">
-        <v>341.2150661490453</v>
+        <v>398.6308967101413</v>
       </c>
       <c r="N65">
-        <v>341.8930971162608</v>
+        <v>284.4772665551648</v>
       </c>
       <c r="O65">
-        <v>102.5679291348782</v>
+        <v>85.34317996654943</v>
       </c>
       <c r="P65">
-        <v>239.3251679813825</v>
+        <v>199.1340865886153</v>
       </c>
       <c r="Q65">
-        <v>316.6251679813826</v>
+        <v>276.4340865886154</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1477207725856461</v>
+        <v>0.1501644135231017</v>
       </c>
       <c r="T65">
-        <v>1.483071427805528</v>
+        <v>1.518629380931431</v>
       </c>
       <c r="U65">
-        <v>0.09465748822216712</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.06626024175551698</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.001987107353927</v>
+        <v>1.713635769085953</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1028273435918475</v>
+        <v>0.1029918490210302</v>
       </c>
       <c r="C66">
-        <v>1333.891708688969</v>
+        <v>1268.590887134016</v>
       </c>
       <c r="D66">
-        <v>4141.043708688969</v>
+        <v>4132.960887134015</v>
       </c>
       <c r="E66">
-        <v>2188.852</v>
+        <v>2246.07</v>
       </c>
       <c r="F66">
-        <v>3661.952</v>
+        <v>3719.17</v>
       </c>
       <c r="G66">
         <v>854.8</v>
@@ -6833,28 +6833,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M66">
-        <v>398.6308967101413</v>
+        <v>404.8595044712372</v>
       </c>
       <c r="N66">
-        <v>284.4772665551648</v>
+        <v>278.2486587940688</v>
       </c>
       <c r="O66">
-        <v>85.34317996654943</v>
+        <v>83.47459763822064</v>
       </c>
       <c r="P66">
-        <v>199.1340865886153</v>
+        <v>194.7740611558482</v>
       </c>
       <c r="Q66">
-        <v>276.4340865886154</v>
+        <v>272.0740611558483</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1501644135231017</v>
+        <v>0.1527476910855547</v>
       </c>
       <c r="T66">
-        <v>1.518629380931431</v>
+        <v>1.5562192170931</v>
       </c>
       <c r="U66">
         <v>0.1088574882221671</v>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.713635769085953</v>
+        <v>1.687272141869246</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1029918490210302</v>
+        <v>0.1031563544502129</v>
       </c>
       <c r="C67">
-        <v>1268.590887134016</v>
+        <v>1203.321557510584</v>
       </c>
       <c r="D67">
-        <v>4132.960887134015</v>
+        <v>4124.909557510584</v>
       </c>
       <c r="E67">
-        <v>2246.07</v>
+        <v>2303.288</v>
       </c>
       <c r="F67">
-        <v>3719.17</v>
+        <v>3776.388</v>
       </c>
       <c r="G67">
         <v>854.8</v>
@@ -6915,28 +6915,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M67">
-        <v>404.8595044712372</v>
+        <v>411.0881122323332</v>
       </c>
       <c r="N67">
-        <v>278.2486587940688</v>
+        <v>272.0200510329728</v>
       </c>
       <c r="O67">
-        <v>83.47459763822064</v>
+        <v>81.60601530989184</v>
       </c>
       <c r="P67">
-        <v>194.7740611558482</v>
+        <v>190.414035723081</v>
       </c>
       <c r="Q67">
-        <v>272.0740611558483</v>
+        <v>267.7140357230811</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1527476910855547</v>
+        <v>0.1554829261516814</v>
       </c>
       <c r="T67">
-        <v>1.5562192170931</v>
+        <v>1.596020220087809</v>
       </c>
       <c r="U67">
         <v>0.1088574882221671</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.687272141869246</v>
+        <v>1.661707412446985</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1031563544502129</v>
+        <v>0.1033208598793956</v>
       </c>
       <c r="C68">
-        <v>1203.321557510584</v>
+        <v>1138.083536130315</v>
       </c>
       <c r="D68">
-        <v>4124.909557510584</v>
+        <v>4116.889536130315</v>
       </c>
       <c r="E68">
-        <v>2303.288</v>
+        <v>2360.506</v>
       </c>
       <c r="F68">
-        <v>3776.388</v>
+        <v>3833.606</v>
       </c>
       <c r="G68">
         <v>854.8</v>
@@ -6997,28 +6997,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M68">
-        <v>411.0881122323332</v>
+        <v>417.3167199934292</v>
       </c>
       <c r="N68">
-        <v>272.0200510329728</v>
+        <v>265.7914432718769</v>
       </c>
       <c r="O68">
-        <v>81.60601530989184</v>
+        <v>79.73743298156307</v>
       </c>
       <c r="P68">
-        <v>190.414035723081</v>
+        <v>186.0540102903138</v>
       </c>
       <c r="Q68">
-        <v>267.7140357230811</v>
+        <v>263.3540102903139</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1554829261516814</v>
+        <v>0.1583839330399976</v>
       </c>
       <c r="T68">
-        <v>1.596020220087809</v>
+        <v>1.638233405082197</v>
       </c>
       <c r="U68">
         <v>0.1088574882221671</v>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.661707412446985</v>
+        <v>1.636905809276134</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1033208598793956</v>
+        <v>0.1034853653085783</v>
       </c>
       <c r="C69">
-        <v>1138.083536130315</v>
+        <v>1072.876640730642</v>
       </c>
       <c r="D69">
-        <v>4116.889536130315</v>
+        <v>4108.900640730641</v>
       </c>
       <c r="E69">
-        <v>2360.506</v>
+        <v>2417.724</v>
       </c>
       <c r="F69">
-        <v>3833.606</v>
+        <v>3890.824</v>
       </c>
       <c r="G69">
         <v>854.8</v>
@@ -7079,28 +7079,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M69">
-        <v>417.3167199934292</v>
+        <v>423.5453277545251</v>
       </c>
       <c r="N69">
-        <v>265.7914432718769</v>
+        <v>259.5628355107809</v>
       </c>
       <c r="O69">
-        <v>79.73743298156307</v>
+        <v>77.86885065323428</v>
       </c>
       <c r="P69">
-        <v>186.0540102903138</v>
+        <v>181.6939848575466</v>
       </c>
       <c r="Q69">
-        <v>263.3540102903139</v>
+        <v>258.9939848575467</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1583839330399976</v>
+        <v>0.1614662528588336</v>
       </c>
       <c r="T69">
-        <v>1.638233405082197</v>
+        <v>1.683084914138734</v>
       </c>
       <c r="U69">
         <v>0.1088574882221671</v>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.636905809276134</v>
+        <v>1.612833665022073</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1034853653085783</v>
+        <v>0.103649870737761</v>
       </c>
       <c r="C70">
-        <v>1072.876640730642</v>
+        <v>1007.700690460997</v>
       </c>
       <c r="D70">
-        <v>4108.900640730641</v>
+        <v>4100.942690460996</v>
       </c>
       <c r="E70">
-        <v>2417.724</v>
+        <v>2474.942</v>
       </c>
       <c r="F70">
-        <v>3890.824</v>
+        <v>3948.042</v>
       </c>
       <c r="G70">
         <v>854.8</v>
@@ -7161,28 +7161,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M70">
-        <v>423.5453277545251</v>
+        <v>429.7739355156211</v>
       </c>
       <c r="N70">
-        <v>259.5628355107809</v>
+        <v>253.3342277496849</v>
       </c>
       <c r="O70">
-        <v>77.86885065323428</v>
+        <v>76.00026832490548</v>
       </c>
       <c r="P70">
-        <v>181.6939848575466</v>
+        <v>177.3339594247795</v>
       </c>
       <c r="Q70">
-        <v>258.9939848575467</v>
+        <v>254.6339594247795</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1614662528588336</v>
+        <v>0.1647474320208203</v>
       </c>
       <c r="T70">
-        <v>1.683084914138734</v>
+        <v>1.730830068940854</v>
       </c>
       <c r="U70">
         <v>0.1088574882221671</v>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.612833665022073</v>
+        <v>1.589459264079724</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.103649870737761</v>
+        <v>0.1038143761669437</v>
       </c>
       <c r="C71">
-        <v>1007.700690460997</v>
+        <v>942.5555058691584</v>
       </c>
       <c r="D71">
-        <v>4100.942690460996</v>
+        <v>4093.015505869158</v>
       </c>
       <c r="E71">
-        <v>2474.942</v>
+        <v>2532.16</v>
       </c>
       <c r="F71">
-        <v>3948.042</v>
+        <v>4005.26</v>
       </c>
       <c r="G71">
         <v>854.8</v>
@@ -7243,28 +7243,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M71">
-        <v>429.7739355156211</v>
+        <v>436.0025432767171</v>
       </c>
       <c r="N71">
-        <v>253.3342277496849</v>
+        <v>247.105619988589</v>
       </c>
       <c r="O71">
-        <v>76.00026832490548</v>
+        <v>74.13168599657671</v>
       </c>
       <c r="P71">
-        <v>177.3339594247795</v>
+        <v>172.9739339920123</v>
       </c>
       <c r="Q71">
-        <v>254.6339594247795</v>
+        <v>250.2739339920124</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1647474320208203</v>
+        <v>0.1682473564602728</v>
       </c>
       <c r="T71">
-        <v>1.730830068940854</v>
+        <v>1.781758234063115</v>
       </c>
       <c r="U71">
         <v>0.1088574882221671</v>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.589459264079724</v>
+        <v>1.5667527031643</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1038143761669437</v>
+        <v>0.1039788815961264</v>
       </c>
       <c r="C72">
-        <v>942.5555058691584</v>
+        <v>877.4409088877655</v>
       </c>
       <c r="D72">
-        <v>4093.015505869158</v>
+        <v>4085.118908887766</v>
       </c>
       <c r="E72">
-        <v>2532.16</v>
+        <v>2589.378</v>
       </c>
       <c r="F72">
-        <v>4005.26</v>
+        <v>4062.478</v>
       </c>
       <c r="G72">
         <v>854.8</v>
@@ -7325,28 +7325,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M72">
-        <v>436.0025432767171</v>
+        <v>442.231151037813</v>
       </c>
       <c r="N72">
-        <v>247.105619988589</v>
+        <v>240.877012227493</v>
       </c>
       <c r="O72">
-        <v>74.13168599657671</v>
+        <v>72.26310366824791</v>
       </c>
       <c r="P72">
-        <v>172.9739339920123</v>
+        <v>168.6139085592451</v>
       </c>
       <c r="Q72">
-        <v>250.2739339920124</v>
+        <v>245.9139085592452</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1682473564602728</v>
+        <v>0.1719886549989979</v>
       </c>
       <c r="T72">
-        <v>1.781758234063115</v>
+        <v>1.836198686435188</v>
       </c>
       <c r="U72">
         <v>0.1088574882221671</v>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.5667527031643</v>
+        <v>1.544685763683112</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1039788815961264</v>
+        <v>0.1041433870253091</v>
       </c>
       <c r="C73">
-        <v>877.4409088877665</v>
+        <v>812.3567228209804</v>
       </c>
       <c r="D73">
-        <v>4085.118908887766</v>
+        <v>4077.252722820979</v>
       </c>
       <c r="E73">
-        <v>2589.377999999999</v>
+        <v>2646.595999999999</v>
       </c>
       <c r="F73">
-        <v>4062.477999999999</v>
+        <v>4119.695999999999</v>
       </c>
       <c r="G73">
         <v>854.8</v>
@@ -7407,28 +7407,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M73">
-        <v>442.2311510378129</v>
+        <v>448.4597587989089</v>
       </c>
       <c r="N73">
-        <v>240.8770122274931</v>
+        <v>234.6484044663972</v>
       </c>
       <c r="O73">
-        <v>72.26310366824794</v>
+        <v>70.39452133991917</v>
       </c>
       <c r="P73">
-        <v>168.6139085592452</v>
+        <v>164.2538831264781</v>
       </c>
       <c r="Q73">
-        <v>245.9139085592453</v>
+        <v>241.5538831264781</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1719886549989978</v>
+        <v>0.1759971891476318</v>
       </c>
       <c r="T73">
-        <v>1.836198686435187</v>
+        <v>1.894527742548122</v>
       </c>
       <c r="U73">
         <v>0.1088574882221671</v>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.544685763683113</v>
+        <v>1.52323179474307</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1041433870253091</v>
+        <v>0.1043078924544918</v>
       </c>
       <c r="C74">
-        <v>812.3567228209804</v>
+        <v>747.3027723313107</v>
       </c>
       <c r="D74">
-        <v>4077.252722820979</v>
+        <v>4069.41677233131</v>
       </c>
       <c r="E74">
-        <v>2646.595999999999</v>
+        <v>2703.814</v>
       </c>
       <c r="F74">
-        <v>4119.695999999999</v>
+        <v>4176.914</v>
       </c>
       <c r="G74">
         <v>854.8</v>
@@ -7489,28 +7489,28 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M74">
-        <v>448.4597587989089</v>
+        <v>454.6883665600049</v>
       </c>
       <c r="N74">
-        <v>234.6484044663972</v>
+        <v>228.4197967053012</v>
       </c>
       <c r="O74">
-        <v>70.39452133991917</v>
+        <v>68.52593901159035</v>
       </c>
       <c r="P74">
-        <v>164.2538831264781</v>
+        <v>159.8938576937108</v>
       </c>
       <c r="Q74">
-        <v>241.5538831264781</v>
+        <v>237.1938576937109</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1759971891476318</v>
+        <v>0.1803026517517202</v>
       </c>
       <c r="T74">
-        <v>1.894527742548122</v>
+        <v>1.957177469484237</v>
       </c>
       <c r="U74">
         <v>0.1088574882221671</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.52323179474307</v>
+        <v>1.502365605773986</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1043078924544918</v>
+        <v>0.1351241125626112</v>
       </c>
       <c r="C75">
-        <v>747.3027723313107</v>
+        <v>-387.1515067099908</v>
       </c>
       <c r="D75">
-        <v>4069.41677233131</v>
+        <v>2992.180493290009</v>
       </c>
       <c r="E75">
-        <v>2703.814</v>
+        <v>2761.032</v>
       </c>
       <c r="F75">
-        <v>4176.914</v>
+        <v>4234.132</v>
       </c>
       <c r="G75">
         <v>854.8</v>
@@ -7571,45 +7571,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M75">
-        <v>454.6883665600049</v>
+        <v>701.415671921101</v>
       </c>
       <c r="N75">
-        <v>228.4197967053012</v>
+        <v>-18.30750865579489</v>
       </c>
       <c r="O75">
-        <v>68.52593901159035</v>
+        <v>-5.492252596738467</v>
       </c>
       <c r="P75">
-        <v>159.8938576937108</v>
+        <v>-12.81525605905642</v>
       </c>
       <c r="Q75">
-        <v>237.1938576937109</v>
+        <v>64.48474394094364</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1803026517517202</v>
+        <v>0.1859755834764475</v>
       </c>
       <c r="T75">
-        <v>1.957177469484237</v>
+        <v>2.039725538336097</v>
       </c>
       <c r="U75">
-        <v>0.1088574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V75">
-        <v>0.3</v>
+        <v>0.2921697606474977</v>
       </c>
       <c r="W75">
-        <v>0.07620024175551698</v>
+        <v>0.1172573795388309</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.502365605773986</v>
+        <v>0.9738992021583256</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1351241125626112</v>
+        <v>0.1363226874448329</v>
       </c>
       <c r="C76">
-        <v>-387.1515067099908</v>
+        <v>-474.8627626544485</v>
       </c>
       <c r="D76">
-        <v>2992.180493290009</v>
+        <v>2961.687237345551</v>
       </c>
       <c r="E76">
-        <v>2761.032</v>
+        <v>2818.25</v>
       </c>
       <c r="F76">
-        <v>4234.132</v>
+        <v>4291.349999999999</v>
       </c>
       <c r="G76">
         <v>854.8</v>
@@ -7653,37 +7653,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M76">
-        <v>701.415671921101</v>
+        <v>710.8942620821969</v>
       </c>
       <c r="N76">
-        <v>-18.30750865579489</v>
+        <v>-27.78609881689079</v>
       </c>
       <c r="O76">
-        <v>-5.492252596738467</v>
+        <v>-8.335829645067236</v>
       </c>
       <c r="P76">
-        <v>-12.81525605905642</v>
+        <v>-19.45026917182355</v>
       </c>
       <c r="Q76">
-        <v>64.48474394094364</v>
+        <v>57.84973082817652</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1859755834764475</v>
+        <v>0.1915826068155055</v>
       </c>
       <c r="T76">
-        <v>2.039725538336097</v>
+        <v>2.121314559869541</v>
       </c>
       <c r="U76">
         <v>0.1656574882221671</v>
       </c>
       <c r="V76">
-        <v>0.2921697606474977</v>
+        <v>0.2882741638388644</v>
       </c>
       <c r="W76">
-        <v>0.1172573795388309</v>
+        <v>0.1179027143212754</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9738992021583256</v>
+        <v>0.9609138794628813</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1363226874448329</v>
+        <v>0.1375212623270546</v>
       </c>
       <c r="C77">
-        <v>-474.8627626544485</v>
+        <v>-561.9587761114699</v>
       </c>
       <c r="D77">
-        <v>2961.687237345551</v>
+        <v>2931.809223888529</v>
       </c>
       <c r="E77">
-        <v>2818.25</v>
+        <v>2875.467999999999</v>
       </c>
       <c r="F77">
-        <v>4291.349999999999</v>
+        <v>4348.567999999999</v>
       </c>
       <c r="G77">
         <v>854.8</v>
@@ -7735,37 +7735,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M77">
-        <v>710.8942620821969</v>
+        <v>720.3728522432928</v>
       </c>
       <c r="N77">
-        <v>-27.78609881689079</v>
+        <v>-37.26468897798668</v>
       </c>
       <c r="O77">
-        <v>-8.335829645067236</v>
+        <v>-11.179406693396</v>
       </c>
       <c r="P77">
-        <v>-19.45026917182355</v>
+        <v>-26.08528228459068</v>
       </c>
       <c r="Q77">
-        <v>57.84973082817652</v>
+        <v>51.21471771540939</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1915826068155055</v>
+        <v>0.1976568820994848</v>
       </c>
       <c r="T77">
-        <v>2.121314559869541</v>
+        <v>2.209702666530772</v>
       </c>
       <c r="U77">
         <v>0.1656574882221671</v>
       </c>
       <c r="V77">
-        <v>0.2882741638388644</v>
+        <v>0.2844810827357214</v>
       </c>
       <c r="W77">
-        <v>0.1179027143212754</v>
+        <v>0.118531066609445</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9609138794628813</v>
+        <v>0.9482702757857382</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1375212623270546</v>
+        <v>0.1387198372092762</v>
       </c>
       <c r="C78">
-        <v>-561.9587761114699</v>
+        <v>-648.4579811332405</v>
       </c>
       <c r="D78">
-        <v>2931.809223888529</v>
+        <v>2902.528018866758</v>
       </c>
       <c r="E78">
-        <v>2875.467999999999</v>
+        <v>2932.685999999999</v>
       </c>
       <c r="F78">
-        <v>4348.567999999999</v>
+        <v>4405.785999999999</v>
       </c>
       <c r="G78">
         <v>854.8</v>
@@ -7817,37 +7817,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M78">
-        <v>720.3728522432928</v>
+        <v>729.8514424043888</v>
       </c>
       <c r="N78">
-        <v>-37.26468897798668</v>
+        <v>-46.74327913908269</v>
       </c>
       <c r="O78">
-        <v>-11.179406693396</v>
+        <v>-14.02298374172481</v>
       </c>
       <c r="P78">
-        <v>-26.08528228459068</v>
+        <v>-32.72029539735788</v>
       </c>
       <c r="Q78">
-        <v>51.21471771540939</v>
+        <v>44.57970460264219</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1976568820994848</v>
+        <v>0.204259355234245</v>
       </c>
       <c r="T78">
-        <v>2.209702666530772</v>
+        <v>2.305776695510371</v>
       </c>
       <c r="U78">
         <v>0.1656574882221671</v>
       </c>
       <c r="V78">
-        <v>0.2844810827357214</v>
+        <v>0.2807865232196731</v>
       </c>
       <c r="W78">
-        <v>0.118531066609445</v>
+        <v>0.1191430980589609</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9482702757857382</v>
+        <v>0.9359550773989104</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1387198372092762</v>
+        <v>0.1399184120914979</v>
       </c>
       <c r="C79">
-        <v>-648.4579811332405</v>
+        <v>-734.3780826199409</v>
       </c>
       <c r="D79">
-        <v>2902.528018866758</v>
+        <v>2873.825917380059</v>
       </c>
       <c r="E79">
-        <v>2932.685999999999</v>
+        <v>2989.904</v>
       </c>
       <c r="F79">
-        <v>4405.785999999999</v>
+        <v>4463.004</v>
       </c>
       <c r="G79">
         <v>854.8</v>
@@ -7899,37 +7899,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M79">
-        <v>729.8514424043888</v>
+        <v>739.3300325654848</v>
       </c>
       <c r="N79">
-        <v>-46.74327913908269</v>
+        <v>-56.2218693001787</v>
       </c>
       <c r="O79">
-        <v>-14.02298374172481</v>
+        <v>-16.86656079005361</v>
       </c>
       <c r="P79">
-        <v>-32.72029539735788</v>
+        <v>-39.35530851012508</v>
       </c>
       <c r="Q79">
-        <v>44.57970460264219</v>
+        <v>37.94469148987498</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.204259355234245</v>
+        <v>0.211462053199438</v>
       </c>
       <c r="T79">
-        <v>2.305776695510371</v>
+        <v>2.410584727124479</v>
       </c>
       <c r="U79">
         <v>0.1656574882221671</v>
       </c>
       <c r="V79">
-        <v>0.2807865232196731</v>
+        <v>0.2771866959989081</v>
       </c>
       <c r="W79">
-        <v>0.1191430980589609</v>
+        <v>0.1197394363943866</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9359550773989104</v>
+        <v>0.9239556533296935</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1399184120914979</v>
+        <v>0.1411169869737196</v>
       </c>
       <c r="C80">
-        <v>-734.3780826199409</v>
+        <v>-819.7360920183855</v>
       </c>
       <c r="D80">
-        <v>2873.825917380059</v>
+        <v>2845.685907981614</v>
       </c>
       <c r="E80">
-        <v>2989.904</v>
+        <v>3047.122</v>
       </c>
       <c r="F80">
-        <v>4463.004</v>
+        <v>4520.222</v>
       </c>
       <c r="G80">
         <v>854.8</v>
@@ -7981,37 +7981,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M80">
-        <v>739.3300325654848</v>
+        <v>748.8086227265808</v>
       </c>
       <c r="N80">
-        <v>-56.2218693001787</v>
+        <v>-65.7004594612747</v>
       </c>
       <c r="O80">
-        <v>-16.86656079005361</v>
+        <v>-19.71013783838241</v>
       </c>
       <c r="P80">
-        <v>-39.35530851012508</v>
+        <v>-45.9903216228923</v>
       </c>
       <c r="Q80">
-        <v>37.94469148987498</v>
+        <v>31.30967837710777</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.211462053199438</v>
+        <v>0.2193507223994113</v>
       </c>
       <c r="T80">
-        <v>2.410584727124479</v>
+        <v>2.525374476035168</v>
       </c>
       <c r="U80">
         <v>0.1656574882221671</v>
       </c>
       <c r="V80">
-        <v>0.2771866959989081</v>
+        <v>0.2736780036444915</v>
       </c>
       <c r="W80">
-        <v>0.1197394363943866</v>
+        <v>0.1203206775567636</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9239556533296935</v>
+        <v>0.912260012148305</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1411169869737196</v>
+        <v>0.1423155618559412</v>
       </c>
       <c r="C81">
-        <v>-819.7360920183855</v>
+        <v>-904.5483609436969</v>
       </c>
       <c r="D81">
-        <v>2845.685907981614</v>
+        <v>2818.091639056302</v>
       </c>
       <c r="E81">
-        <v>3047.122</v>
+        <v>3104.34</v>
       </c>
       <c r="F81">
-        <v>4520.222</v>
+        <v>4577.44</v>
       </c>
       <c r="G81">
         <v>854.8</v>
@@ -8063,37 +8063,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M81">
-        <v>748.8086227265808</v>
+        <v>758.2872128876767</v>
       </c>
       <c r="N81">
-        <v>-65.7004594612747</v>
+        <v>-75.1790496223706</v>
       </c>
       <c r="O81">
-        <v>-19.71013783838241</v>
+        <v>-22.55371488671118</v>
       </c>
       <c r="P81">
-        <v>-45.9903216228923</v>
+        <v>-52.62533473565942</v>
       </c>
       <c r="Q81">
-        <v>31.30967837710777</v>
+        <v>24.67466526434065</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2193507223994113</v>
+        <v>0.2280282585193818</v>
       </c>
       <c r="T81">
-        <v>2.525374476035168</v>
+        <v>2.651643199836927</v>
       </c>
       <c r="U81">
         <v>0.1656574882221671</v>
       </c>
       <c r="V81">
-        <v>0.2736780036444915</v>
+        <v>0.2702570285989354</v>
       </c>
       <c r="W81">
-        <v>0.1203206775567636</v>
+        <v>0.1208873876900811</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.912260012148305</v>
+        <v>0.9008567619964511</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1423155618559412</v>
+        <v>0.1435141367381629</v>
       </c>
       <c r="C82">
-        <v>-904.5483609436969</v>
+        <v>-988.8306128636077</v>
       </c>
       <c r="D82">
-        <v>2818.091639056302</v>
+        <v>2791.027387136392</v>
       </c>
       <c r="E82">
-        <v>3104.34</v>
+        <v>3161.558</v>
       </c>
       <c r="F82">
-        <v>4577.44</v>
+        <v>4634.657999999999</v>
       </c>
       <c r="G82">
         <v>854.8</v>
@@ -8145,37 +8145,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M82">
-        <v>758.2872128876767</v>
+        <v>767.7658030487726</v>
       </c>
       <c r="N82">
-        <v>-75.1790496223706</v>
+        <v>-84.65763978346649</v>
       </c>
       <c r="O82">
-        <v>-22.55371488671118</v>
+        <v>-25.39729193503995</v>
       </c>
       <c r="P82">
-        <v>-52.62533473565942</v>
+        <v>-59.26034784842655</v>
       </c>
       <c r="Q82">
-        <v>24.67466526434065</v>
+        <v>18.03965215157352</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2280282585193818</v>
+        <v>0.2376192194940861</v>
       </c>
       <c r="T82">
-        <v>2.651643199836927</v>
+        <v>2.791203368249397</v>
       </c>
       <c r="U82">
         <v>0.1656574882221671</v>
       </c>
       <c r="V82">
-        <v>0.2702570285989354</v>
+        <v>0.2669205220730226</v>
       </c>
       <c r="W82">
-        <v>0.1208873876900811</v>
+        <v>0.1214401049806007</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9008567619964511</v>
+        <v>0.889735073576742</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1435141367381629</v>
+        <v>0.1447127116203846</v>
       </c>
       <c r="C83">
-        <v>-988.8306128636077</v>
+        <v>-1072.597972974389</v>
       </c>
       <c r="D83">
-        <v>2791.027387136392</v>
+        <v>2764.478027025611</v>
       </c>
       <c r="E83">
-        <v>3161.558</v>
+        <v>3218.776</v>
       </c>
       <c r="F83">
-        <v>4634.657999999999</v>
+        <v>4691.876</v>
       </c>
       <c r="G83">
         <v>854.8</v>
@@ -8227,37 +8227,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M83">
-        <v>767.7658030487726</v>
+        <v>777.2443932098687</v>
       </c>
       <c r="N83">
-        <v>-84.65763978346649</v>
+        <v>-94.13622994456261</v>
       </c>
       <c r="O83">
-        <v>-25.39729193503995</v>
+        <v>-28.24086898336878</v>
       </c>
       <c r="P83">
-        <v>-59.26034784842655</v>
+        <v>-65.89536096119383</v>
       </c>
       <c r="Q83">
-        <v>18.03965215157352</v>
+        <v>11.40463903880624</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2376192194940861</v>
+        <v>0.2482758427993132</v>
       </c>
       <c r="T83">
-        <v>2.791203368249397</v>
+        <v>2.946270222041031</v>
       </c>
       <c r="U83">
         <v>0.1656574882221671</v>
       </c>
       <c r="V83">
-        <v>0.2669205220730226</v>
+        <v>0.2636653937550589</v>
       </c>
       <c r="W83">
-        <v>0.1214401049806007</v>
+        <v>0.1219793413615954</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.889735073576742</v>
+        <v>0.8788846458501962</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1447127116203846</v>
+        <v>0.1459112865026063</v>
       </c>
       <c r="C84">
-        <v>-1072.597972974389</v>
+        <v>-1155.864996387698</v>
       </c>
       <c r="D84">
-        <v>2764.478027025611</v>
+        <v>2738.429003612302</v>
       </c>
       <c r="E84">
-        <v>3218.776</v>
+        <v>3275.994</v>
       </c>
       <c r="F84">
-        <v>4691.876</v>
+        <v>4749.094</v>
       </c>
       <c r="G84">
         <v>854.8</v>
@@ -8309,37 +8309,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M84">
-        <v>777.2443932098687</v>
+        <v>786.7229833709646</v>
       </c>
       <c r="N84">
-        <v>-94.13622994456261</v>
+        <v>-103.6148201056585</v>
       </c>
       <c r="O84">
-        <v>-28.24086898336878</v>
+        <v>-31.08444603169755</v>
       </c>
       <c r="P84">
-        <v>-65.89536096119383</v>
+        <v>-72.53037407396096</v>
       </c>
       <c r="Q84">
-        <v>11.40463903880624</v>
+        <v>4.769625926039112</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2482758427993132</v>
+        <v>0.2601861864933904</v>
       </c>
       <c r="T84">
-        <v>2.946270222041031</v>
+        <v>3.119580235102267</v>
       </c>
       <c r="U84">
         <v>0.1656574882221671</v>
       </c>
       <c r="V84">
-        <v>0.2636653937550589</v>
+        <v>0.260488702264034</v>
       </c>
       <c r="W84">
-        <v>0.1219793413615954</v>
+        <v>0.1225055840948553</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8788846458501962</v>
+        <v>0.8682956742134469</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1459112865026063</v>
+        <v>0.1471098613848279</v>
       </c>
       <c r="C85">
-        <v>-1155.864996387698</v>
+        <v>-1238.645694738736</v>
       </c>
       <c r="D85">
-        <v>2738.429003612302</v>
+        <v>2712.866305261264</v>
       </c>
       <c r="E85">
-        <v>3275.994</v>
+        <v>3333.212</v>
       </c>
       <c r="F85">
-        <v>4749.094</v>
+        <v>4806.312</v>
       </c>
       <c r="G85">
         <v>854.8</v>
@@ -8391,37 +8391,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M85">
-        <v>786.7229833709646</v>
+        <v>796.2015735320606</v>
       </c>
       <c r="N85">
-        <v>-103.6148201056585</v>
+        <v>-113.0934102667545</v>
       </c>
       <c r="O85">
-        <v>-31.08444603169755</v>
+        <v>-33.92802308002636</v>
       </c>
       <c r="P85">
-        <v>-72.53037407396096</v>
+        <v>-79.16538718672817</v>
       </c>
       <c r="Q85">
-        <v>4.769625926039112</v>
+        <v>-1.8653871867281</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2601861864933904</v>
+        <v>0.2735853231492273</v>
       </c>
       <c r="T85">
-        <v>3.119580235102267</v>
+        <v>3.314553999796159</v>
       </c>
       <c r="U85">
         <v>0.1656574882221671</v>
       </c>
       <c r="V85">
-        <v>0.260488702264034</v>
+        <v>0.2573876462847003</v>
       </c>
       <c r="W85">
-        <v>0.1225055840948553</v>
+        <v>0.1230192972392281</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8682956742134469</v>
+        <v>0.857958820949001</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1471098613848279</v>
+        <v>0.1483084362670496</v>
       </c>
       <c r="C86">
-        <v>-1238.645694738733</v>
+        <v>-1320.953561317867</v>
       </c>
       <c r="D86">
-        <v>2712.866305261266</v>
+        <v>2687.776438682132</v>
       </c>
       <c r="E86">
-        <v>3333.211999999999</v>
+        <v>3390.429999999999</v>
       </c>
       <c r="F86">
-        <v>4806.311999999999</v>
+        <v>4863.529999999999</v>
       </c>
       <c r="G86">
         <v>854.8</v>
@@ -8473,37 +8473,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M86">
-        <v>796.2015735320604</v>
+        <v>805.6801636931564</v>
       </c>
       <c r="N86">
-        <v>-113.0934102667543</v>
+        <v>-122.5720004278503</v>
       </c>
       <c r="O86">
-        <v>-33.92802308002629</v>
+        <v>-36.77160012835509</v>
       </c>
       <c r="P86">
-        <v>-79.165387186728</v>
+        <v>-85.80040029949521</v>
       </c>
       <c r="Q86">
-        <v>-1.865387186727929</v>
+        <v>-8.500400299495141</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2735853231492272</v>
+        <v>0.2887710113591757</v>
       </c>
       <c r="T86">
-        <v>3.314553999796157</v>
+        <v>3.535524266449235</v>
       </c>
       <c r="U86">
         <v>0.1656574882221671</v>
       </c>
       <c r="V86">
-        <v>0.2573876462847004</v>
+        <v>0.2543595563284098</v>
       </c>
       <c r="W86">
-        <v>0.1230192972392281</v>
+        <v>0.1235209230154979</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8579588209490013</v>
+        <v>0.8478651877613659</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1483084362670496</v>
+        <v>0.1495070111492713</v>
       </c>
       <c r="C87">
-        <v>-1320.953561317867</v>
+        <v>-1402.801594820465</v>
       </c>
       <c r="D87">
-        <v>2687.776438682132</v>
+        <v>2663.146405179535</v>
       </c>
       <c r="E87">
-        <v>3390.429999999999</v>
+        <v>3447.648</v>
       </c>
       <c r="F87">
-        <v>4863.529999999999</v>
+        <v>4920.748</v>
       </c>
       <c r="G87">
         <v>854.8</v>
@@ -8555,37 +8555,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M87">
-        <v>805.6801636931564</v>
+        <v>815.1587538542524</v>
       </c>
       <c r="N87">
-        <v>-122.5720004278503</v>
+        <v>-132.0505905889463</v>
       </c>
       <c r="O87">
-        <v>-36.77160012835509</v>
+        <v>-39.61517717668389</v>
       </c>
       <c r="P87">
-        <v>-85.80040029949521</v>
+        <v>-92.43541341226242</v>
       </c>
       <c r="Q87">
-        <v>-8.500400299495141</v>
+        <v>-15.13541341226235</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2887710113591757</v>
+        <v>0.3061260835991168</v>
       </c>
       <c r="T87">
-        <v>3.535524266449235</v>
+        <v>3.788061714052752</v>
       </c>
       <c r="U87">
         <v>0.1656574882221671</v>
       </c>
       <c r="V87">
-        <v>0.2543595563284098</v>
+        <v>0.2514018870687771</v>
       </c>
       <c r="W87">
-        <v>0.1235209230154979</v>
+        <v>0.1240108830760406</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8478651877613659</v>
+        <v>0.838006290229257</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1495070111492713</v>
+        <v>0.150705586031493</v>
       </c>
       <c r="C88">
-        <v>-1402.801594820465</v>
+        <v>-1484.202321802774</v>
       </c>
       <c r="D88">
-        <v>2663.146405179535</v>
+        <v>2638.963678197225</v>
       </c>
       <c r="E88">
-        <v>3447.648</v>
+        <v>3504.866</v>
       </c>
       <c r="F88">
-        <v>4920.748</v>
+        <v>4977.965999999999</v>
       </c>
       <c r="G88">
         <v>854.8</v>
@@ -8637,37 +8637,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M88">
-        <v>815.1587538542524</v>
+        <v>824.6373440153484</v>
       </c>
       <c r="N88">
-        <v>-132.0505905889463</v>
+        <v>-141.5291807500423</v>
       </c>
       <c r="O88">
-        <v>-39.61517717668389</v>
+        <v>-42.45875422501269</v>
       </c>
       <c r="P88">
-        <v>-92.43541341226242</v>
+        <v>-99.07042652502963</v>
       </c>
       <c r="Q88">
-        <v>-15.13541341226235</v>
+        <v>-21.77042652502956</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3061260835991168</v>
+        <v>0.326151166952895</v>
       </c>
       <c r="T88">
-        <v>3.788061714052752</v>
+        <v>4.079451076672195</v>
       </c>
       <c r="U88">
         <v>0.1656574882221671</v>
       </c>
       <c r="V88">
-        <v>0.2514018870687771</v>
+        <v>0.2485122102059175</v>
       </c>
       <c r="W88">
-        <v>0.1240108830760406</v>
+        <v>0.1244895796869156</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.838006290229257</v>
+        <v>0.8283740340197252</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.150705586031493</v>
+        <v>0.1519041609137146</v>
       </c>
       <c r="C89">
-        <v>-1484.202321802774</v>
+        <v>-1565.167817925339</v>
       </c>
       <c r="D89">
-        <v>2638.963678197225</v>
+        <v>2615.21618207466</v>
       </c>
       <c r="E89">
-        <v>3504.866</v>
+        <v>3562.083999999999</v>
       </c>
       <c r="F89">
-        <v>4977.965999999999</v>
+        <v>5035.183999999999</v>
       </c>
       <c r="G89">
         <v>854.8</v>
@@ -8719,37 +8719,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M89">
-        <v>824.6373440153484</v>
+        <v>834.1159341764443</v>
       </c>
       <c r="N89">
-        <v>-141.5291807500423</v>
+        <v>-151.0077709111382</v>
       </c>
       <c r="O89">
-        <v>-42.45875422501269</v>
+        <v>-45.30233127334146</v>
       </c>
       <c r="P89">
-        <v>-99.07042652502963</v>
+        <v>-105.7054396377968</v>
       </c>
       <c r="Q89">
-        <v>-21.77042652502956</v>
+        <v>-28.40543963779669</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.326151166952895</v>
+        <v>0.3495137641989696</v>
       </c>
       <c r="T89">
-        <v>4.079451076672195</v>
+        <v>4.419405333061544</v>
       </c>
       <c r="U89">
         <v>0.1656574882221671</v>
       </c>
       <c r="V89">
-        <v>0.2485122102059175</v>
+        <v>0.245688207817214</v>
       </c>
       <c r="W89">
-        <v>0.1244895796869156</v>
+        <v>0.1249573968293617</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8283740340197252</v>
+        <v>0.8189606927240466</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1519041609137146</v>
+        <v>0.1531027357959363</v>
       </c>
       <c r="C90">
-        <v>-1565.167817925339</v>
+        <v>-1645.709728059663</v>
       </c>
       <c r="D90">
-        <v>2615.21618207466</v>
+        <v>2591.892271940337</v>
       </c>
       <c r="E90">
-        <v>3562.083999999999</v>
+        <v>3619.301999999999</v>
       </c>
       <c r="F90">
-        <v>5035.183999999999</v>
+        <v>5092.401999999999</v>
       </c>
       <c r="G90">
         <v>854.8</v>
@@ -8801,37 +8801,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M90">
-        <v>834.1159341764443</v>
+        <v>843.5945243375402</v>
       </c>
       <c r="N90">
-        <v>-151.0077709111382</v>
+        <v>-160.4863610722341</v>
       </c>
       <c r="O90">
-        <v>-45.30233127334146</v>
+        <v>-48.14590832167023</v>
       </c>
       <c r="P90">
-        <v>-105.7054396377968</v>
+        <v>-112.3404527505639</v>
       </c>
       <c r="Q90">
-        <v>-28.40543963779669</v>
+        <v>-35.04045275056382</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3495137641989696</v>
+        <v>0.3771241063988759</v>
       </c>
       <c r="T90">
-        <v>4.419405333061544</v>
+        <v>4.821169454248957</v>
       </c>
       <c r="U90">
         <v>0.1656574882221671</v>
       </c>
       <c r="V90">
-        <v>0.245688207817214</v>
+        <v>0.2429276661563464</v>
       </c>
       <c r="W90">
-        <v>0.1249573968293617</v>
+        <v>0.1254147012270336</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8189606927240466</v>
+        <v>0.8097588871878214</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1531027357959363</v>
+        <v>0.1543013106781579</v>
       </c>
       <c r="C91">
-        <v>-1645.709728059663</v>
+        <v>-1725.839285328429</v>
       </c>
       <c r="D91">
-        <v>2591.892271940337</v>
+        <v>2568.98071467157</v>
       </c>
       <c r="E91">
-        <v>3619.301999999999</v>
+        <v>3676.52</v>
       </c>
       <c r="F91">
-        <v>5092.401999999999</v>
+        <v>5149.62</v>
       </c>
       <c r="G91">
         <v>854.8</v>
@@ -8883,37 +8883,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M91">
-        <v>843.5945243375402</v>
+        <v>853.0731144986363</v>
       </c>
       <c r="N91">
-        <v>-160.4863610722341</v>
+        <v>-169.9649512333302</v>
       </c>
       <c r="O91">
-        <v>-48.14590832167023</v>
+        <v>-50.98948536999907</v>
       </c>
       <c r="P91">
-        <v>-112.3404527505639</v>
+        <v>-118.9754658633312</v>
       </c>
       <c r="Q91">
-        <v>-35.04045275056382</v>
+        <v>-41.67546586333108</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3771241063988759</v>
+        <v>0.4102565170387636</v>
       </c>
       <c r="T91">
-        <v>4.821169454248957</v>
+        <v>5.303286399673854</v>
       </c>
       <c r="U91">
         <v>0.1656574882221671</v>
       </c>
       <c r="V91">
-        <v>0.2429276661563464</v>
+        <v>0.2402284698657203</v>
       </c>
       <c r="W91">
-        <v>0.1254147012270336</v>
+        <v>0.1258618433047573</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8097588871878214</v>
+        <v>0.8007615662190677</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1543013106781579</v>
+        <v>0.2071113724333695</v>
       </c>
       <c r="C92">
-        <v>-1725.839285328429</v>
+        <v>-2503.163546062043</v>
       </c>
       <c r="D92">
-        <v>2568.98071467157</v>
+        <v>1848.874453937957</v>
       </c>
       <c r="E92">
-        <v>3676.52</v>
+        <v>3733.738</v>
       </c>
       <c r="F92">
-        <v>5149.62</v>
+        <v>5206.838</v>
       </c>
       <c r="G92">
         <v>854.8</v>
@@ -8965,45 +8965,45 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M92">
-        <v>853.0731144986363</v>
+        <v>1143.720956659732</v>
       </c>
       <c r="N92">
-        <v>-169.9649512333302</v>
+        <v>-460.612793394426</v>
       </c>
       <c r="O92">
-        <v>-50.98948536999907</v>
+        <v>-138.1838380183278</v>
       </c>
       <c r="P92">
-        <v>-118.9754658633312</v>
+        <v>-322.4289553760982</v>
       </c>
       <c r="Q92">
-        <v>-41.67546586333108</v>
+        <v>-245.1289553760981</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4102565170387636</v>
+        <v>0.4782126508540689</v>
       </c>
       <c r="T92">
-        <v>5.303286399673854</v>
+        <v>6.292130948717255</v>
       </c>
       <c r="U92">
-        <v>0.1656574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V92">
-        <v>0.2402284698657203</v>
+        <v>0.1791804616207283</v>
       </c>
       <c r="W92">
-        <v>0.1258618433047573</v>
+        <v>0.1802991580840695</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.8007615662190677</v>
+        <v>0.5972682054024278</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2071113724333695</v>
+        <v>0.2088499473155911</v>
       </c>
       <c r="C93">
-        <v>-2503.163546062043</v>
+        <v>-2577.287144715825</v>
       </c>
       <c r="D93">
-        <v>1848.874453937957</v>
+        <v>1831.968855284175</v>
       </c>
       <c r="E93">
-        <v>3733.738</v>
+        <v>3790.956</v>
       </c>
       <c r="F93">
-        <v>5206.838</v>
+        <v>5264.056</v>
       </c>
       <c r="G93">
         <v>854.8</v>
@@ -9047,37 +9047,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M93">
-        <v>1143.720956659732</v>
+        <v>1156.289318820828</v>
       </c>
       <c r="N93">
-        <v>-460.612793394426</v>
+        <v>-473.1811555555221</v>
       </c>
       <c r="O93">
-        <v>-138.1838380183278</v>
+        <v>-141.9543466666566</v>
       </c>
       <c r="P93">
-        <v>-322.4289553760982</v>
+        <v>-331.2268088888654</v>
       </c>
       <c r="Q93">
-        <v>-245.1289553760981</v>
+        <v>-253.9268088888654</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4782126508540689</v>
+        <v>0.5322642322108276</v>
       </c>
       <c r="T93">
-        <v>6.292130948717255</v>
+        <v>7.078647317306913</v>
       </c>
       <c r="U93">
         <v>0.2196574882221671</v>
       </c>
       <c r="V93">
-        <v>0.1791804616207283</v>
+        <v>0.1772328479074595</v>
       </c>
       <c r="W93">
-        <v>0.1802991580840695</v>
+        <v>0.1807269660203532</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5972682054024278</v>
+        <v>0.5907761596915317</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2088499473155911</v>
+        <v>0.2105885221978128</v>
       </c>
       <c r="C94">
-        <v>-2577.287144715825</v>
+        <v>-2651.104384358591</v>
       </c>
       <c r="D94">
-        <v>1831.968855284175</v>
+        <v>1815.369615641408</v>
       </c>
       <c r="E94">
-        <v>3790.956</v>
+        <v>3848.174</v>
       </c>
       <c r="F94">
-        <v>5264.056</v>
+        <v>5321.273999999999</v>
       </c>
       <c r="G94">
         <v>854.8</v>
@@ -9129,37 +9129,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M94">
-        <v>1156.289318820828</v>
+        <v>1168.857680981924</v>
       </c>
       <c r="N94">
-        <v>-473.1811555555221</v>
+        <v>-485.7495177166179</v>
       </c>
       <c r="O94">
-        <v>-141.9543466666566</v>
+        <v>-145.7248553149854</v>
       </c>
       <c r="P94">
-        <v>-331.2268088888654</v>
+        <v>-340.0246624016326</v>
       </c>
       <c r="Q94">
-        <v>-253.9268088888654</v>
+        <v>-262.7246624016325</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5322642322108276</v>
+        <v>0.6017591225266602</v>
       </c>
       <c r="T94">
-        <v>7.078647317306913</v>
+        <v>8.089882648350759</v>
       </c>
       <c r="U94">
         <v>0.2196574882221671</v>
       </c>
       <c r="V94">
-        <v>0.1772328479074595</v>
+        <v>0.1753271183600675</v>
       </c>
       <c r="W94">
-        <v>0.1807269660203532</v>
+        <v>0.1811455737859641</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5907761596915317</v>
+        <v>0.5844237278668918</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2105885221978128</v>
+        <v>0.2123270970800345</v>
       </c>
       <c r="C95">
-        <v>-2651.104384358591</v>
+        <v>-2724.623517853713</v>
       </c>
       <c r="D95">
-        <v>1815.369615641408</v>
+        <v>1799.068482146286</v>
       </c>
       <c r="E95">
-        <v>3848.174</v>
+        <v>3905.391999999999</v>
       </c>
       <c r="F95">
-        <v>5321.273999999999</v>
+        <v>5378.491999999999</v>
       </c>
       <c r="G95">
         <v>854.8</v>
@@ -9211,37 +9211,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M95">
-        <v>1168.857680981924</v>
+        <v>1181.42604314302</v>
       </c>
       <c r="N95">
-        <v>-485.7495177166179</v>
+        <v>-498.3178798777139</v>
       </c>
       <c r="O95">
-        <v>-145.7248553149854</v>
+        <v>-149.4953639633142</v>
       </c>
       <c r="P95">
-        <v>-340.0246624016326</v>
+        <v>-348.8225159143998</v>
       </c>
       <c r="Q95">
-        <v>-262.7246624016325</v>
+        <v>-271.5225159143997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6017591225266602</v>
+        <v>0.6944189762811036</v>
       </c>
       <c r="T95">
-        <v>8.089882648350759</v>
+        <v>9.438196423075887</v>
       </c>
       <c r="U95">
         <v>0.2196574882221671</v>
       </c>
       <c r="V95">
-        <v>0.1753271183600675</v>
+        <v>0.173461936249854</v>
       </c>
       <c r="W95">
-        <v>0.1811455737859641</v>
+        <v>0.1815552750033705</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5844237278668918</v>
+        <v>0.57820645416618</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2123270970800345</v>
+        <v>0.2140656719622561</v>
       </c>
       <c r="C96">
-        <v>-2724.623517853713</v>
+        <v>-2797.852504275897</v>
       </c>
       <c r="D96">
-        <v>1799.068482146286</v>
+        <v>1783.057495724104</v>
       </c>
       <c r="E96">
-        <v>3905.391999999999</v>
+        <v>3962.61</v>
       </c>
       <c r="F96">
-        <v>5378.491999999999</v>
+        <v>5435.71</v>
       </c>
       <c r="G96">
         <v>854.8</v>
@@ -9293,37 +9293,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M96">
-        <v>1181.42604314302</v>
+        <v>1193.994405304116</v>
       </c>
       <c r="N96">
-        <v>-498.3178798777139</v>
+        <v>-510.88624203881</v>
       </c>
       <c r="O96">
-        <v>-149.4953639633142</v>
+        <v>-153.265872611643</v>
       </c>
       <c r="P96">
-        <v>-348.8225159143998</v>
+        <v>-357.620369427167</v>
       </c>
       <c r="Q96">
-        <v>-271.5225159143997</v>
+        <v>-280.320369427167</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6944189762811036</v>
+        <v>0.8241427715373248</v>
       </c>
       <c r="T96">
-        <v>9.438196423075887</v>
+        <v>11.32583570769107</v>
       </c>
       <c r="U96">
         <v>0.2196574882221671</v>
       </c>
       <c r="V96">
-        <v>0.173461936249854</v>
+        <v>0.1716360211314345</v>
       </c>
       <c r="W96">
-        <v>0.1815552750033705</v>
+        <v>0.1819563509319894</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.57820645416618</v>
+        <v>0.572120070438115</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2140656719622561</v>
+        <v>0.2158042468444778</v>
       </c>
       <c r="C97">
-        <v>-2797.852504275897</v>
+        <v>-2870.799021868861</v>
       </c>
       <c r="D97">
-        <v>1783.057495724104</v>
+        <v>1767.328978131138</v>
       </c>
       <c r="E97">
-        <v>3962.61</v>
+        <v>4019.828</v>
       </c>
       <c r="F97">
-        <v>5435.71</v>
+        <v>5492.928</v>
       </c>
       <c r="G97">
         <v>854.8</v>
@@ -9375,37 +9375,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M97">
-        <v>1193.994405304116</v>
+        <v>1206.562767465212</v>
       </c>
       <c r="N97">
-        <v>-510.88624203881</v>
+        <v>-523.454604199906</v>
       </c>
       <c r="O97">
-        <v>-153.265872611643</v>
+        <v>-157.0363812599718</v>
       </c>
       <c r="P97">
-        <v>-357.620369427167</v>
+        <v>-366.4182229399343</v>
       </c>
       <c r="Q97">
-        <v>-280.320369427167</v>
+        <v>-289.1182229399342</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8241427715373248</v>
+        <v>1.018728464421657</v>
       </c>
       <c r="T97">
-        <v>11.32583570769107</v>
+        <v>14.15729463461385</v>
       </c>
       <c r="U97">
         <v>0.2196574882221671</v>
       </c>
       <c r="V97">
-        <v>0.1716360211314345</v>
+        <v>0.1698481459113154</v>
       </c>
       <c r="W97">
-        <v>0.1819563509319894</v>
+        <v>0.1823490711120954</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.572120070438115</v>
+        <v>0.5661604863710512</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2158042468444778</v>
+        <v>0.2175428217266995</v>
       </c>
       <c r="C98">
-        <v>-2870.799021868861</v>
+        <v>-2943.470480323228</v>
       </c>
       <c r="D98">
-        <v>1767.328978131138</v>
+        <v>1751.875519676771</v>
       </c>
       <c r="E98">
-        <v>4019.827999999999</v>
+        <v>4077.045999999999</v>
       </c>
       <c r="F98">
-        <v>5492.927999999999</v>
+        <v>5550.145999999999</v>
       </c>
       <c r="G98">
         <v>854.8</v>
@@ -9457,37 +9457,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M98">
-        <v>1206.562767465212</v>
+        <v>1219.131129626308</v>
       </c>
       <c r="N98">
-        <v>-523.4546041999058</v>
+        <v>-536.0229663610016</v>
       </c>
       <c r="O98">
-        <v>-157.0363812599717</v>
+        <v>-160.8068899083005</v>
       </c>
       <c r="P98">
-        <v>-366.4182229399341</v>
+        <v>-375.2160764527011</v>
       </c>
       <c r="Q98">
-        <v>-289.118222939934</v>
+        <v>-297.9160764527011</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.018728464421654</v>
+        <v>1.343037952562205</v>
       </c>
       <c r="T98">
-        <v>14.15729463461381</v>
+        <v>18.87639284615175</v>
       </c>
       <c r="U98">
         <v>0.2196574882221671</v>
       </c>
       <c r="V98">
-        <v>0.1698481459113154</v>
+        <v>0.1680971340977967</v>
       </c>
       <c r="W98">
-        <v>0.1823490711120954</v>
+        <v>0.1827336939689003</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5661604863710513</v>
+        <v>0.5603237803259891</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2175428217266995</v>
+        <v>0.2192813966089212</v>
       </c>
       <c r="C99">
-        <v>-2943.470480323228</v>
+        <v>-3015.874032415833</v>
       </c>
       <c r="D99">
-        <v>1751.875519676771</v>
+        <v>1736.689967584167</v>
       </c>
       <c r="E99">
-        <v>4077.045999999999</v>
+        <v>4134.263999999999</v>
       </c>
       <c r="F99">
-        <v>5550.145999999999</v>
+        <v>5607.364</v>
       </c>
       <c r="G99">
         <v>854.8</v>
@@ -9539,37 +9539,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M99">
-        <v>1219.131129626308</v>
+        <v>1231.699491787404</v>
       </c>
       <c r="N99">
-        <v>-536.0229663610016</v>
+        <v>-548.5913285220979</v>
       </c>
       <c r="O99">
-        <v>-160.8068899083005</v>
+        <v>-164.5773985566294</v>
       </c>
       <c r="P99">
-        <v>-375.2160764527011</v>
+        <v>-384.0139299654685</v>
       </c>
       <c r="Q99">
-        <v>-297.9160764527011</v>
+        <v>-306.7139299654685</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.343037952562205</v>
+        <v>1.991656928843308</v>
       </c>
       <c r="T99">
-        <v>18.87639284615175</v>
+        <v>28.31458926922762</v>
       </c>
       <c r="U99">
         <v>0.2196574882221671</v>
       </c>
       <c r="V99">
-        <v>0.1680971340977967</v>
+        <v>0.1663818572192477</v>
       </c>
       <c r="W99">
-        <v>0.1827336939689003</v>
+        <v>0.1831104673796479</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5603237803259891</v>
+        <v>0.5546061907308257</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2192813966089212</v>
+        <v>0.2210199714911429</v>
       </c>
       <c r="C100">
-        <v>-3015.874032415833</v>
+        <v>-3088.016585048893</v>
       </c>
       <c r="D100">
-        <v>1736.689967584167</v>
+        <v>1721.765414951107</v>
       </c>
       <c r="E100">
-        <v>4134.263999999999</v>
+        <v>4191.482</v>
       </c>
       <c r="F100">
-        <v>5607.364</v>
+        <v>5664.581999999999</v>
       </c>
       <c r="G100">
         <v>854.8</v>
@@ -9621,37 +9621,37 @@
         <v>683.1081632653061</v>
       </c>
       <c r="M100">
-        <v>1231.699491787404</v>
+        <v>1244.2678539485</v>
       </c>
       <c r="N100">
-        <v>-548.5913285220979</v>
+        <v>-561.1596906831937</v>
       </c>
       <c r="O100">
-        <v>-164.5773985566294</v>
+        <v>-168.3479072049581</v>
       </c>
       <c r="P100">
-        <v>-384.0139299654685</v>
+        <v>-392.8117834782356</v>
       </c>
       <c r="Q100">
-        <v>-306.7139299654685</v>
+        <v>-315.5117834782355</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.991656928843308</v>
+        <v>3.937513857686616</v>
       </c>
       <c r="T100">
-        <v>28.31458926922762</v>
+        <v>56.62917853845524</v>
       </c>
       <c r="U100">
         <v>0.2196574882221671</v>
       </c>
       <c r="V100">
-        <v>0.1663818572192477</v>
+        <v>0.1647012323988513</v>
       </c>
       <c r="W100">
-        <v>0.1831104673796479</v>
+        <v>0.1834796292063401</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5546061907308257</v>
+        <v>0.5490041079961709</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2210199714911429</v>
-      </c>
-      <c r="C101">
-        <v>-3088.016585048893</v>
-      </c>
-      <c r="D101">
-        <v>1721.765414951107</v>
-      </c>
-      <c r="E101">
-        <v>4191.482</v>
-      </c>
-      <c r="F101">
-        <v>5664.581999999999</v>
-      </c>
-      <c r="G101">
-        <v>854.8</v>
-      </c>
-      <c r="H101">
-        <v>4248.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>760.4081632653061</v>
-      </c>
-      <c r="K101">
-        <v>77.30000000000007</v>
-      </c>
-      <c r="L101">
-        <v>683.1081632653061</v>
-      </c>
-      <c r="M101">
-        <v>1244.2678539485</v>
-      </c>
-      <c r="N101">
-        <v>-561.1596906831937</v>
-      </c>
-      <c r="O101">
-        <v>-168.3479072049581</v>
-      </c>
-      <c r="P101">
-        <v>-392.8117834782356</v>
-      </c>
-      <c r="Q101">
-        <v>-315.5117834782355</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.937513857686616</v>
-      </c>
-      <c r="T101">
-        <v>56.62917853845524</v>
-      </c>
-      <c r="U101">
-        <v>0.2196574882221671</v>
-      </c>
-      <c r="V101">
-        <v>0.1647012323988513</v>
-      </c>
-      <c r="W101">
-        <v>0.1834796292063401</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5490041079961709</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
